--- a/docs/101_方音符號聲韻調對照表.xlsx
+++ b/docs/101_方音符號聲韻調對照表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3DF082-0B86-4BC6-92A2-B95FD63574CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C414E980-AA9C-4AF8-8663-B4040A7DB815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{298E0E31-C5B6-4337-BAAB-84B2B6E61BF1}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="7" xr2:uid="{298E0E31-C5B6-4337-BAAB-84B2B6E61BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="宋人三十六字母表" sheetId="10" r:id="rId1"/>
@@ -11949,14 +11949,56 @@
     <xf numFmtId="0" fontId="113" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="distributed" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="141" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="141" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="110" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11965,33 +12007,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="17" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="113" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12012,58 +12027,46 @@
     <xf numFmtId="0" fontId="113" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="distributed" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="141" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="113" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="distributed" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="111" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="113" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="113" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="113" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="17" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="110" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="17" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="176" fontId="122" fillId="19" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="122" fillId="19" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="122" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12072,7 +12075,82 @@
     <xf numFmtId="176" fontId="122" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12099,30 +12177,6 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -12135,56 +12189,29 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -12198,35 +12225,8 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -30975,54 +30975,54 @@
   <sheetData>
     <row r="1" spans="2:14" ht="10.5" customHeight="1"/>
     <row r="2" spans="2:14" ht="38.25">
-      <c r="B2" s="288" t="s">
+      <c r="B2" s="268" t="s">
         <v>1411</v>
       </c>
-      <c r="C2" s="255"/>
-      <c r="D2" s="280" t="s">
+      <c r="C2" s="269"/>
+      <c r="D2" s="266" t="s">
         <v>1412</v>
       </c>
-      <c r="E2" s="277" t="s">
+      <c r="E2" s="263" t="s">
         <v>1426</v>
       </c>
-      <c r="F2" s="278"/>
-      <c r="G2" s="278"/>
-      <c r="H2" s="278"/>
-      <c r="I2" s="278"/>
-      <c r="J2" s="278"/>
-      <c r="K2" s="278"/>
-      <c r="L2" s="279"/>
+      <c r="F2" s="264"/>
+      <c r="G2" s="264"/>
+      <c r="H2" s="264"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="265"/>
       <c r="N2" s="247" t="s">
         <v>1509</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="32.25" customHeight="1">
-      <c r="B3" s="256"/>
-      <c r="C3" s="257"/>
-      <c r="D3" s="281"/>
-      <c r="E3" s="265" t="s">
+      <c r="B3" s="270"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="267"/>
+      <c r="E3" s="261" t="s">
         <v>1427</v>
       </c>
-      <c r="F3" s="266"/>
-      <c r="G3" s="265" t="s">
+      <c r="F3" s="262"/>
+      <c r="G3" s="261" t="s">
         <v>1428</v>
       </c>
-      <c r="H3" s="266"/>
-      <c r="I3" s="265" t="s">
+      <c r="H3" s="262"/>
+      <c r="I3" s="261" t="s">
         <v>1429</v>
       </c>
-      <c r="J3" s="266"/>
-      <c r="K3" s="265" t="s">
+      <c r="J3" s="262"/>
+      <c r="K3" s="261" t="s">
         <v>1430</v>
       </c>
-      <c r="L3" s="266"/>
+      <c r="L3" s="262"/>
       <c r="N3" s="248"/>
     </row>
     <row r="4" spans="2:14" ht="51">
-      <c r="B4" s="285" t="s">
+      <c r="B4" s="255" t="s">
         <v>971</v>
       </c>
-      <c r="C4" s="273" t="s">
+      <c r="C4" s="258" t="s">
         <v>1413</v>
       </c>
       <c r="D4" s="250" t="s">
@@ -31057,8 +31057,8 @@
       </c>
     </row>
     <row r="5" spans="2:14">
-      <c r="B5" s="286"/>
-      <c r="C5" s="275"/>
+      <c r="B5" s="256"/>
+      <c r="C5" s="259"/>
       <c r="D5" s="251"/>
       <c r="E5" s="243" t="s">
         <v>19</v>
@@ -31089,8 +31089,8 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="51">
-      <c r="B6" s="286"/>
-      <c r="C6" s="273" t="s">
+      <c r="B6" s="256"/>
+      <c r="C6" s="258" t="s">
         <v>1414</v>
       </c>
       <c r="D6" s="250" t="s">
@@ -31125,8 +31125,8 @@
       </c>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="287"/>
-      <c r="C7" s="275"/>
+      <c r="B7" s="257"/>
+      <c r="C7" s="259"/>
       <c r="D7" s="251"/>
       <c r="E7" s="195"/>
       <c r="F7" s="196"/>
@@ -31141,10 +31141,10 @@
       </c>
     </row>
     <row r="8" spans="2:14" ht="51">
-      <c r="B8" s="285" t="s">
+      <c r="B8" s="255" t="s">
         <v>1419</v>
       </c>
-      <c r="C8" s="273" t="s">
+      <c r="C8" s="258" t="s">
         <v>1420</v>
       </c>
       <c r="D8" s="250" t="s">
@@ -31179,8 +31179,8 @@
       </c>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="286"/>
-      <c r="C9" s="275"/>
+      <c r="B9" s="256"/>
+      <c r="C9" s="259"/>
       <c r="D9" s="251"/>
       <c r="E9" s="243" t="s">
         <v>43</v>
@@ -31207,8 +31207,8 @@
       </c>
     </row>
     <row r="10" spans="2:14" ht="51">
-      <c r="B10" s="286"/>
-      <c r="C10" s="273" t="s">
+      <c r="B10" s="256"/>
+      <c r="C10" s="258" t="s">
         <v>1421</v>
       </c>
       <c r="D10" s="250" t="s">
@@ -31243,8 +31243,8 @@
       </c>
     </row>
     <row r="11" spans="2:14">
-      <c r="B11" s="287"/>
-      <c r="C11" s="275"/>
+      <c r="B11" s="257"/>
+      <c r="C11" s="259"/>
       <c r="D11" s="251"/>
       <c r="E11" s="195"/>
       <c r="F11" s="196"/>
@@ -31259,10 +31259,10 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="51">
-      <c r="B12" s="282" t="s">
+      <c r="B12" s="252" t="s">
         <v>1435</v>
       </c>
-      <c r="C12" s="273" t="s">
+      <c r="C12" s="258" t="s">
         <v>1436</v>
       </c>
       <c r="D12" s="250" t="s">
@@ -31293,9 +31293,9 @@
       </c>
     </row>
     <row r="13" spans="2:14">
-      <c r="B13" s="283"/>
-      <c r="C13" s="274"/>
-      <c r="D13" s="276"/>
+      <c r="B13" s="253"/>
+      <c r="C13" s="260"/>
+      <c r="D13" s="278"/>
       <c r="E13" s="243" t="s">
         <v>73</v>
       </c>
@@ -31321,9 +31321,9 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="51">
-      <c r="B14" s="283"/>
-      <c r="C14" s="274"/>
-      <c r="D14" s="276"/>
+      <c r="B14" s="253"/>
+      <c r="C14" s="260"/>
+      <c r="D14" s="278"/>
       <c r="E14" s="241" t="s">
         <v>1482</v>
       </c>
@@ -31343,8 +31343,8 @@
       <c r="N14" s="248"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="B15" s="283"/>
-      <c r="C15" s="275"/>
+      <c r="B15" s="253"/>
+      <c r="C15" s="259"/>
       <c r="D15" s="251"/>
       <c r="E15" s="243" t="s">
         <v>1007</v>
@@ -31363,8 +31363,8 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="51">
-      <c r="B16" s="283"/>
-      <c r="C16" s="273" t="s">
+      <c r="B16" s="253"/>
+      <c r="C16" s="258" t="s">
         <v>1437</v>
       </c>
       <c r="D16" s="250" t="s">
@@ -31395,9 +31395,9 @@
       </c>
     </row>
     <row r="17" spans="2:16">
-      <c r="B17" s="283"/>
-      <c r="C17" s="274"/>
-      <c r="D17" s="276"/>
+      <c r="B17" s="253"/>
+      <c r="C17" s="260"/>
+      <c r="D17" s="278"/>
       <c r="E17" s="243" t="s">
         <v>69</v>
       </c>
@@ -31423,9 +31423,9 @@
       </c>
     </row>
     <row r="18" spans="2:16" ht="51">
-      <c r="B18" s="283"/>
-      <c r="C18" s="274"/>
-      <c r="D18" s="276"/>
+      <c r="B18" s="253"/>
+      <c r="C18" s="260"/>
+      <c r="D18" s="278"/>
       <c r="E18" s="241" t="s">
         <v>1501</v>
       </c>
@@ -31447,8 +31447,8 @@
       </c>
     </row>
     <row r="19" spans="2:16">
-      <c r="B19" s="284"/>
-      <c r="C19" s="275"/>
+      <c r="B19" s="254"/>
+      <c r="C19" s="259"/>
       <c r="D19" s="251"/>
       <c r="E19" s="243" t="s">
         <v>92</v>
@@ -31467,10 +31467,10 @@
       </c>
     </row>
     <row r="20" spans="2:16" ht="45.75" customHeight="1">
-      <c r="B20" s="267" t="s">
+      <c r="B20" s="272" t="s">
         <v>1438</v>
       </c>
-      <c r="C20" s="268"/>
+      <c r="C20" s="273"/>
       <c r="D20" s="250" t="s">
         <v>1439</v>
       </c>
@@ -31503,8 +31503,8 @@
       </c>
     </row>
     <row r="21" spans="2:16">
-      <c r="B21" s="269"/>
-      <c r="C21" s="270"/>
+      <c r="B21" s="274"/>
+      <c r="C21" s="275"/>
       <c r="D21" s="251"/>
       <c r="E21" s="243" t="s">
         <v>45</v>
@@ -31535,10 +31535,10 @@
       </c>
     </row>
     <row r="22" spans="2:16" ht="45.75" customHeight="1">
-      <c r="B22" s="267" t="s">
+      <c r="B22" s="272" t="s">
         <v>1033</v>
       </c>
-      <c r="C22" s="268"/>
+      <c r="C22" s="273"/>
       <c r="D22" s="250" t="s">
         <v>1033</v>
       </c>
@@ -31559,8 +31559,8 @@
       </c>
     </row>
     <row r="23" spans="2:16" s="192" customFormat="1">
-      <c r="B23" s="271"/>
-      <c r="C23" s="272"/>
+      <c r="B23" s="276"/>
+      <c r="C23" s="277"/>
       <c r="D23" s="251"/>
       <c r="E23" s="243" t="s">
         <v>1039</v>
@@ -31581,8 +31581,8 @@
       <c r="P23" s="239"/>
     </row>
     <row r="24" spans="2:16" ht="45.75" customHeight="1">
-      <c r="B24" s="271"/>
-      <c r="C24" s="272"/>
+      <c r="B24" s="276"/>
+      <c r="C24" s="277"/>
       <c r="D24" s="250" t="s">
         <v>1439</v>
       </c>
@@ -31607,8 +31607,8 @@
       </c>
     </row>
     <row r="25" spans="2:16" s="192" customFormat="1">
-      <c r="B25" s="271"/>
-      <c r="C25" s="272"/>
+      <c r="B25" s="276"/>
+      <c r="C25" s="277"/>
       <c r="D25" s="251"/>
       <c r="E25" s="243" t="s">
         <v>86</v>
@@ -31629,8 +31629,8 @@
       <c r="P25" s="239"/>
     </row>
     <row r="26" spans="2:16" ht="45.75" customHeight="1">
-      <c r="B26" s="271"/>
-      <c r="C26" s="272"/>
+      <c r="B26" s="276"/>
+      <c r="C26" s="277"/>
       <c r="D26" s="250" t="s">
         <v>1441</v>
       </c>
@@ -31651,8 +31651,8 @@
       </c>
     </row>
     <row r="27" spans="2:16" s="192" customFormat="1">
-      <c r="B27" s="269"/>
-      <c r="C27" s="270"/>
+      <c r="B27" s="274"/>
+      <c r="C27" s="275"/>
       <c r="D27" s="251"/>
       <c r="E27" s="195"/>
       <c r="F27" s="196"/>
@@ -31669,10 +31669,10 @@
       <c r="P27" s="239"/>
     </row>
     <row r="28" spans="2:16" ht="45.75" customHeight="1">
-      <c r="B28" s="267" t="s">
+      <c r="B28" s="272" t="s">
         <v>1443</v>
       </c>
-      <c r="C28" s="268"/>
+      <c r="C28" s="273"/>
       <c r="D28" s="250" t="s">
         <v>1417</v>
       </c>
@@ -31693,8 +31693,8 @@
       </c>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="269"/>
-      <c r="C29" s="270"/>
+      <c r="B29" s="274"/>
+      <c r="C29" s="275"/>
       <c r="D29" s="251"/>
       <c r="E29" s="195"/>
       <c r="F29" s="196"/>
@@ -31711,10 +31711,10 @@
       <c r="N29" s="248"/>
     </row>
     <row r="30" spans="2:16" ht="51">
-      <c r="B30" s="267" t="s">
+      <c r="B30" s="272" t="s">
         <v>1444</v>
       </c>
-      <c r="C30" s="268"/>
+      <c r="C30" s="273"/>
       <c r="D30" s="250" t="s">
         <v>1440</v>
       </c>
@@ -31735,8 +31735,8 @@
       </c>
     </row>
     <row r="31" spans="2:16">
-      <c r="B31" s="269"/>
-      <c r="C31" s="270"/>
+      <c r="B31" s="274"/>
+      <c r="C31" s="275"/>
       <c r="D31" s="251"/>
       <c r="E31" s="195"/>
       <c r="F31" s="196"/>
@@ -31863,24 +31863,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B12:B19"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
     <mergeCell ref="B30:C31"/>
     <mergeCell ref="D30:D31"/>
     <mergeCell ref="D10:D11"/>
@@ -31895,6 +31877,24 @@
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="D28:D29"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="B12:B19"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40121,58 +40121,58 @@
   <sheetData>
     <row r="1" spans="2:19" ht="10.5" customHeight="1"/>
     <row r="2" spans="2:19" ht="39">
-      <c r="B2" s="254" t="s">
+      <c r="B2" s="283" t="s">
         <v>965</v>
       </c>
-      <c r="C2" s="255"/>
-      <c r="D2" s="258" t="s">
+      <c r="C2" s="269"/>
+      <c r="D2" s="284" t="s">
         <v>966</v>
       </c>
-      <c r="E2" s="259"/>
-      <c r="F2" s="259"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="261" t="s">
+      <c r="E2" s="285"/>
+      <c r="F2" s="285"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="279" t="s">
         <v>967</v>
       </c>
-      <c r="I2" s="262"/>
-      <c r="J2" s="261" t="s">
+      <c r="I2" s="280"/>
+      <c r="J2" s="279" t="s">
         <v>968</v>
       </c>
-      <c r="K2" s="262"/>
-      <c r="L2" s="261" t="s">
+      <c r="K2" s="280"/>
+      <c r="L2" s="279" t="s">
         <v>969</v>
       </c>
-      <c r="M2" s="262"/>
-      <c r="N2" s="261" t="s">
+      <c r="M2" s="280"/>
+      <c r="N2" s="279" t="s">
         <v>970</v>
       </c>
-      <c r="O2" s="262"/>
+      <c r="O2" s="280"/>
     </row>
     <row r="3" spans="2:19" ht="32.25" customHeight="1">
-      <c r="B3" s="256"/>
-      <c r="C3" s="257"/>
-      <c r="D3" s="265" t="s">
+      <c r="B3" s="270"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="261" t="s">
         <v>1046</v>
       </c>
-      <c r="E3" s="266"/>
-      <c r="F3" s="265" t="s">
+      <c r="E3" s="262"/>
+      <c r="F3" s="261" t="s">
         <v>1047</v>
       </c>
-      <c r="G3" s="266"/>
-      <c r="H3" s="263"/>
-      <c r="I3" s="264"/>
-      <c r="J3" s="263"/>
-      <c r="K3" s="264"/>
-      <c r="L3" s="263"/>
-      <c r="M3" s="264"/>
-      <c r="N3" s="263"/>
-      <c r="O3" s="264"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="281"/>
+      <c r="I3" s="282"/>
+      <c r="J3" s="281"/>
+      <c r="K3" s="282"/>
+      <c r="L3" s="281"/>
+      <c r="M3" s="282"/>
+      <c r="N3" s="281"/>
+      <c r="O3" s="282"/>
     </row>
     <row r="4" spans="2:19" ht="45.75">
       <c r="B4" s="250" t="s">
         <v>971</v>
       </c>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="287" t="s">
         <v>971</v>
       </c>
       <c r="D4" s="193" t="s">
@@ -40211,7 +40211,7 @@
     </row>
     <row r="5" spans="2:19" ht="44.25">
       <c r="B5" s="251"/>
-      <c r="C5" s="253"/>
+      <c r="C5" s="288"/>
       <c r="D5" s="195" t="s">
         <v>19</v>
       </c>
@@ -40246,7 +40246,7 @@
       <c r="B6" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="252" t="s">
+      <c r="C6" s="287" t="s">
         <v>983</v>
       </c>
       <c r="D6" s="193" t="s">
@@ -40282,7 +40282,7 @@
     </row>
     <row r="7" spans="2:19" ht="44.25">
       <c r="B7" s="251"/>
-      <c r="C7" s="253"/>
+      <c r="C7" s="288"/>
       <c r="D7" s="195" t="s">
         <v>43</v>
       </c>
@@ -40316,7 +40316,7 @@
       <c r="B8" s="250" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="252" t="s">
+      <c r="C8" s="287" t="s">
         <v>995</v>
       </c>
       <c r="D8" s="193" t="s">
@@ -40352,7 +40352,7 @@
     </row>
     <row r="9" spans="2:19" ht="44.25">
       <c r="B9" s="251"/>
-      <c r="C9" s="253"/>
+      <c r="C9" s="288"/>
       <c r="D9" s="195" t="s">
         <v>73</v>
       </c>
@@ -40386,7 +40386,7 @@
       <c r="B10" s="250" t="s">
         <v>1009</v>
       </c>
-      <c r="C10" s="252" t="s">
+      <c r="C10" s="287" t="s">
         <v>1009</v>
       </c>
       <c r="D10" s="193" t="s">
@@ -40422,7 +40422,7 @@
     </row>
     <row r="11" spans="2:19" ht="44.25">
       <c r="B11" s="251"/>
-      <c r="C11" s="253"/>
+      <c r="C11" s="288"/>
       <c r="D11" s="195" t="s">
         <v>69</v>
       </c>
@@ -40456,7 +40456,7 @@
       <c r="B12" s="250" t="s">
         <v>1021</v>
       </c>
-      <c r="C12" s="252" t="s">
+      <c r="C12" s="287" t="s">
         <v>1021</v>
       </c>
       <c r="D12" s="193" t="s">
@@ -40494,7 +40494,7 @@
     </row>
     <row r="13" spans="2:19" ht="44.25">
       <c r="B13" s="251"/>
-      <c r="C13" s="253"/>
+      <c r="C13" s="288"/>
       <c r="D13" s="195" t="s">
         <v>45</v>
       </c>
@@ -40528,7 +40528,7 @@
       <c r="B14" s="250" t="s">
         <v>1033</v>
       </c>
-      <c r="C14" s="252" t="s">
+      <c r="C14" s="287" t="s">
         <v>1033</v>
       </c>
       <c r="D14" s="193"/>
@@ -40552,7 +40552,7 @@
     </row>
     <row r="15" spans="2:19" ht="44.25">
       <c r="B15" s="251"/>
-      <c r="C15" s="253"/>
+      <c r="C15" s="288"/>
       <c r="D15" s="195"/>
       <c r="E15" s="196"/>
       <c r="F15" s="195"/>
@@ -40574,7 +40574,7 @@
       <c r="B16" s="250" t="s">
         <v>1037</v>
       </c>
-      <c r="C16" s="252" t="s">
+      <c r="C16" s="287" t="s">
         <v>1038</v>
       </c>
       <c r="D16" s="197" t="s">
@@ -40598,7 +40598,7 @@
     </row>
     <row r="17" spans="2:15" ht="44.25">
       <c r="B17" s="251"/>
-      <c r="C17" s="253"/>
+      <c r="C17" s="288"/>
       <c r="D17" s="198"/>
       <c r="E17" s="196" t="s">
         <v>1040</v>
@@ -40618,6 +40618,20 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
     <mergeCell ref="N2:O3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
@@ -40626,20 +40640,6 @@
     <mergeCell ref="H2:I3"/>
     <mergeCell ref="J2:K3"/>
     <mergeCell ref="L2:M3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40657,15 +40657,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="30">
-      <c r="B2" s="293" t="s">
+      <c r="B2" s="291" t="s">
         <v>1048</v>
       </c>
-      <c r="C2" s="293" t="s">
+      <c r="C2" s="291" t="s">
         <v>1049</v>
       </c>
-      <c r="D2" s="293"/>
-      <c r="E2" s="293"/>
-      <c r="F2" s="293"/>
+      <c r="D2" s="291"/>
+      <c r="E2" s="291"/>
+      <c r="F2" s="291"/>
       <c r="G2" s="199" t="s">
         <v>1050</v>
       </c>
@@ -40688,35 +40688,35 @@
       <c r="V2" s="201"/>
     </row>
     <row r="3" spans="2:22">
-      <c r="B3" s="293"/>
-      <c r="C3" s="293"/>
-      <c r="D3" s="293"/>
-      <c r="E3" s="293"/>
-      <c r="F3" s="293"/>
-      <c r="G3" s="291" t="s">
+      <c r="B3" s="291"/>
+      <c r="C3" s="291"/>
+      <c r="D3" s="291"/>
+      <c r="E3" s="291"/>
+      <c r="F3" s="291"/>
+      <c r="G3" s="292" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="292"/>
-      <c r="I3" s="291" t="s">
+      <c r="H3" s="293"/>
+      <c r="I3" s="292" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="292"/>
-      <c r="K3" s="291" t="s">
+      <c r="J3" s="293"/>
+      <c r="K3" s="292" t="s">
         <v>156</v>
       </c>
-      <c r="L3" s="292"/>
-      <c r="M3" s="291" t="s">
+      <c r="L3" s="293"/>
+      <c r="M3" s="292" t="s">
         <v>1052</v>
       </c>
-      <c r="N3" s="292"/>
-      <c r="O3" s="291" t="s">
+      <c r="N3" s="293"/>
+      <c r="O3" s="292" t="s">
         <v>1053</v>
       </c>
-      <c r="P3" s="292"/>
-      <c r="Q3" s="291" t="s">
+      <c r="P3" s="293"/>
+      <c r="Q3" s="292" t="s">
         <v>1054</v>
       </c>
-      <c r="R3" s="292"/>
+      <c r="R3" s="293"/>
       <c r="S3" s="203" t="s">
         <v>874</v>
       </c>
@@ -42732,18 +42732,15 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B46:B47"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B14:B15"/>
@@ -42756,15 +42753,18 @@
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -42795,293 +42795,293 @@
     <row r="2" spans="2:70" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="344" t="s">
+      <c r="D2" s="294" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="344"/>
-      <c r="F2" s="344"/>
-      <c r="G2" s="344"/>
-      <c r="H2" s="344"/>
-      <c r="I2" s="344"/>
-      <c r="J2" s="344"/>
-      <c r="K2" s="344"/>
-      <c r="L2" s="344" t="s">
+      <c r="E2" s="294"/>
+      <c r="F2" s="294"/>
+      <c r="G2" s="294"/>
+      <c r="H2" s="294"/>
+      <c r="I2" s="294"/>
+      <c r="J2" s="294"/>
+      <c r="K2" s="294"/>
+      <c r="L2" s="294" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="344"/>
-      <c r="N2" s="344"/>
-      <c r="O2" s="344"/>
-      <c r="P2" s="344"/>
-      <c r="Q2" s="344"/>
-      <c r="R2" s="344"/>
-      <c r="S2" s="344"/>
-      <c r="T2" s="344" t="s">
+      <c r="M2" s="294"/>
+      <c r="N2" s="294"/>
+      <c r="O2" s="294"/>
+      <c r="P2" s="294"/>
+      <c r="Q2" s="294"/>
+      <c r="R2" s="294"/>
+      <c r="S2" s="294"/>
+      <c r="T2" s="294" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="344"/>
-      <c r="V2" s="344"/>
-      <c r="W2" s="344"/>
-      <c r="X2" s="344"/>
-      <c r="Y2" s="344"/>
-      <c r="Z2" s="344"/>
-      <c r="AA2" s="344"/>
-      <c r="AB2" s="344" t="s">
+      <c r="U2" s="294"/>
+      <c r="V2" s="294"/>
+      <c r="W2" s="294"/>
+      <c r="X2" s="294"/>
+      <c r="Y2" s="294"/>
+      <c r="Z2" s="294"/>
+      <c r="AA2" s="294"/>
+      <c r="AB2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="AC2" s="344"/>
-      <c r="AD2" s="344"/>
-      <c r="AE2" s="344"/>
-      <c r="AF2" s="344"/>
-      <c r="AG2" s="344"/>
-      <c r="AH2" s="344"/>
-      <c r="AI2" s="344"/>
-      <c r="AJ2" s="344" t="s">
+      <c r="AC2" s="294"/>
+      <c r="AD2" s="294"/>
+      <c r="AE2" s="294"/>
+      <c r="AF2" s="294"/>
+      <c r="AG2" s="294"/>
+      <c r="AH2" s="294"/>
+      <c r="AI2" s="294"/>
+      <c r="AJ2" s="294" t="s">
         <v>4</v>
       </c>
-      <c r="AK2" s="344"/>
-      <c r="AL2" s="344"/>
-      <c r="AM2" s="344"/>
+      <c r="AK2" s="294"/>
+      <c r="AL2" s="294"/>
+      <c r="AM2" s="294"/>
       <c r="BP2" s="3"/>
     </row>
     <row r="3" spans="2:70" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="344" t="s">
+      <c r="D3" s="294" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="344"/>
-      <c r="F3" s="344"/>
-      <c r="G3" s="344"/>
-      <c r="H3" s="344"/>
-      <c r="I3" s="344"/>
-      <c r="J3" s="344"/>
-      <c r="K3" s="344"/>
-      <c r="L3" s="344" t="s">
+      <c r="E3" s="294"/>
+      <c r="F3" s="294"/>
+      <c r="G3" s="294"/>
+      <c r="H3" s="294"/>
+      <c r="I3" s="294"/>
+      <c r="J3" s="294"/>
+      <c r="K3" s="294"/>
+      <c r="L3" s="294" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="344"/>
-      <c r="N3" s="344"/>
-      <c r="O3" s="344"/>
-      <c r="P3" s="344"/>
-      <c r="Q3" s="344"/>
-      <c r="R3" s="344"/>
-      <c r="S3" s="344"/>
-      <c r="T3" s="344" t="s">
+      <c r="M3" s="294"/>
+      <c r="N3" s="294"/>
+      <c r="O3" s="294"/>
+      <c r="P3" s="294"/>
+      <c r="Q3" s="294"/>
+      <c r="R3" s="294"/>
+      <c r="S3" s="294"/>
+      <c r="T3" s="294" t="s">
         <v>7</v>
       </c>
-      <c r="U3" s="344"/>
-      <c r="V3" s="344"/>
-      <c r="W3" s="344"/>
-      <c r="X3" s="344"/>
-      <c r="Y3" s="344"/>
-      <c r="Z3" s="344"/>
-      <c r="AA3" s="344"/>
-      <c r="AB3" s="344" t="s">
+      <c r="U3" s="294"/>
+      <c r="V3" s="294"/>
+      <c r="W3" s="294"/>
+      <c r="X3" s="294"/>
+      <c r="Y3" s="294"/>
+      <c r="Z3" s="294"/>
+      <c r="AA3" s="294"/>
+      <c r="AB3" s="294" t="s">
         <v>8</v>
       </c>
-      <c r="AC3" s="344"/>
-      <c r="AD3" s="344"/>
-      <c r="AE3" s="344"/>
-      <c r="AF3" s="344"/>
-      <c r="AG3" s="344"/>
-      <c r="AH3" s="344"/>
-      <c r="AI3" s="344"/>
-      <c r="AJ3" s="344" t="s">
+      <c r="AC3" s="294"/>
+      <c r="AD3" s="294"/>
+      <c r="AE3" s="294"/>
+      <c r="AF3" s="294"/>
+      <c r="AG3" s="294"/>
+      <c r="AH3" s="294"/>
+      <c r="AI3" s="294"/>
+      <c r="AJ3" s="294" t="s">
         <v>9</v>
       </c>
-      <c r="AK3" s="344"/>
-      <c r="AL3" s="344"/>
-      <c r="AM3" s="344"/>
+      <c r="AK3" s="294"/>
+      <c r="AL3" s="294"/>
+      <c r="AM3" s="294"/>
       <c r="BP3" s="3"/>
     </row>
     <row r="4" spans="2:70" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="344" t="s">
+      <c r="D4" s="294" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="344"/>
-      <c r="F4" s="344"/>
-      <c r="G4" s="344"/>
-      <c r="H4" s="344" t="s">
+      <c r="E4" s="294"/>
+      <c r="F4" s="294"/>
+      <c r="G4" s="294"/>
+      <c r="H4" s="294" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="344"/>
-      <c r="J4" s="344"/>
-      <c r="K4" s="344"/>
-      <c r="L4" s="344" t="s">
+      <c r="I4" s="294"/>
+      <c r="J4" s="294"/>
+      <c r="K4" s="294"/>
+      <c r="L4" s="294" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="344"/>
-      <c r="N4" s="344"/>
-      <c r="O4" s="344"/>
-      <c r="P4" s="344" t="s">
+      <c r="M4" s="294"/>
+      <c r="N4" s="294"/>
+      <c r="O4" s="294"/>
+      <c r="P4" s="294" t="s">
         <v>11</v>
       </c>
-      <c r="Q4" s="344"/>
-      <c r="R4" s="344"/>
-      <c r="S4" s="344"/>
-      <c r="T4" s="344" t="s">
+      <c r="Q4" s="294"/>
+      <c r="R4" s="294"/>
+      <c r="S4" s="294"/>
+      <c r="T4" s="294" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="344"/>
-      <c r="V4" s="344"/>
-      <c r="W4" s="344"/>
-      <c r="X4" s="344" t="s">
+      <c r="U4" s="294"/>
+      <c r="V4" s="294"/>
+      <c r="W4" s="294"/>
+      <c r="X4" s="294" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" s="344"/>
-      <c r="Z4" s="344"/>
-      <c r="AA4" s="344"/>
-      <c r="AB4" s="344" t="s">
+      <c r="Y4" s="294"/>
+      <c r="Z4" s="294"/>
+      <c r="AA4" s="294"/>
+      <c r="AB4" s="294" t="s">
         <v>10</v>
       </c>
-      <c r="AC4" s="344"/>
-      <c r="AD4" s="344"/>
-      <c r="AE4" s="344"/>
-      <c r="AF4" s="344" t="s">
+      <c r="AC4" s="294"/>
+      <c r="AD4" s="294"/>
+      <c r="AE4" s="294"/>
+      <c r="AF4" s="294" t="s">
         <v>11</v>
       </c>
-      <c r="AG4" s="344"/>
-      <c r="AH4" s="344"/>
-      <c r="AI4" s="344"/>
-      <c r="AJ4" s="344" t="s">
+      <c r="AG4" s="294"/>
+      <c r="AH4" s="294"/>
+      <c r="AI4" s="294"/>
+      <c r="AJ4" s="294" t="s">
         <v>10</v>
       </c>
-      <c r="AK4" s="344"/>
-      <c r="AL4" s="344"/>
-      <c r="AM4" s="344"/>
-      <c r="AP4" s="344" t="s">
+      <c r="AK4" s="294"/>
+      <c r="AL4" s="294"/>
+      <c r="AM4" s="294"/>
+      <c r="AP4" s="294" t="s">
         <v>1044</v>
       </c>
-      <c r="AQ4" s="344"/>
-      <c r="AR4" s="344"/>
-      <c r="AS4" s="344"/>
-      <c r="AT4" s="344" t="s">
+      <c r="AQ4" s="294"/>
+      <c r="AR4" s="294"/>
+      <c r="AS4" s="294"/>
+      <c r="AT4" s="294" t="s">
         <v>11</v>
       </c>
-      <c r="AU4" s="344"/>
-      <c r="AV4" s="344"/>
-      <c r="AW4" s="344"/>
-      <c r="AX4" s="344" t="s">
+      <c r="AU4" s="294"/>
+      <c r="AV4" s="294"/>
+      <c r="AW4" s="294"/>
+      <c r="AX4" s="294" t="s">
         <v>1045</v>
       </c>
-      <c r="AY4" s="344"/>
-      <c r="AZ4" s="344"/>
-      <c r="BA4" s="344"/>
-      <c r="BB4" s="344" t="s">
+      <c r="AY4" s="294"/>
+      <c r="AZ4" s="294"/>
+      <c r="BA4" s="294"/>
+      <c r="BB4" s="294" t="s">
         <v>1043</v>
       </c>
-      <c r="BC4" s="344"/>
-      <c r="BD4" s="344"/>
-      <c r="BE4" s="344"/>
-      <c r="BF4" s="344" t="s">
+      <c r="BC4" s="294"/>
+      <c r="BD4" s="294"/>
+      <c r="BE4" s="294"/>
+      <c r="BF4" s="294" t="s">
         <v>1042</v>
       </c>
-      <c r="BG4" s="344"/>
-      <c r="BH4" s="344"/>
-      <c r="BI4" s="344"/>
-      <c r="BJ4" s="344" t="s">
+      <c r="BG4" s="294"/>
+      <c r="BH4" s="294"/>
+      <c r="BI4" s="294"/>
+      <c r="BJ4" s="294" t="s">
         <v>1041</v>
       </c>
-      <c r="BK4" s="344"/>
-      <c r="BL4" s="344"/>
-      <c r="BM4" s="344"/>
+      <c r="BK4" s="294"/>
+      <c r="BL4" s="294"/>
+      <c r="BM4" s="294"/>
       <c r="BP4" s="3"/>
     </row>
     <row r="5" spans="2:70" ht="33" customHeight="1">
-      <c r="B5" s="330" t="s">
+      <c r="B5" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="330"/>
-      <c r="D5" s="322"/>
-      <c r="E5" s="323"/>
-      <c r="F5" s="326"/>
-      <c r="G5" s="327"/>
-      <c r="H5" s="314" t="s">
+      <c r="C5" s="295"/>
+      <c r="D5" s="296"/>
+      <c r="E5" s="297"/>
+      <c r="F5" s="300"/>
+      <c r="G5" s="301"/>
+      <c r="H5" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="315"/>
-      <c r="J5" s="318" t="s">
+      <c r="I5" s="305"/>
+      <c r="J5" s="308" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="319"/>
-      <c r="L5" s="322"/>
-      <c r="M5" s="323"/>
-      <c r="N5" s="326"/>
-      <c r="O5" s="327"/>
-      <c r="P5" s="314"/>
-      <c r="Q5" s="315"/>
-      <c r="R5" s="318"/>
-      <c r="S5" s="319"/>
-      <c r="T5" s="322"/>
-      <c r="U5" s="323"/>
-      <c r="V5" s="326"/>
-      <c r="W5" s="327"/>
-      <c r="X5" s="314" t="s">
+      <c r="K5" s="309"/>
+      <c r="L5" s="296"/>
+      <c r="M5" s="297"/>
+      <c r="N5" s="300"/>
+      <c r="O5" s="301"/>
+      <c r="P5" s="304"/>
+      <c r="Q5" s="305"/>
+      <c r="R5" s="308"/>
+      <c r="S5" s="309"/>
+      <c r="T5" s="296"/>
+      <c r="U5" s="297"/>
+      <c r="V5" s="300"/>
+      <c r="W5" s="301"/>
+      <c r="X5" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="Y5" s="315"/>
-      <c r="Z5" s="318" t="s">
+      <c r="Y5" s="305"/>
+      <c r="Z5" s="308" t="s">
         <v>16</v>
       </c>
-      <c r="AA5" s="319"/>
-      <c r="AB5" s="322"/>
-      <c r="AC5" s="323"/>
-      <c r="AD5" s="326"/>
-      <c r="AE5" s="327"/>
-      <c r="AF5" s="314" t="s">
+      <c r="AA5" s="309"/>
+      <c r="AB5" s="296"/>
+      <c r="AC5" s="297"/>
+      <c r="AD5" s="300"/>
+      <c r="AE5" s="301"/>
+      <c r="AF5" s="304" t="s">
         <v>17</v>
       </c>
-      <c r="AG5" s="315"/>
-      <c r="AH5" s="318" t="s">
+      <c r="AG5" s="305"/>
+      <c r="AH5" s="308" t="s">
         <v>18</v>
       </c>
-      <c r="AI5" s="319"/>
-      <c r="AJ5" s="322"/>
-      <c r="AK5" s="323"/>
-      <c r="AL5" s="326"/>
-      <c r="AM5" s="327"/>
-      <c r="AP5" s="322" t="s">
+      <c r="AI5" s="309"/>
+      <c r="AJ5" s="296"/>
+      <c r="AK5" s="297"/>
+      <c r="AL5" s="300"/>
+      <c r="AM5" s="301"/>
+      <c r="AP5" s="296" t="s">
         <v>28</v>
       </c>
-      <c r="AQ5" s="323"/>
-      <c r="AR5" s="326" t="s">
+      <c r="AQ5" s="297"/>
+      <c r="AR5" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="AS5" s="327"/>
-      <c r="AT5" s="314" t="s">
+      <c r="AS5" s="301"/>
+      <c r="AT5" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="AU5" s="315"/>
-      <c r="AV5" s="318" t="s">
+      <c r="AU5" s="305"/>
+      <c r="AV5" s="308" t="s">
         <v>30</v>
       </c>
-      <c r="AW5" s="319"/>
-      <c r="AX5" s="322" t="s">
+      <c r="AW5" s="309"/>
+      <c r="AX5" s="296" t="s">
         <v>38</v>
       </c>
-      <c r="AY5" s="323"/>
-      <c r="AZ5" s="326" t="s">
+      <c r="AY5" s="297"/>
+      <c r="AZ5" s="300" t="s">
         <v>39</v>
       </c>
-      <c r="BA5" s="327"/>
-      <c r="BB5" s="339" t="s">
+      <c r="BA5" s="301"/>
+      <c r="BB5" s="332" t="s">
         <v>40</v>
       </c>
-      <c r="BC5" s="340"/>
-      <c r="BD5" s="318" t="s">
+      <c r="BC5" s="333"/>
+      <c r="BD5" s="308" t="s">
         <v>14</v>
       </c>
-      <c r="BE5" s="319"/>
-      <c r="BF5" s="322"/>
-      <c r="BG5" s="323"/>
-      <c r="BH5" s="326"/>
-      <c r="BI5" s="327"/>
-      <c r="BJ5" s="314"/>
-      <c r="BK5" s="315"/>
-      <c r="BL5" s="318"/>
-      <c r="BM5" s="319"/>
+      <c r="BE5" s="309"/>
+      <c r="BF5" s="296"/>
+      <c r="BG5" s="297"/>
+      <c r="BH5" s="300"/>
+      <c r="BI5" s="301"/>
+      <c r="BJ5" s="304"/>
+      <c r="BK5" s="305"/>
+      <c r="BL5" s="308"/>
+      <c r="BM5" s="309"/>
       <c r="BP5" s="6">
         <v>1</v>
       </c>
@@ -43091,68 +43091,68 @@
       <c r="BR5" s="2"/>
     </row>
     <row r="6" spans="2:70" ht="33" customHeight="1">
-      <c r="B6" s="330"/>
-      <c r="C6" s="330"/>
-      <c r="D6" s="324"/>
-      <c r="E6" s="325"/>
-      <c r="F6" s="328"/>
-      <c r="G6" s="329"/>
-      <c r="H6" s="316"/>
-      <c r="I6" s="317"/>
-      <c r="J6" s="320"/>
-      <c r="K6" s="321"/>
-      <c r="L6" s="324"/>
-      <c r="M6" s="325"/>
-      <c r="N6" s="328"/>
-      <c r="O6" s="329"/>
-      <c r="P6" s="316"/>
-      <c r="Q6" s="317"/>
-      <c r="R6" s="320"/>
-      <c r="S6" s="321"/>
-      <c r="T6" s="324"/>
-      <c r="U6" s="325"/>
-      <c r="V6" s="328"/>
-      <c r="W6" s="329"/>
-      <c r="X6" s="316"/>
-      <c r="Y6" s="317"/>
-      <c r="Z6" s="320"/>
-      <c r="AA6" s="321"/>
-      <c r="AB6" s="324"/>
-      <c r="AC6" s="325"/>
-      <c r="AD6" s="328"/>
-      <c r="AE6" s="329"/>
-      <c r="AF6" s="316"/>
-      <c r="AG6" s="317"/>
-      <c r="AH6" s="320"/>
-      <c r="AI6" s="321"/>
-      <c r="AJ6" s="324"/>
-      <c r="AK6" s="325"/>
-      <c r="AL6" s="328"/>
-      <c r="AM6" s="329"/>
-      <c r="AP6" s="324"/>
-      <c r="AQ6" s="325"/>
-      <c r="AR6" s="328"/>
-      <c r="AS6" s="329"/>
-      <c r="AT6" s="316"/>
-      <c r="AU6" s="317"/>
-      <c r="AV6" s="320"/>
-      <c r="AW6" s="321"/>
-      <c r="AX6" s="324"/>
-      <c r="AY6" s="325"/>
-      <c r="AZ6" s="328"/>
-      <c r="BA6" s="329"/>
-      <c r="BB6" s="341"/>
-      <c r="BC6" s="342"/>
-      <c r="BD6" s="320"/>
-      <c r="BE6" s="321"/>
-      <c r="BF6" s="324"/>
-      <c r="BG6" s="325"/>
-      <c r="BH6" s="328"/>
-      <c r="BI6" s="329"/>
-      <c r="BJ6" s="316"/>
-      <c r="BK6" s="317"/>
-      <c r="BL6" s="320"/>
-      <c r="BM6" s="321"/>
+      <c r="B6" s="295"/>
+      <c r="C6" s="295"/>
+      <c r="D6" s="298"/>
+      <c r="E6" s="299"/>
+      <c r="F6" s="302"/>
+      <c r="G6" s="303"/>
+      <c r="H6" s="306"/>
+      <c r="I6" s="307"/>
+      <c r="J6" s="310"/>
+      <c r="K6" s="311"/>
+      <c r="L6" s="298"/>
+      <c r="M6" s="299"/>
+      <c r="N6" s="302"/>
+      <c r="O6" s="303"/>
+      <c r="P6" s="306"/>
+      <c r="Q6" s="307"/>
+      <c r="R6" s="310"/>
+      <c r="S6" s="311"/>
+      <c r="T6" s="298"/>
+      <c r="U6" s="299"/>
+      <c r="V6" s="302"/>
+      <c r="W6" s="303"/>
+      <c r="X6" s="306"/>
+      <c r="Y6" s="307"/>
+      <c r="Z6" s="310"/>
+      <c r="AA6" s="311"/>
+      <c r="AB6" s="298"/>
+      <c r="AC6" s="299"/>
+      <c r="AD6" s="302"/>
+      <c r="AE6" s="303"/>
+      <c r="AF6" s="306"/>
+      <c r="AG6" s="307"/>
+      <c r="AH6" s="310"/>
+      <c r="AI6" s="311"/>
+      <c r="AJ6" s="298"/>
+      <c r="AK6" s="299"/>
+      <c r="AL6" s="302"/>
+      <c r="AM6" s="303"/>
+      <c r="AP6" s="298"/>
+      <c r="AQ6" s="299"/>
+      <c r="AR6" s="302"/>
+      <c r="AS6" s="303"/>
+      <c r="AT6" s="306"/>
+      <c r="AU6" s="307"/>
+      <c r="AV6" s="310"/>
+      <c r="AW6" s="311"/>
+      <c r="AX6" s="298"/>
+      <c r="AY6" s="299"/>
+      <c r="AZ6" s="302"/>
+      <c r="BA6" s="303"/>
+      <c r="BB6" s="334"/>
+      <c r="BC6" s="335"/>
+      <c r="BD6" s="310"/>
+      <c r="BE6" s="311"/>
+      <c r="BF6" s="298"/>
+      <c r="BG6" s="299"/>
+      <c r="BH6" s="302"/>
+      <c r="BI6" s="303"/>
+      <c r="BJ6" s="306"/>
+      <c r="BK6" s="307"/>
+      <c r="BL6" s="310"/>
+      <c r="BM6" s="311"/>
       <c r="BP6" s="6">
         <v>2</v>
       </c>
@@ -43162,96 +43162,96 @@
       <c r="BR6" s="2"/>
     </row>
     <row r="7" spans="2:70" ht="33" customHeight="1">
-      <c r="B7" s="330"/>
-      <c r="C7" s="330"/>
-      <c r="D7" s="302"/>
-      <c r="E7" s="303"/>
-      <c r="F7" s="306"/>
-      <c r="G7" s="307"/>
-      <c r="H7" s="294" t="s">
+      <c r="B7" s="295"/>
+      <c r="C7" s="295"/>
+      <c r="D7" s="312"/>
+      <c r="E7" s="313"/>
+      <c r="F7" s="316"/>
+      <c r="G7" s="317"/>
+      <c r="H7" s="320" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="295"/>
-      <c r="J7" s="298" t="s">
+      <c r="I7" s="321"/>
+      <c r="J7" s="324" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="299"/>
-      <c r="L7" s="302"/>
-      <c r="M7" s="303"/>
-      <c r="N7" s="306"/>
-      <c r="O7" s="307"/>
-      <c r="P7" s="294"/>
-      <c r="Q7" s="295"/>
-      <c r="R7" s="298"/>
-      <c r="S7" s="299"/>
-      <c r="T7" s="302"/>
-      <c r="U7" s="303"/>
-      <c r="V7" s="306"/>
-      <c r="W7" s="307"/>
-      <c r="X7" s="294" t="s">
+      <c r="K7" s="325"/>
+      <c r="L7" s="312"/>
+      <c r="M7" s="313"/>
+      <c r="N7" s="316"/>
+      <c r="O7" s="317"/>
+      <c r="P7" s="320"/>
+      <c r="Q7" s="321"/>
+      <c r="R7" s="324"/>
+      <c r="S7" s="325"/>
+      <c r="T7" s="312"/>
+      <c r="U7" s="313"/>
+      <c r="V7" s="316"/>
+      <c r="W7" s="317"/>
+      <c r="X7" s="320" t="s">
         <v>22</v>
       </c>
-      <c r="Y7" s="295"/>
-      <c r="Z7" s="298" t="s">
+      <c r="Y7" s="321"/>
+      <c r="Z7" s="324" t="s">
         <v>23</v>
       </c>
-      <c r="AA7" s="299"/>
-      <c r="AB7" s="302"/>
-      <c r="AC7" s="303"/>
-      <c r="AD7" s="306"/>
-      <c r="AE7" s="307"/>
-      <c r="AF7" s="294" t="s">
+      <c r="AA7" s="325"/>
+      <c r="AB7" s="312"/>
+      <c r="AC7" s="313"/>
+      <c r="AD7" s="316"/>
+      <c r="AE7" s="317"/>
+      <c r="AF7" s="320" t="s">
         <v>24</v>
       </c>
-      <c r="AG7" s="295"/>
-      <c r="AH7" s="298" t="s">
+      <c r="AG7" s="321"/>
+      <c r="AH7" s="324" t="s">
         <v>25</v>
       </c>
-      <c r="AI7" s="299"/>
-      <c r="AJ7" s="310"/>
-      <c r="AK7" s="311"/>
-      <c r="AL7" s="306"/>
-      <c r="AM7" s="307"/>
-      <c r="AP7" s="302" t="s">
+      <c r="AI7" s="325"/>
+      <c r="AJ7" s="328"/>
+      <c r="AK7" s="329"/>
+      <c r="AL7" s="316"/>
+      <c r="AM7" s="317"/>
+      <c r="AP7" s="312" t="s">
         <v>19</v>
       </c>
-      <c r="AQ7" s="303"/>
-      <c r="AR7" s="306" t="s">
+      <c r="AQ7" s="313"/>
+      <c r="AR7" s="316" t="s">
         <v>30</v>
       </c>
-      <c r="AS7" s="307"/>
-      <c r="AT7" s="294" t="s">
+      <c r="AS7" s="317"/>
+      <c r="AT7" s="320" t="s">
         <v>41</v>
       </c>
-      <c r="AU7" s="295"/>
-      <c r="AV7" s="298" t="s">
+      <c r="AU7" s="321"/>
+      <c r="AV7" s="324" t="s">
         <v>42</v>
       </c>
-      <c r="AW7" s="299"/>
-      <c r="AX7" s="302" t="s">
+      <c r="AW7" s="325"/>
+      <c r="AX7" s="312" t="s">
         <v>50</v>
       </c>
-      <c r="AY7" s="303"/>
-      <c r="AZ7" s="306" t="s">
+      <c r="AY7" s="313"/>
+      <c r="AZ7" s="316" t="s">
         <v>29</v>
       </c>
-      <c r="BA7" s="307"/>
-      <c r="BB7" s="294" t="s">
+      <c r="BA7" s="317"/>
+      <c r="BB7" s="320" t="s">
         <v>20</v>
       </c>
-      <c r="BC7" s="295"/>
-      <c r="BD7" s="298" t="s">
+      <c r="BC7" s="321"/>
+      <c r="BD7" s="324" t="s">
         <v>21</v>
       </c>
-      <c r="BE7" s="299"/>
-      <c r="BF7" s="302"/>
-      <c r="BG7" s="303"/>
-      <c r="BH7" s="306"/>
-      <c r="BI7" s="307"/>
-      <c r="BJ7" s="294"/>
-      <c r="BK7" s="295"/>
-      <c r="BL7" s="298"/>
-      <c r="BM7" s="299"/>
+      <c r="BE7" s="325"/>
+      <c r="BF7" s="312"/>
+      <c r="BG7" s="313"/>
+      <c r="BH7" s="316"/>
+      <c r="BI7" s="317"/>
+      <c r="BJ7" s="320"/>
+      <c r="BK7" s="321"/>
+      <c r="BL7" s="324"/>
+      <c r="BM7" s="325"/>
       <c r="BP7" s="6">
         <v>3</v>
       </c>
@@ -43261,68 +43261,68 @@
       <c r="BR7" s="2"/>
     </row>
     <row r="8" spans="2:70" ht="33" customHeight="1">
-      <c r="B8" s="330"/>
-      <c r="C8" s="330"/>
-      <c r="D8" s="304"/>
-      <c r="E8" s="305"/>
-      <c r="F8" s="308"/>
-      <c r="G8" s="309"/>
-      <c r="H8" s="296"/>
-      <c r="I8" s="297"/>
-      <c r="J8" s="300"/>
-      <c r="K8" s="301"/>
-      <c r="L8" s="304"/>
-      <c r="M8" s="305"/>
-      <c r="N8" s="308"/>
-      <c r="O8" s="309"/>
-      <c r="P8" s="296"/>
-      <c r="Q8" s="297"/>
-      <c r="R8" s="300"/>
-      <c r="S8" s="301"/>
-      <c r="T8" s="304"/>
-      <c r="U8" s="305"/>
-      <c r="V8" s="308"/>
-      <c r="W8" s="309"/>
-      <c r="X8" s="296"/>
-      <c r="Y8" s="297"/>
-      <c r="Z8" s="300"/>
-      <c r="AA8" s="301"/>
-      <c r="AB8" s="304"/>
-      <c r="AC8" s="305"/>
-      <c r="AD8" s="308"/>
-      <c r="AE8" s="309"/>
-      <c r="AF8" s="296"/>
-      <c r="AG8" s="297"/>
-      <c r="AH8" s="300"/>
-      <c r="AI8" s="301"/>
-      <c r="AJ8" s="312"/>
-      <c r="AK8" s="313"/>
-      <c r="AL8" s="308"/>
-      <c r="AM8" s="309"/>
-      <c r="AP8" s="304"/>
-      <c r="AQ8" s="305"/>
-      <c r="AR8" s="308"/>
-      <c r="AS8" s="309"/>
-      <c r="AT8" s="296"/>
-      <c r="AU8" s="297"/>
-      <c r="AV8" s="300"/>
-      <c r="AW8" s="301"/>
-      <c r="AX8" s="304"/>
-      <c r="AY8" s="305"/>
-      <c r="AZ8" s="308"/>
-      <c r="BA8" s="309"/>
-      <c r="BB8" s="296"/>
-      <c r="BC8" s="297"/>
-      <c r="BD8" s="300"/>
-      <c r="BE8" s="301"/>
-      <c r="BF8" s="304"/>
-      <c r="BG8" s="305"/>
-      <c r="BH8" s="308"/>
-      <c r="BI8" s="309"/>
-      <c r="BJ8" s="296"/>
-      <c r="BK8" s="297"/>
-      <c r="BL8" s="300"/>
-      <c r="BM8" s="301"/>
+      <c r="B8" s="295"/>
+      <c r="C8" s="295"/>
+      <c r="D8" s="314"/>
+      <c r="E8" s="315"/>
+      <c r="F8" s="318"/>
+      <c r="G8" s="319"/>
+      <c r="H8" s="322"/>
+      <c r="I8" s="323"/>
+      <c r="J8" s="326"/>
+      <c r="K8" s="327"/>
+      <c r="L8" s="314"/>
+      <c r="M8" s="315"/>
+      <c r="N8" s="318"/>
+      <c r="O8" s="319"/>
+      <c r="P8" s="322"/>
+      <c r="Q8" s="323"/>
+      <c r="R8" s="326"/>
+      <c r="S8" s="327"/>
+      <c r="T8" s="314"/>
+      <c r="U8" s="315"/>
+      <c r="V8" s="318"/>
+      <c r="W8" s="319"/>
+      <c r="X8" s="322"/>
+      <c r="Y8" s="323"/>
+      <c r="Z8" s="326"/>
+      <c r="AA8" s="327"/>
+      <c r="AB8" s="314"/>
+      <c r="AC8" s="315"/>
+      <c r="AD8" s="318"/>
+      <c r="AE8" s="319"/>
+      <c r="AF8" s="322"/>
+      <c r="AG8" s="323"/>
+      <c r="AH8" s="326"/>
+      <c r="AI8" s="327"/>
+      <c r="AJ8" s="330"/>
+      <c r="AK8" s="331"/>
+      <c r="AL8" s="318"/>
+      <c r="AM8" s="319"/>
+      <c r="AP8" s="314"/>
+      <c r="AQ8" s="315"/>
+      <c r="AR8" s="318"/>
+      <c r="AS8" s="319"/>
+      <c r="AT8" s="322"/>
+      <c r="AU8" s="323"/>
+      <c r="AV8" s="326"/>
+      <c r="AW8" s="327"/>
+      <c r="AX8" s="314"/>
+      <c r="AY8" s="315"/>
+      <c r="AZ8" s="318"/>
+      <c r="BA8" s="319"/>
+      <c r="BB8" s="322"/>
+      <c r="BC8" s="323"/>
+      <c r="BD8" s="326"/>
+      <c r="BE8" s="327"/>
+      <c r="BF8" s="314"/>
+      <c r="BG8" s="315"/>
+      <c r="BH8" s="318"/>
+      <c r="BI8" s="319"/>
+      <c r="BJ8" s="322"/>
+      <c r="BK8" s="323"/>
+      <c r="BL8" s="326"/>
+      <c r="BM8" s="327"/>
       <c r="BP8" s="6">
         <v>4</v>
       </c>
@@ -43332,112 +43332,112 @@
       <c r="BR8" s="2"/>
     </row>
     <row r="9" spans="2:70" ht="33" customHeight="1">
-      <c r="B9" s="330" t="s">
+      <c r="B9" s="295" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="343" t="s">
+      <c r="C9" s="344" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="322" t="s">
+      <c r="D9" s="296" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="323"/>
-      <c r="F9" s="326" t="s">
+      <c r="E9" s="297"/>
+      <c r="F9" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="327"/>
-      <c r="H9" s="314" t="s">
+      <c r="G9" s="301"/>
+      <c r="H9" s="304" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="315"/>
-      <c r="J9" s="318" t="s">
+      <c r="I9" s="305"/>
+      <c r="J9" s="308" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="319"/>
-      <c r="L9" s="322"/>
-      <c r="M9" s="323"/>
-      <c r="N9" s="326"/>
-      <c r="O9" s="327"/>
-      <c r="P9" s="314"/>
-      <c r="Q9" s="315"/>
-      <c r="R9" s="318"/>
-      <c r="S9" s="319"/>
-      <c r="T9" s="322" t="s">
+      <c r="K9" s="309"/>
+      <c r="L9" s="296"/>
+      <c r="M9" s="297"/>
+      <c r="N9" s="300"/>
+      <c r="O9" s="301"/>
+      <c r="P9" s="304"/>
+      <c r="Q9" s="305"/>
+      <c r="R9" s="308"/>
+      <c r="S9" s="309"/>
+      <c r="T9" s="296" t="s">
         <v>31</v>
       </c>
-      <c r="U9" s="323"/>
-      <c r="V9" s="326" t="s">
+      <c r="U9" s="297"/>
+      <c r="V9" s="300" t="s">
         <v>32</v>
       </c>
-      <c r="W9" s="327"/>
-      <c r="X9" s="314"/>
-      <c r="Y9" s="315"/>
-      <c r="Z9" s="318"/>
-      <c r="AA9" s="319"/>
-      <c r="AB9" s="322" t="s">
+      <c r="W9" s="301"/>
+      <c r="X9" s="304"/>
+      <c r="Y9" s="305"/>
+      <c r="Z9" s="308"/>
+      <c r="AA9" s="309"/>
+      <c r="AB9" s="296" t="s">
         <v>33</v>
       </c>
-      <c r="AC9" s="323"/>
-      <c r="AD9" s="326" t="s">
+      <c r="AC9" s="297"/>
+      <c r="AD9" s="300" t="s">
         <v>34</v>
       </c>
-      <c r="AE9" s="327"/>
-      <c r="AF9" s="314" t="s">
+      <c r="AE9" s="301"/>
+      <c r="AF9" s="304" t="s">
         <v>17</v>
       </c>
-      <c r="AG9" s="315"/>
-      <c r="AH9" s="318" t="s">
+      <c r="AG9" s="305"/>
+      <c r="AH9" s="308" t="s">
         <v>35</v>
       </c>
-      <c r="AI9" s="319"/>
-      <c r="AJ9" s="322" t="s">
+      <c r="AI9" s="309"/>
+      <c r="AJ9" s="296" t="s">
         <v>36</v>
       </c>
-      <c r="AK9" s="323"/>
-      <c r="AL9" s="335" t="s">
+      <c r="AK9" s="297"/>
+      <c r="AL9" s="336" t="s">
         <v>37</v>
       </c>
-      <c r="AM9" s="336"/>
-      <c r="AP9" s="322" t="s">
+      <c r="AM9" s="337"/>
+      <c r="AP9" s="296" t="s">
         <v>31</v>
       </c>
-      <c r="AQ9" s="323"/>
-      <c r="AR9" s="326" t="s">
+      <c r="AQ9" s="297"/>
+      <c r="AR9" s="300" t="s">
         <v>32</v>
       </c>
-      <c r="AS9" s="327"/>
-      <c r="AT9" s="314"/>
-      <c r="AU9" s="315"/>
-      <c r="AV9" s="318"/>
-      <c r="AW9" s="319"/>
-      <c r="AX9" s="322" t="s">
+      <c r="AS9" s="301"/>
+      <c r="AT9" s="304"/>
+      <c r="AU9" s="305"/>
+      <c r="AV9" s="308"/>
+      <c r="AW9" s="309"/>
+      <c r="AX9" s="296" t="s">
         <v>52</v>
       </c>
-      <c r="AY9" s="323"/>
-      <c r="AZ9" s="326" t="s">
+      <c r="AY9" s="297"/>
+      <c r="AZ9" s="300" t="s">
         <v>53</v>
       </c>
-      <c r="BA9" s="327"/>
-      <c r="BB9" s="339" t="s">
+      <c r="BA9" s="301"/>
+      <c r="BB9" s="332" t="s">
         <v>56</v>
       </c>
-      <c r="BC9" s="340"/>
-      <c r="BD9" s="318" t="s">
+      <c r="BC9" s="333"/>
+      <c r="BD9" s="308" t="s">
         <v>16</v>
       </c>
-      <c r="BE9" s="319"/>
-      <c r="BF9" s="322" t="s">
+      <c r="BE9" s="309"/>
+      <c r="BF9" s="296" t="s">
         <v>15</v>
       </c>
-      <c r="BG9" s="323"/>
-      <c r="BH9" s="326" t="s">
+      <c r="BG9" s="297"/>
+      <c r="BH9" s="300" t="s">
         <v>57</v>
       </c>
-      <c r="BI9" s="327"/>
-      <c r="BJ9" s="314"/>
-      <c r="BK9" s="315"/>
-      <c r="BL9" s="318"/>
-      <c r="BM9" s="319"/>
+      <c r="BI9" s="301"/>
+      <c r="BJ9" s="304"/>
+      <c r="BK9" s="305"/>
+      <c r="BL9" s="308"/>
+      <c r="BM9" s="309"/>
       <c r="BP9" s="6">
         <v>5</v>
       </c>
@@ -43447,68 +43447,68 @@
       <c r="BR9" s="2"/>
     </row>
     <row r="10" spans="2:70" ht="33" customHeight="1">
-      <c r="B10" s="330"/>
-      <c r="C10" s="343"/>
-      <c r="D10" s="324"/>
-      <c r="E10" s="325"/>
-      <c r="F10" s="328"/>
-      <c r="G10" s="329"/>
-      <c r="H10" s="316"/>
-      <c r="I10" s="317"/>
-      <c r="J10" s="320"/>
-      <c r="K10" s="321"/>
-      <c r="L10" s="324"/>
-      <c r="M10" s="325"/>
-      <c r="N10" s="328"/>
-      <c r="O10" s="329"/>
-      <c r="P10" s="316"/>
-      <c r="Q10" s="317"/>
-      <c r="R10" s="320"/>
-      <c r="S10" s="321"/>
-      <c r="T10" s="324"/>
-      <c r="U10" s="325"/>
-      <c r="V10" s="328"/>
-      <c r="W10" s="329"/>
-      <c r="X10" s="316"/>
-      <c r="Y10" s="317"/>
-      <c r="Z10" s="320"/>
-      <c r="AA10" s="321"/>
-      <c r="AB10" s="324"/>
-      <c r="AC10" s="325"/>
-      <c r="AD10" s="328"/>
-      <c r="AE10" s="329"/>
-      <c r="AF10" s="316"/>
-      <c r="AG10" s="317"/>
-      <c r="AH10" s="320"/>
-      <c r="AI10" s="321"/>
-      <c r="AJ10" s="324"/>
-      <c r="AK10" s="325"/>
-      <c r="AL10" s="337"/>
-      <c r="AM10" s="338"/>
-      <c r="AP10" s="324"/>
-      <c r="AQ10" s="325"/>
-      <c r="AR10" s="328"/>
-      <c r="AS10" s="329"/>
-      <c r="AT10" s="316"/>
-      <c r="AU10" s="317"/>
-      <c r="AV10" s="320"/>
-      <c r="AW10" s="321"/>
-      <c r="AX10" s="324"/>
-      <c r="AY10" s="325"/>
-      <c r="AZ10" s="328"/>
-      <c r="BA10" s="329"/>
-      <c r="BB10" s="341"/>
-      <c r="BC10" s="342"/>
-      <c r="BD10" s="320"/>
-      <c r="BE10" s="321"/>
-      <c r="BF10" s="324"/>
-      <c r="BG10" s="325"/>
-      <c r="BH10" s="328"/>
-      <c r="BI10" s="329"/>
-      <c r="BJ10" s="316"/>
-      <c r="BK10" s="317"/>
-      <c r="BL10" s="320"/>
-      <c r="BM10" s="321"/>
+      <c r="B10" s="295"/>
+      <c r="C10" s="344"/>
+      <c r="D10" s="298"/>
+      <c r="E10" s="299"/>
+      <c r="F10" s="302"/>
+      <c r="G10" s="303"/>
+      <c r="H10" s="306"/>
+      <c r="I10" s="307"/>
+      <c r="J10" s="310"/>
+      <c r="K10" s="311"/>
+      <c r="L10" s="298"/>
+      <c r="M10" s="299"/>
+      <c r="N10" s="302"/>
+      <c r="O10" s="303"/>
+      <c r="P10" s="306"/>
+      <c r="Q10" s="307"/>
+      <c r="R10" s="310"/>
+      <c r="S10" s="311"/>
+      <c r="T10" s="298"/>
+      <c r="U10" s="299"/>
+      <c r="V10" s="302"/>
+      <c r="W10" s="303"/>
+      <c r="X10" s="306"/>
+      <c r="Y10" s="307"/>
+      <c r="Z10" s="310"/>
+      <c r="AA10" s="311"/>
+      <c r="AB10" s="298"/>
+      <c r="AC10" s="299"/>
+      <c r="AD10" s="302"/>
+      <c r="AE10" s="303"/>
+      <c r="AF10" s="306"/>
+      <c r="AG10" s="307"/>
+      <c r="AH10" s="310"/>
+      <c r="AI10" s="311"/>
+      <c r="AJ10" s="298"/>
+      <c r="AK10" s="299"/>
+      <c r="AL10" s="338"/>
+      <c r="AM10" s="339"/>
+      <c r="AP10" s="298"/>
+      <c r="AQ10" s="299"/>
+      <c r="AR10" s="302"/>
+      <c r="AS10" s="303"/>
+      <c r="AT10" s="306"/>
+      <c r="AU10" s="307"/>
+      <c r="AV10" s="310"/>
+      <c r="AW10" s="311"/>
+      <c r="AX10" s="298"/>
+      <c r="AY10" s="299"/>
+      <c r="AZ10" s="302"/>
+      <c r="BA10" s="303"/>
+      <c r="BB10" s="334"/>
+      <c r="BC10" s="335"/>
+      <c r="BD10" s="310"/>
+      <c r="BE10" s="311"/>
+      <c r="BF10" s="298"/>
+      <c r="BG10" s="299"/>
+      <c r="BH10" s="302"/>
+      <c r="BI10" s="303"/>
+      <c r="BJ10" s="306"/>
+      <c r="BK10" s="307"/>
+      <c r="BL10" s="310"/>
+      <c r="BM10" s="311"/>
       <c r="BP10" s="6">
         <v>6</v>
       </c>
@@ -43518,108 +43518,108 @@
       <c r="BR10" s="2"/>
     </row>
     <row r="11" spans="2:70" ht="33" customHeight="1">
-      <c r="B11" s="330"/>
-      <c r="C11" s="343"/>
-      <c r="D11" s="302" t="s">
+      <c r="B11" s="295"/>
+      <c r="C11" s="344"/>
+      <c r="D11" s="312" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="303"/>
-      <c r="F11" s="306" t="s">
+      <c r="E11" s="313"/>
+      <c r="F11" s="316" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="307"/>
-      <c r="H11" s="294" t="s">
+      <c r="G11" s="317"/>
+      <c r="H11" s="320" t="s">
         <v>41</v>
       </c>
-      <c r="I11" s="295"/>
-      <c r="J11" s="298" t="s">
+      <c r="I11" s="321"/>
+      <c r="J11" s="324" t="s">
         <v>42</v>
       </c>
-      <c r="K11" s="299"/>
-      <c r="L11" s="302"/>
-      <c r="M11" s="303"/>
-      <c r="N11" s="306"/>
-      <c r="O11" s="307"/>
-      <c r="P11" s="294"/>
-      <c r="Q11" s="295"/>
-      <c r="R11" s="298"/>
-      <c r="S11" s="299"/>
-      <c r="T11" s="302" t="s">
+      <c r="K11" s="325"/>
+      <c r="L11" s="312"/>
+      <c r="M11" s="313"/>
+      <c r="N11" s="316"/>
+      <c r="O11" s="317"/>
+      <c r="P11" s="320"/>
+      <c r="Q11" s="321"/>
+      <c r="R11" s="324"/>
+      <c r="S11" s="325"/>
+      <c r="T11" s="312" t="s">
         <v>43</v>
       </c>
-      <c r="U11" s="303"/>
-      <c r="V11" s="306" t="s">
+      <c r="U11" s="313"/>
+      <c r="V11" s="316" t="s">
         <v>44</v>
       </c>
-      <c r="W11" s="307"/>
-      <c r="X11" s="294"/>
-      <c r="Y11" s="295"/>
-      <c r="Z11" s="298"/>
-      <c r="AA11" s="299"/>
-      <c r="AB11" s="302" t="s">
+      <c r="W11" s="317"/>
+      <c r="X11" s="320"/>
+      <c r="Y11" s="321"/>
+      <c r="Z11" s="324"/>
+      <c r="AA11" s="325"/>
+      <c r="AB11" s="312" t="s">
         <v>45</v>
       </c>
-      <c r="AC11" s="303"/>
-      <c r="AD11" s="306" t="s">
+      <c r="AC11" s="313"/>
+      <c r="AD11" s="316" t="s">
         <v>46</v>
       </c>
-      <c r="AE11" s="307"/>
-      <c r="AF11" s="294" t="s">
+      <c r="AE11" s="317"/>
+      <c r="AF11" s="320" t="s">
         <v>47</v>
       </c>
-      <c r="AG11" s="295"/>
-      <c r="AH11" s="298" t="s">
+      <c r="AG11" s="321"/>
+      <c r="AH11" s="324" t="s">
         <v>48</v>
       </c>
-      <c r="AI11" s="299"/>
-      <c r="AJ11" s="302" t="s">
+      <c r="AI11" s="325"/>
+      <c r="AJ11" s="312" t="s">
         <v>49</v>
       </c>
-      <c r="AK11" s="303"/>
-      <c r="AL11" s="331" t="s">
+      <c r="AK11" s="313"/>
+      <c r="AL11" s="340" t="s">
         <v>37</v>
       </c>
-      <c r="AM11" s="332"/>
-      <c r="AP11" s="302" t="s">
+      <c r="AM11" s="341"/>
+      <c r="AP11" s="312" t="s">
         <v>43</v>
       </c>
-      <c r="AQ11" s="303"/>
-      <c r="AR11" s="306" t="s">
+      <c r="AQ11" s="313"/>
+      <c r="AR11" s="316" t="s">
         <v>44</v>
       </c>
-      <c r="AS11" s="307"/>
-      <c r="AT11" s="294"/>
-      <c r="AU11" s="295"/>
-      <c r="AV11" s="298"/>
-      <c r="AW11" s="299"/>
-      <c r="AX11" s="302" t="s">
+      <c r="AS11" s="317"/>
+      <c r="AT11" s="320"/>
+      <c r="AU11" s="321"/>
+      <c r="AV11" s="324"/>
+      <c r="AW11" s="325"/>
+      <c r="AX11" s="312" t="s">
         <v>58</v>
       </c>
-      <c r="AY11" s="303"/>
-      <c r="AZ11" s="306" t="s">
+      <c r="AY11" s="313"/>
+      <c r="AZ11" s="316" t="s">
         <v>32</v>
       </c>
-      <c r="BA11" s="307"/>
-      <c r="BB11" s="294" t="s">
+      <c r="BA11" s="317"/>
+      <c r="BB11" s="320" t="s">
         <v>22</v>
       </c>
-      <c r="BC11" s="295"/>
-      <c r="BD11" s="298" t="s">
+      <c r="BC11" s="321"/>
+      <c r="BD11" s="324" t="s">
         <v>23</v>
       </c>
-      <c r="BE11" s="299"/>
-      <c r="BF11" s="302" t="s">
+      <c r="BE11" s="325"/>
+      <c r="BF11" s="312" t="s">
         <v>60</v>
       </c>
-      <c r="BG11" s="303"/>
-      <c r="BH11" s="306" t="s">
+      <c r="BG11" s="313"/>
+      <c r="BH11" s="316" t="s">
         <v>57</v>
       </c>
-      <c r="BI11" s="307"/>
-      <c r="BJ11" s="294"/>
-      <c r="BK11" s="295"/>
-      <c r="BL11" s="298"/>
-      <c r="BM11" s="299"/>
+      <c r="BI11" s="317"/>
+      <c r="BJ11" s="320"/>
+      <c r="BK11" s="321"/>
+      <c r="BL11" s="324"/>
+      <c r="BM11" s="325"/>
       <c r="BP11" s="6">
         <v>7</v>
       </c>
@@ -43629,68 +43629,68 @@
       <c r="BR11" s="2"/>
     </row>
     <row r="12" spans="2:70" ht="33" customHeight="1">
-      <c r="B12" s="330"/>
-      <c r="C12" s="343"/>
-      <c r="D12" s="304"/>
-      <c r="E12" s="305"/>
-      <c r="F12" s="308"/>
-      <c r="G12" s="309"/>
-      <c r="H12" s="296"/>
-      <c r="I12" s="297"/>
-      <c r="J12" s="300"/>
-      <c r="K12" s="301"/>
-      <c r="L12" s="304"/>
-      <c r="M12" s="305"/>
-      <c r="N12" s="308"/>
-      <c r="O12" s="309"/>
-      <c r="P12" s="296"/>
-      <c r="Q12" s="297"/>
-      <c r="R12" s="300"/>
-      <c r="S12" s="301"/>
-      <c r="T12" s="304"/>
-      <c r="U12" s="305"/>
-      <c r="V12" s="308"/>
-      <c r="W12" s="309"/>
-      <c r="X12" s="296"/>
-      <c r="Y12" s="297"/>
-      <c r="Z12" s="300"/>
-      <c r="AA12" s="301"/>
-      <c r="AB12" s="304"/>
-      <c r="AC12" s="305"/>
-      <c r="AD12" s="308"/>
-      <c r="AE12" s="309"/>
-      <c r="AF12" s="296"/>
-      <c r="AG12" s="297"/>
-      <c r="AH12" s="300"/>
-      <c r="AI12" s="301"/>
-      <c r="AJ12" s="304"/>
-      <c r="AK12" s="305"/>
-      <c r="AL12" s="333"/>
-      <c r="AM12" s="334"/>
-      <c r="AP12" s="304"/>
-      <c r="AQ12" s="305"/>
-      <c r="AR12" s="308"/>
-      <c r="AS12" s="309"/>
-      <c r="AT12" s="296"/>
-      <c r="AU12" s="297"/>
-      <c r="AV12" s="300"/>
-      <c r="AW12" s="301"/>
-      <c r="AX12" s="304"/>
-      <c r="AY12" s="305"/>
-      <c r="AZ12" s="308"/>
-      <c r="BA12" s="309"/>
-      <c r="BB12" s="296"/>
-      <c r="BC12" s="297"/>
-      <c r="BD12" s="300"/>
-      <c r="BE12" s="301"/>
-      <c r="BF12" s="304"/>
-      <c r="BG12" s="305"/>
-      <c r="BH12" s="308"/>
-      <c r="BI12" s="309"/>
-      <c r="BJ12" s="296"/>
-      <c r="BK12" s="297"/>
-      <c r="BL12" s="300"/>
-      <c r="BM12" s="301"/>
+      <c r="B12" s="295"/>
+      <c r="C12" s="344"/>
+      <c r="D12" s="314"/>
+      <c r="E12" s="315"/>
+      <c r="F12" s="318"/>
+      <c r="G12" s="319"/>
+      <c r="H12" s="322"/>
+      <c r="I12" s="323"/>
+      <c r="J12" s="326"/>
+      <c r="K12" s="327"/>
+      <c r="L12" s="314"/>
+      <c r="M12" s="315"/>
+      <c r="N12" s="318"/>
+      <c r="O12" s="319"/>
+      <c r="P12" s="322"/>
+      <c r="Q12" s="323"/>
+      <c r="R12" s="326"/>
+      <c r="S12" s="327"/>
+      <c r="T12" s="314"/>
+      <c r="U12" s="315"/>
+      <c r="V12" s="318"/>
+      <c r="W12" s="319"/>
+      <c r="X12" s="322"/>
+      <c r="Y12" s="323"/>
+      <c r="Z12" s="326"/>
+      <c r="AA12" s="327"/>
+      <c r="AB12" s="314"/>
+      <c r="AC12" s="315"/>
+      <c r="AD12" s="318"/>
+      <c r="AE12" s="319"/>
+      <c r="AF12" s="322"/>
+      <c r="AG12" s="323"/>
+      <c r="AH12" s="326"/>
+      <c r="AI12" s="327"/>
+      <c r="AJ12" s="314"/>
+      <c r="AK12" s="315"/>
+      <c r="AL12" s="342"/>
+      <c r="AM12" s="343"/>
+      <c r="AP12" s="314"/>
+      <c r="AQ12" s="315"/>
+      <c r="AR12" s="318"/>
+      <c r="AS12" s="319"/>
+      <c r="AT12" s="322"/>
+      <c r="AU12" s="323"/>
+      <c r="AV12" s="326"/>
+      <c r="AW12" s="327"/>
+      <c r="AX12" s="314"/>
+      <c r="AY12" s="315"/>
+      <c r="AZ12" s="318"/>
+      <c r="BA12" s="319"/>
+      <c r="BB12" s="322"/>
+      <c r="BC12" s="323"/>
+      <c r="BD12" s="326"/>
+      <c r="BE12" s="327"/>
+      <c r="BF12" s="314"/>
+      <c r="BG12" s="315"/>
+      <c r="BH12" s="318"/>
+      <c r="BI12" s="319"/>
+      <c r="BJ12" s="322"/>
+      <c r="BK12" s="323"/>
+      <c r="BL12" s="326"/>
+      <c r="BM12" s="327"/>
       <c r="BP12" s="6">
         <v>8</v>
       </c>
@@ -43700,98 +43700,98 @@
       <c r="BR12" s="2"/>
     </row>
     <row r="13" spans="2:70" ht="33" customHeight="1">
-      <c r="B13" s="330"/>
-      <c r="C13" s="330" t="s">
+      <c r="B13" s="295"/>
+      <c r="C13" s="295" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="322" t="s">
+      <c r="D13" s="296" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="323"/>
-      <c r="F13" s="326" t="s">
+      <c r="E13" s="297"/>
+      <c r="F13" s="300" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="327"/>
-      <c r="H13" s="314"/>
-      <c r="I13" s="315"/>
-      <c r="J13" s="318"/>
-      <c r="K13" s="319"/>
-      <c r="L13" s="322"/>
-      <c r="M13" s="323"/>
-      <c r="N13" s="326"/>
-      <c r="O13" s="327"/>
-      <c r="P13" s="314"/>
-      <c r="Q13" s="315"/>
-      <c r="R13" s="318"/>
-      <c r="S13" s="319"/>
-      <c r="T13" s="322" t="s">
+      <c r="G13" s="301"/>
+      <c r="H13" s="304"/>
+      <c r="I13" s="305"/>
+      <c r="J13" s="308"/>
+      <c r="K13" s="309"/>
+      <c r="L13" s="296"/>
+      <c r="M13" s="297"/>
+      <c r="N13" s="300"/>
+      <c r="O13" s="301"/>
+      <c r="P13" s="304"/>
+      <c r="Q13" s="305"/>
+      <c r="R13" s="308"/>
+      <c r="S13" s="309"/>
+      <c r="T13" s="296" t="s">
         <v>52</v>
       </c>
-      <c r="U13" s="323"/>
-      <c r="V13" s="326" t="s">
+      <c r="U13" s="297"/>
+      <c r="V13" s="300" t="s">
         <v>53</v>
       </c>
-      <c r="W13" s="327"/>
-      <c r="X13" s="314"/>
-      <c r="Y13" s="315"/>
-      <c r="Z13" s="318"/>
-      <c r="AA13" s="319"/>
-      <c r="AB13" s="322" t="s">
+      <c r="W13" s="301"/>
+      <c r="X13" s="304"/>
+      <c r="Y13" s="305"/>
+      <c r="Z13" s="308"/>
+      <c r="AA13" s="309"/>
+      <c r="AB13" s="296" t="s">
         <v>54</v>
       </c>
-      <c r="AC13" s="323"/>
-      <c r="AD13" s="326" t="s">
+      <c r="AC13" s="297"/>
+      <c r="AD13" s="300" t="s">
         <v>55</v>
       </c>
-      <c r="AE13" s="327"/>
-      <c r="AF13" s="314"/>
-      <c r="AG13" s="315"/>
-      <c r="AH13" s="318"/>
-      <c r="AI13" s="319"/>
-      <c r="AJ13" s="322"/>
-      <c r="AK13" s="323"/>
-      <c r="AL13" s="335"/>
-      <c r="AM13" s="336"/>
-      <c r="AP13" s="322" t="s">
+      <c r="AE13" s="301"/>
+      <c r="AF13" s="304"/>
+      <c r="AG13" s="305"/>
+      <c r="AH13" s="308"/>
+      <c r="AI13" s="309"/>
+      <c r="AJ13" s="296"/>
+      <c r="AK13" s="297"/>
+      <c r="AL13" s="336"/>
+      <c r="AM13" s="337"/>
+      <c r="AP13" s="296" t="s">
         <v>33</v>
       </c>
-      <c r="AQ13" s="323"/>
-      <c r="AR13" s="326" t="s">
+      <c r="AQ13" s="297"/>
+      <c r="AR13" s="300" t="s">
         <v>34</v>
       </c>
-      <c r="AS13" s="327"/>
-      <c r="AT13" s="314" t="s">
+      <c r="AS13" s="301"/>
+      <c r="AT13" s="304" t="s">
         <v>17</v>
       </c>
-      <c r="AU13" s="315"/>
-      <c r="AV13" s="318" t="s">
+      <c r="AU13" s="305"/>
+      <c r="AV13" s="308" t="s">
         <v>35</v>
       </c>
-      <c r="AW13" s="319"/>
-      <c r="AX13" s="322" t="s">
+      <c r="AW13" s="309"/>
+      <c r="AX13" s="296" t="s">
         <v>54</v>
       </c>
-      <c r="AY13" s="323"/>
-      <c r="AZ13" s="326" t="s">
+      <c r="AY13" s="297"/>
+      <c r="AZ13" s="300" t="s">
         <v>55</v>
       </c>
-      <c r="BA13" s="327"/>
-      <c r="BB13" s="339" t="s">
+      <c r="BA13" s="301"/>
+      <c r="BB13" s="332" t="s">
         <v>68</v>
       </c>
-      <c r="BC13" s="340"/>
-      <c r="BD13" s="318" t="s">
+      <c r="BC13" s="333"/>
+      <c r="BD13" s="308" t="s">
         <v>18</v>
       </c>
-      <c r="BE13" s="319"/>
-      <c r="BF13" s="322"/>
-      <c r="BG13" s="323"/>
-      <c r="BH13" s="326"/>
-      <c r="BI13" s="327"/>
-      <c r="BJ13" s="314"/>
-      <c r="BK13" s="315"/>
-      <c r="BL13" s="318"/>
-      <c r="BM13" s="319"/>
+      <c r="BE13" s="309"/>
+      <c r="BF13" s="296"/>
+      <c r="BG13" s="297"/>
+      <c r="BH13" s="300"/>
+      <c r="BI13" s="301"/>
+      <c r="BJ13" s="304"/>
+      <c r="BK13" s="305"/>
+      <c r="BL13" s="308"/>
+      <c r="BM13" s="309"/>
       <c r="BP13" s="6">
         <v>9</v>
       </c>
@@ -43801,68 +43801,68 @@
       <c r="BR13" s="2"/>
     </row>
     <row r="14" spans="2:70" ht="33" customHeight="1">
-      <c r="B14" s="330"/>
-      <c r="C14" s="330"/>
-      <c r="D14" s="324"/>
-      <c r="E14" s="325"/>
-      <c r="F14" s="328"/>
-      <c r="G14" s="329"/>
-      <c r="H14" s="316"/>
-      <c r="I14" s="317"/>
-      <c r="J14" s="320"/>
-      <c r="K14" s="321"/>
-      <c r="L14" s="324"/>
-      <c r="M14" s="325"/>
-      <c r="N14" s="328"/>
-      <c r="O14" s="329"/>
-      <c r="P14" s="316"/>
-      <c r="Q14" s="317"/>
-      <c r="R14" s="320"/>
-      <c r="S14" s="321"/>
-      <c r="T14" s="324"/>
-      <c r="U14" s="325"/>
-      <c r="V14" s="328"/>
-      <c r="W14" s="329"/>
-      <c r="X14" s="316"/>
-      <c r="Y14" s="317"/>
-      <c r="Z14" s="320"/>
-      <c r="AA14" s="321"/>
-      <c r="AB14" s="324"/>
-      <c r="AC14" s="325"/>
-      <c r="AD14" s="328"/>
-      <c r="AE14" s="329"/>
-      <c r="AF14" s="316"/>
-      <c r="AG14" s="317"/>
-      <c r="AH14" s="320"/>
-      <c r="AI14" s="321"/>
-      <c r="AJ14" s="324"/>
-      <c r="AK14" s="325"/>
-      <c r="AL14" s="337"/>
-      <c r="AM14" s="338"/>
-      <c r="AP14" s="324"/>
-      <c r="AQ14" s="325"/>
-      <c r="AR14" s="328"/>
-      <c r="AS14" s="329"/>
-      <c r="AT14" s="316"/>
-      <c r="AU14" s="317"/>
-      <c r="AV14" s="320"/>
-      <c r="AW14" s="321"/>
-      <c r="AX14" s="324"/>
-      <c r="AY14" s="325"/>
-      <c r="AZ14" s="328"/>
-      <c r="BA14" s="329"/>
-      <c r="BB14" s="341"/>
-      <c r="BC14" s="342"/>
-      <c r="BD14" s="320"/>
-      <c r="BE14" s="321"/>
-      <c r="BF14" s="324"/>
-      <c r="BG14" s="325"/>
-      <c r="BH14" s="328"/>
-      <c r="BI14" s="329"/>
-      <c r="BJ14" s="316"/>
-      <c r="BK14" s="317"/>
-      <c r="BL14" s="320"/>
-      <c r="BM14" s="321"/>
+      <c r="B14" s="295"/>
+      <c r="C14" s="295"/>
+      <c r="D14" s="298"/>
+      <c r="E14" s="299"/>
+      <c r="F14" s="302"/>
+      <c r="G14" s="303"/>
+      <c r="H14" s="306"/>
+      <c r="I14" s="307"/>
+      <c r="J14" s="310"/>
+      <c r="K14" s="311"/>
+      <c r="L14" s="298"/>
+      <c r="M14" s="299"/>
+      <c r="N14" s="302"/>
+      <c r="O14" s="303"/>
+      <c r="P14" s="306"/>
+      <c r="Q14" s="307"/>
+      <c r="R14" s="310"/>
+      <c r="S14" s="311"/>
+      <c r="T14" s="298"/>
+      <c r="U14" s="299"/>
+      <c r="V14" s="302"/>
+      <c r="W14" s="303"/>
+      <c r="X14" s="306"/>
+      <c r="Y14" s="307"/>
+      <c r="Z14" s="310"/>
+      <c r="AA14" s="311"/>
+      <c r="AB14" s="298"/>
+      <c r="AC14" s="299"/>
+      <c r="AD14" s="302"/>
+      <c r="AE14" s="303"/>
+      <c r="AF14" s="306"/>
+      <c r="AG14" s="307"/>
+      <c r="AH14" s="310"/>
+      <c r="AI14" s="311"/>
+      <c r="AJ14" s="298"/>
+      <c r="AK14" s="299"/>
+      <c r="AL14" s="338"/>
+      <c r="AM14" s="339"/>
+      <c r="AP14" s="298"/>
+      <c r="AQ14" s="299"/>
+      <c r="AR14" s="302"/>
+      <c r="AS14" s="303"/>
+      <c r="AT14" s="306"/>
+      <c r="AU14" s="307"/>
+      <c r="AV14" s="310"/>
+      <c r="AW14" s="311"/>
+      <c r="AX14" s="298"/>
+      <c r="AY14" s="299"/>
+      <c r="AZ14" s="302"/>
+      <c r="BA14" s="303"/>
+      <c r="BB14" s="334"/>
+      <c r="BC14" s="335"/>
+      <c r="BD14" s="310"/>
+      <c r="BE14" s="311"/>
+      <c r="BF14" s="298"/>
+      <c r="BG14" s="299"/>
+      <c r="BH14" s="302"/>
+      <c r="BI14" s="303"/>
+      <c r="BJ14" s="306"/>
+      <c r="BK14" s="307"/>
+      <c r="BL14" s="310"/>
+      <c r="BM14" s="311"/>
       <c r="BP14" s="6">
         <v>10</v>
       </c>
@@ -43872,96 +43872,96 @@
       <c r="BR14" s="2"/>
     </row>
     <row r="15" spans="2:70" ht="33" customHeight="1">
-      <c r="B15" s="330"/>
-      <c r="C15" s="330"/>
-      <c r="D15" s="302" t="s">
+      <c r="B15" s="295"/>
+      <c r="C15" s="295"/>
+      <c r="D15" s="312" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="303"/>
-      <c r="F15" s="306" t="s">
+      <c r="E15" s="313"/>
+      <c r="F15" s="316" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="307"/>
-      <c r="H15" s="294"/>
-      <c r="I15" s="295"/>
-      <c r="J15" s="298"/>
-      <c r="K15" s="299"/>
-      <c r="L15" s="302"/>
-      <c r="M15" s="303"/>
-      <c r="N15" s="306"/>
-      <c r="O15" s="307"/>
-      <c r="P15" s="294"/>
-      <c r="Q15" s="295"/>
-      <c r="R15" s="298"/>
-      <c r="S15" s="299"/>
-      <c r="T15" s="302" t="s">
+      <c r="G15" s="317"/>
+      <c r="H15" s="320"/>
+      <c r="I15" s="321"/>
+      <c r="J15" s="324"/>
+      <c r="K15" s="325"/>
+      <c r="L15" s="312"/>
+      <c r="M15" s="313"/>
+      <c r="N15" s="316"/>
+      <c r="O15" s="317"/>
+      <c r="P15" s="320"/>
+      <c r="Q15" s="321"/>
+      <c r="R15" s="324"/>
+      <c r="S15" s="325"/>
+      <c r="T15" s="312" t="s">
         <v>58</v>
       </c>
-      <c r="U15" s="303"/>
-      <c r="V15" s="306" t="s">
+      <c r="U15" s="313"/>
+      <c r="V15" s="316" t="s">
         <v>32</v>
       </c>
-      <c r="W15" s="307"/>
-      <c r="X15" s="294"/>
-      <c r="Y15" s="295"/>
-      <c r="Z15" s="298"/>
-      <c r="AA15" s="299"/>
-      <c r="AB15" s="302" t="s">
+      <c r="W15" s="317"/>
+      <c r="X15" s="320"/>
+      <c r="Y15" s="321"/>
+      <c r="Z15" s="324"/>
+      <c r="AA15" s="325"/>
+      <c r="AB15" s="312" t="s">
         <v>59</v>
       </c>
-      <c r="AC15" s="303"/>
-      <c r="AD15" s="306" t="s">
+      <c r="AC15" s="313"/>
+      <c r="AD15" s="316" t="s">
         <v>34</v>
       </c>
-      <c r="AE15" s="307"/>
-      <c r="AF15" s="294"/>
-      <c r="AG15" s="295"/>
-      <c r="AH15" s="298"/>
-      <c r="AI15" s="299"/>
-      <c r="AJ15" s="302"/>
-      <c r="AK15" s="303"/>
-      <c r="AL15" s="331"/>
-      <c r="AM15" s="332"/>
-      <c r="AP15" s="302" t="s">
+      <c r="AE15" s="317"/>
+      <c r="AF15" s="320"/>
+      <c r="AG15" s="321"/>
+      <c r="AH15" s="324"/>
+      <c r="AI15" s="325"/>
+      <c r="AJ15" s="312"/>
+      <c r="AK15" s="313"/>
+      <c r="AL15" s="340"/>
+      <c r="AM15" s="341"/>
+      <c r="AP15" s="312" t="s">
         <v>45</v>
       </c>
-      <c r="AQ15" s="303"/>
-      <c r="AR15" s="306" t="s">
+      <c r="AQ15" s="313"/>
+      <c r="AR15" s="316" t="s">
         <v>46</v>
       </c>
-      <c r="AS15" s="307"/>
-      <c r="AT15" s="294" t="s">
+      <c r="AS15" s="317"/>
+      <c r="AT15" s="320" t="s">
         <v>47</v>
       </c>
-      <c r="AU15" s="295"/>
-      <c r="AV15" s="298" t="s">
+      <c r="AU15" s="321"/>
+      <c r="AV15" s="324" t="s">
         <v>48</v>
       </c>
-      <c r="AW15" s="299"/>
-      <c r="AX15" s="302" t="s">
+      <c r="AW15" s="325"/>
+      <c r="AX15" s="312" t="s">
         <v>59</v>
       </c>
-      <c r="AY15" s="303"/>
-      <c r="AZ15" s="306" t="s">
+      <c r="AY15" s="313"/>
+      <c r="AZ15" s="316" t="s">
         <v>34</v>
       </c>
-      <c r="BA15" s="307"/>
-      <c r="BB15" s="294" t="s">
+      <c r="BA15" s="317"/>
+      <c r="BB15" s="320" t="s">
         <v>24</v>
       </c>
-      <c r="BC15" s="295"/>
-      <c r="BD15" s="298" t="s">
+      <c r="BC15" s="321"/>
+      <c r="BD15" s="324" t="s">
         <v>25</v>
       </c>
-      <c r="BE15" s="299"/>
-      <c r="BF15" s="302"/>
-      <c r="BG15" s="303"/>
-      <c r="BH15" s="306"/>
-      <c r="BI15" s="307"/>
-      <c r="BJ15" s="294"/>
-      <c r="BK15" s="295"/>
-      <c r="BL15" s="298"/>
-      <c r="BM15" s="299"/>
+      <c r="BE15" s="325"/>
+      <c r="BF15" s="312"/>
+      <c r="BG15" s="313"/>
+      <c r="BH15" s="316"/>
+      <c r="BI15" s="317"/>
+      <c r="BJ15" s="320"/>
+      <c r="BK15" s="321"/>
+      <c r="BL15" s="324"/>
+      <c r="BM15" s="325"/>
       <c r="BP15" s="6">
         <v>11</v>
       </c>
@@ -43971,68 +43971,68 @@
       <c r="BR15" s="2"/>
     </row>
     <row r="16" spans="2:70" ht="33" customHeight="1">
-      <c r="B16" s="330"/>
-      <c r="C16" s="330"/>
-      <c r="D16" s="304"/>
-      <c r="E16" s="305"/>
-      <c r="F16" s="308"/>
-      <c r="G16" s="309"/>
-      <c r="H16" s="296"/>
-      <c r="I16" s="297"/>
-      <c r="J16" s="300"/>
-      <c r="K16" s="301"/>
-      <c r="L16" s="304"/>
-      <c r="M16" s="305"/>
-      <c r="N16" s="308"/>
-      <c r="O16" s="309"/>
-      <c r="P16" s="296"/>
-      <c r="Q16" s="297"/>
-      <c r="R16" s="300"/>
-      <c r="S16" s="301"/>
-      <c r="T16" s="304"/>
-      <c r="U16" s="305"/>
-      <c r="V16" s="308"/>
-      <c r="W16" s="309"/>
-      <c r="X16" s="296"/>
-      <c r="Y16" s="297"/>
-      <c r="Z16" s="300"/>
-      <c r="AA16" s="301"/>
-      <c r="AB16" s="304"/>
-      <c r="AC16" s="305"/>
-      <c r="AD16" s="308"/>
-      <c r="AE16" s="309"/>
-      <c r="AF16" s="296"/>
-      <c r="AG16" s="297"/>
-      <c r="AH16" s="300"/>
-      <c r="AI16" s="301"/>
-      <c r="AJ16" s="304"/>
-      <c r="AK16" s="305"/>
-      <c r="AL16" s="333"/>
-      <c r="AM16" s="334"/>
-      <c r="AP16" s="304"/>
-      <c r="AQ16" s="305"/>
-      <c r="AR16" s="308"/>
-      <c r="AS16" s="309"/>
-      <c r="AT16" s="296"/>
-      <c r="AU16" s="297"/>
-      <c r="AV16" s="300"/>
-      <c r="AW16" s="301"/>
-      <c r="AX16" s="304"/>
-      <c r="AY16" s="305"/>
-      <c r="AZ16" s="308"/>
-      <c r="BA16" s="309"/>
-      <c r="BB16" s="296"/>
-      <c r="BC16" s="297"/>
-      <c r="BD16" s="300"/>
-      <c r="BE16" s="301"/>
-      <c r="BF16" s="304"/>
-      <c r="BG16" s="305"/>
-      <c r="BH16" s="308"/>
-      <c r="BI16" s="309"/>
-      <c r="BJ16" s="296"/>
-      <c r="BK16" s="297"/>
-      <c r="BL16" s="300"/>
-      <c r="BM16" s="301"/>
+      <c r="B16" s="295"/>
+      <c r="C16" s="295"/>
+      <c r="D16" s="314"/>
+      <c r="E16" s="315"/>
+      <c r="F16" s="318"/>
+      <c r="G16" s="319"/>
+      <c r="H16" s="322"/>
+      <c r="I16" s="323"/>
+      <c r="J16" s="326"/>
+      <c r="K16" s="327"/>
+      <c r="L16" s="314"/>
+      <c r="M16" s="315"/>
+      <c r="N16" s="318"/>
+      <c r="O16" s="319"/>
+      <c r="P16" s="322"/>
+      <c r="Q16" s="323"/>
+      <c r="R16" s="326"/>
+      <c r="S16" s="327"/>
+      <c r="T16" s="314"/>
+      <c r="U16" s="315"/>
+      <c r="V16" s="318"/>
+      <c r="W16" s="319"/>
+      <c r="X16" s="322"/>
+      <c r="Y16" s="323"/>
+      <c r="Z16" s="326"/>
+      <c r="AA16" s="327"/>
+      <c r="AB16" s="314"/>
+      <c r="AC16" s="315"/>
+      <c r="AD16" s="318"/>
+      <c r="AE16" s="319"/>
+      <c r="AF16" s="322"/>
+      <c r="AG16" s="323"/>
+      <c r="AH16" s="326"/>
+      <c r="AI16" s="327"/>
+      <c r="AJ16" s="314"/>
+      <c r="AK16" s="315"/>
+      <c r="AL16" s="342"/>
+      <c r="AM16" s="343"/>
+      <c r="AP16" s="314"/>
+      <c r="AQ16" s="315"/>
+      <c r="AR16" s="318"/>
+      <c r="AS16" s="319"/>
+      <c r="AT16" s="322"/>
+      <c r="AU16" s="323"/>
+      <c r="AV16" s="326"/>
+      <c r="AW16" s="327"/>
+      <c r="AX16" s="314"/>
+      <c r="AY16" s="315"/>
+      <c r="AZ16" s="318"/>
+      <c r="BA16" s="319"/>
+      <c r="BB16" s="322"/>
+      <c r="BC16" s="323"/>
+      <c r="BD16" s="326"/>
+      <c r="BE16" s="327"/>
+      <c r="BF16" s="314"/>
+      <c r="BG16" s="315"/>
+      <c r="BH16" s="318"/>
+      <c r="BI16" s="319"/>
+      <c r="BJ16" s="322"/>
+      <c r="BK16" s="323"/>
+      <c r="BL16" s="326"/>
+      <c r="BM16" s="327"/>
       <c r="BP16" s="6">
         <v>12</v>
       </c>
@@ -44042,92 +44042,92 @@
       <c r="BR16" s="2"/>
     </row>
     <row r="17" spans="2:70" ht="33" customHeight="1">
-      <c r="B17" s="330" t="s">
+      <c r="B17" s="295" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="330" t="s">
+      <c r="C17" s="295" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="322"/>
-      <c r="E17" s="323"/>
-      <c r="F17" s="326"/>
-      <c r="G17" s="327"/>
-      <c r="H17" s="314"/>
-      <c r="I17" s="315"/>
-      <c r="J17" s="318"/>
-      <c r="K17" s="319"/>
-      <c r="L17" s="322" t="s">
+      <c r="D17" s="296"/>
+      <c r="E17" s="297"/>
+      <c r="F17" s="300"/>
+      <c r="G17" s="301"/>
+      <c r="H17" s="304"/>
+      <c r="I17" s="305"/>
+      <c r="J17" s="308"/>
+      <c r="K17" s="309"/>
+      <c r="L17" s="296" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="323"/>
-      <c r="N17" s="326" t="s">
+      <c r="M17" s="297"/>
+      <c r="N17" s="300" t="s">
         <v>63</v>
       </c>
-      <c r="O17" s="327"/>
-      <c r="P17" s="314" t="s">
+      <c r="O17" s="301"/>
+      <c r="P17" s="304" t="s">
         <v>64</v>
       </c>
-      <c r="Q17" s="315"/>
-      <c r="R17" s="318" t="s">
+      <c r="Q17" s="305"/>
+      <c r="R17" s="308" t="s">
         <v>65</v>
       </c>
-      <c r="S17" s="319"/>
-      <c r="T17" s="322" t="s">
+      <c r="S17" s="309"/>
+      <c r="T17" s="296" t="s">
         <v>62</v>
       </c>
-      <c r="U17" s="323"/>
-      <c r="V17" s="326" t="s">
+      <c r="U17" s="297"/>
+      <c r="V17" s="300" t="s">
         <v>66</v>
       </c>
-      <c r="W17" s="327"/>
-      <c r="X17" s="314" t="s">
+      <c r="W17" s="301"/>
+      <c r="X17" s="304" t="s">
         <v>64</v>
       </c>
-      <c r="Y17" s="315"/>
-      <c r="Z17" s="318" t="s">
+      <c r="Y17" s="305"/>
+      <c r="Z17" s="308" t="s">
         <v>67</v>
       </c>
-      <c r="AA17" s="319"/>
-      <c r="AB17" s="322"/>
-      <c r="AC17" s="323"/>
-      <c r="AD17" s="326"/>
-      <c r="AE17" s="327"/>
-      <c r="AF17" s="314"/>
-      <c r="AG17" s="315"/>
-      <c r="AH17" s="318"/>
-      <c r="AI17" s="319"/>
-      <c r="AJ17" s="322"/>
-      <c r="AK17" s="323"/>
-      <c r="AL17" s="335"/>
-      <c r="AM17" s="336"/>
-      <c r="AP17" s="322"/>
-      <c r="AQ17" s="323"/>
-      <c r="AR17" s="326"/>
-      <c r="AS17" s="327"/>
-      <c r="AT17" s="314"/>
-      <c r="AU17" s="315"/>
-      <c r="AV17" s="318"/>
-      <c r="AW17" s="319"/>
-      <c r="AX17" s="322"/>
-      <c r="AY17" s="323"/>
-      <c r="AZ17" s="326"/>
-      <c r="BA17" s="327"/>
-      <c r="BB17" s="314"/>
-      <c r="BC17" s="315"/>
-      <c r="BD17" s="318"/>
-      <c r="BE17" s="319"/>
-      <c r="BF17" s="322"/>
-      <c r="BG17" s="323"/>
-      <c r="BH17" s="326"/>
-      <c r="BI17" s="327"/>
-      <c r="BJ17" s="314" t="s">
+      <c r="AA17" s="309"/>
+      <c r="AB17" s="296"/>
+      <c r="AC17" s="297"/>
+      <c r="AD17" s="300"/>
+      <c r="AE17" s="301"/>
+      <c r="AF17" s="304"/>
+      <c r="AG17" s="305"/>
+      <c r="AH17" s="308"/>
+      <c r="AI17" s="309"/>
+      <c r="AJ17" s="296"/>
+      <c r="AK17" s="297"/>
+      <c r="AL17" s="336"/>
+      <c r="AM17" s="337"/>
+      <c r="AP17" s="296"/>
+      <c r="AQ17" s="297"/>
+      <c r="AR17" s="300"/>
+      <c r="AS17" s="301"/>
+      <c r="AT17" s="304"/>
+      <c r="AU17" s="305"/>
+      <c r="AV17" s="308"/>
+      <c r="AW17" s="309"/>
+      <c r="AX17" s="296"/>
+      <c r="AY17" s="297"/>
+      <c r="AZ17" s="300"/>
+      <c r="BA17" s="301"/>
+      <c r="BB17" s="304"/>
+      <c r="BC17" s="305"/>
+      <c r="BD17" s="308"/>
+      <c r="BE17" s="309"/>
+      <c r="BF17" s="296"/>
+      <c r="BG17" s="297"/>
+      <c r="BH17" s="300"/>
+      <c r="BI17" s="301"/>
+      <c r="BJ17" s="304" t="s">
         <v>80</v>
       </c>
-      <c r="BK17" s="315"/>
-      <c r="BL17" s="318" t="s">
+      <c r="BK17" s="305"/>
+      <c r="BL17" s="308" t="s">
         <v>81</v>
       </c>
-      <c r="BM17" s="319"/>
+      <c r="BM17" s="309"/>
       <c r="BP17" s="6">
         <v>13</v>
       </c>
@@ -44137,68 +44137,68 @@
       <c r="BR17" s="2"/>
     </row>
     <row r="18" spans="2:70" ht="33" customHeight="1">
-      <c r="B18" s="330"/>
-      <c r="C18" s="330"/>
-      <c r="D18" s="324"/>
-      <c r="E18" s="325"/>
-      <c r="F18" s="328"/>
-      <c r="G18" s="329"/>
-      <c r="H18" s="316"/>
-      <c r="I18" s="317"/>
-      <c r="J18" s="320"/>
-      <c r="K18" s="321"/>
-      <c r="L18" s="324"/>
-      <c r="M18" s="325"/>
-      <c r="N18" s="328"/>
-      <c r="O18" s="329"/>
-      <c r="P18" s="316"/>
-      <c r="Q18" s="317"/>
-      <c r="R18" s="320"/>
-      <c r="S18" s="321"/>
-      <c r="T18" s="324"/>
-      <c r="U18" s="325"/>
-      <c r="V18" s="328"/>
-      <c r="W18" s="329"/>
-      <c r="X18" s="316"/>
-      <c r="Y18" s="317"/>
-      <c r="Z18" s="320"/>
-      <c r="AA18" s="321"/>
-      <c r="AB18" s="324"/>
-      <c r="AC18" s="325"/>
-      <c r="AD18" s="328"/>
-      <c r="AE18" s="329"/>
-      <c r="AF18" s="316"/>
-      <c r="AG18" s="317"/>
-      <c r="AH18" s="320"/>
-      <c r="AI18" s="321"/>
-      <c r="AJ18" s="324"/>
-      <c r="AK18" s="325"/>
-      <c r="AL18" s="337"/>
-      <c r="AM18" s="338"/>
-      <c r="AP18" s="324"/>
-      <c r="AQ18" s="325"/>
-      <c r="AR18" s="328"/>
-      <c r="AS18" s="329"/>
-      <c r="AT18" s="316"/>
-      <c r="AU18" s="317"/>
-      <c r="AV18" s="320"/>
-      <c r="AW18" s="321"/>
-      <c r="AX18" s="324"/>
-      <c r="AY18" s="325"/>
-      <c r="AZ18" s="328"/>
-      <c r="BA18" s="329"/>
-      <c r="BB18" s="316"/>
-      <c r="BC18" s="317"/>
-      <c r="BD18" s="320"/>
-      <c r="BE18" s="321"/>
-      <c r="BF18" s="324"/>
-      <c r="BG18" s="325"/>
-      <c r="BH18" s="328"/>
-      <c r="BI18" s="329"/>
-      <c r="BJ18" s="316"/>
-      <c r="BK18" s="317"/>
-      <c r="BL18" s="320"/>
-      <c r="BM18" s="321"/>
+      <c r="B18" s="295"/>
+      <c r="C18" s="295"/>
+      <c r="D18" s="298"/>
+      <c r="E18" s="299"/>
+      <c r="F18" s="302"/>
+      <c r="G18" s="303"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="307"/>
+      <c r="J18" s="310"/>
+      <c r="K18" s="311"/>
+      <c r="L18" s="298"/>
+      <c r="M18" s="299"/>
+      <c r="N18" s="302"/>
+      <c r="O18" s="303"/>
+      <c r="P18" s="306"/>
+      <c r="Q18" s="307"/>
+      <c r="R18" s="310"/>
+      <c r="S18" s="311"/>
+      <c r="T18" s="298"/>
+      <c r="U18" s="299"/>
+      <c r="V18" s="302"/>
+      <c r="W18" s="303"/>
+      <c r="X18" s="306"/>
+      <c r="Y18" s="307"/>
+      <c r="Z18" s="310"/>
+      <c r="AA18" s="311"/>
+      <c r="AB18" s="298"/>
+      <c r="AC18" s="299"/>
+      <c r="AD18" s="302"/>
+      <c r="AE18" s="303"/>
+      <c r="AF18" s="306"/>
+      <c r="AG18" s="307"/>
+      <c r="AH18" s="310"/>
+      <c r="AI18" s="311"/>
+      <c r="AJ18" s="298"/>
+      <c r="AK18" s="299"/>
+      <c r="AL18" s="338"/>
+      <c r="AM18" s="339"/>
+      <c r="AP18" s="298"/>
+      <c r="AQ18" s="299"/>
+      <c r="AR18" s="302"/>
+      <c r="AS18" s="303"/>
+      <c r="AT18" s="306"/>
+      <c r="AU18" s="307"/>
+      <c r="AV18" s="310"/>
+      <c r="AW18" s="311"/>
+      <c r="AX18" s="298"/>
+      <c r="AY18" s="299"/>
+      <c r="AZ18" s="302"/>
+      <c r="BA18" s="303"/>
+      <c r="BB18" s="306"/>
+      <c r="BC18" s="307"/>
+      <c r="BD18" s="310"/>
+      <c r="BE18" s="311"/>
+      <c r="BF18" s="298"/>
+      <c r="BG18" s="299"/>
+      <c r="BH18" s="302"/>
+      <c r="BI18" s="303"/>
+      <c r="BJ18" s="306"/>
+      <c r="BK18" s="307"/>
+      <c r="BL18" s="310"/>
+      <c r="BM18" s="311"/>
       <c r="BP18" s="6">
         <v>14</v>
       </c>
@@ -44208,88 +44208,88 @@
       <c r="BR18" s="2"/>
     </row>
     <row r="19" spans="2:70" ht="33" customHeight="1">
-      <c r="B19" s="330"/>
-      <c r="C19" s="330"/>
-      <c r="D19" s="310"/>
-      <c r="E19" s="311"/>
-      <c r="F19" s="306"/>
-      <c r="G19" s="307"/>
-      <c r="H19" s="294"/>
-      <c r="I19" s="295"/>
-      <c r="J19" s="298"/>
-      <c r="K19" s="299"/>
-      <c r="L19" s="302" t="s">
+      <c r="B19" s="295"/>
+      <c r="C19" s="295"/>
+      <c r="D19" s="328"/>
+      <c r="E19" s="329"/>
+      <c r="F19" s="316"/>
+      <c r="G19" s="317"/>
+      <c r="H19" s="320"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="324"/>
+      <c r="K19" s="325"/>
+      <c r="L19" s="312" t="s">
         <v>69</v>
       </c>
-      <c r="M19" s="303"/>
-      <c r="N19" s="306" t="s">
+      <c r="M19" s="313"/>
+      <c r="N19" s="316" t="s">
         <v>70</v>
       </c>
-      <c r="O19" s="307"/>
-      <c r="P19" s="294" t="s">
+      <c r="O19" s="317"/>
+      <c r="P19" s="320" t="s">
         <v>71</v>
       </c>
-      <c r="Q19" s="295"/>
-      <c r="R19" s="298" t="s">
+      <c r="Q19" s="321"/>
+      <c r="R19" s="324" t="s">
         <v>72</v>
       </c>
-      <c r="S19" s="299"/>
-      <c r="T19" s="302" t="s">
+      <c r="S19" s="325"/>
+      <c r="T19" s="312" t="s">
         <v>73</v>
       </c>
-      <c r="U19" s="303"/>
-      <c r="V19" s="306" t="s">
+      <c r="U19" s="313"/>
+      <c r="V19" s="316" t="s">
         <v>74</v>
       </c>
-      <c r="W19" s="307"/>
-      <c r="X19" s="294" t="s">
+      <c r="W19" s="317"/>
+      <c r="X19" s="320" t="s">
         <v>75</v>
       </c>
-      <c r="Y19" s="295"/>
-      <c r="Z19" s="298" t="s">
+      <c r="Y19" s="321"/>
+      <c r="Z19" s="324" t="s">
         <v>76</v>
       </c>
-      <c r="AA19" s="299"/>
-      <c r="AB19" s="310"/>
-      <c r="AC19" s="311"/>
-      <c r="AD19" s="306"/>
-      <c r="AE19" s="307"/>
-      <c r="AF19" s="294"/>
-      <c r="AG19" s="295"/>
-      <c r="AH19" s="298"/>
-      <c r="AI19" s="299"/>
-      <c r="AJ19" s="302"/>
-      <c r="AK19" s="303"/>
-      <c r="AL19" s="331"/>
-      <c r="AM19" s="332"/>
-      <c r="AP19" s="310"/>
-      <c r="AQ19" s="311"/>
-      <c r="AR19" s="306"/>
-      <c r="AS19" s="307"/>
-      <c r="AT19" s="294"/>
-      <c r="AU19" s="295"/>
-      <c r="AV19" s="298"/>
-      <c r="AW19" s="299"/>
-      <c r="AX19" s="310"/>
-      <c r="AY19" s="311"/>
-      <c r="AZ19" s="306"/>
-      <c r="BA19" s="307"/>
-      <c r="BB19" s="294"/>
-      <c r="BC19" s="295"/>
-      <c r="BD19" s="298"/>
-      <c r="BE19" s="299"/>
-      <c r="BF19" s="310"/>
-      <c r="BG19" s="311"/>
-      <c r="BH19" s="306"/>
-      <c r="BI19" s="307"/>
-      <c r="BJ19" s="294" t="s">
+      <c r="AA19" s="325"/>
+      <c r="AB19" s="328"/>
+      <c r="AC19" s="329"/>
+      <c r="AD19" s="316"/>
+      <c r="AE19" s="317"/>
+      <c r="AF19" s="320"/>
+      <c r="AG19" s="321"/>
+      <c r="AH19" s="324"/>
+      <c r="AI19" s="325"/>
+      <c r="AJ19" s="312"/>
+      <c r="AK19" s="313"/>
+      <c r="AL19" s="340"/>
+      <c r="AM19" s="341"/>
+      <c r="AP19" s="328"/>
+      <c r="AQ19" s="329"/>
+      <c r="AR19" s="316"/>
+      <c r="AS19" s="317"/>
+      <c r="AT19" s="320"/>
+      <c r="AU19" s="321"/>
+      <c r="AV19" s="324"/>
+      <c r="AW19" s="325"/>
+      <c r="AX19" s="328"/>
+      <c r="AY19" s="329"/>
+      <c r="AZ19" s="316"/>
+      <c r="BA19" s="317"/>
+      <c r="BB19" s="320"/>
+      <c r="BC19" s="321"/>
+      <c r="BD19" s="324"/>
+      <c r="BE19" s="325"/>
+      <c r="BF19" s="328"/>
+      <c r="BG19" s="329"/>
+      <c r="BH19" s="316"/>
+      <c r="BI19" s="317"/>
+      <c r="BJ19" s="320" t="s">
         <v>86</v>
       </c>
-      <c r="BK19" s="295"/>
-      <c r="BL19" s="298" t="s">
+      <c r="BK19" s="321"/>
+      <c r="BL19" s="324" t="s">
         <v>87</v>
       </c>
-      <c r="BM19" s="299"/>
+      <c r="BM19" s="325"/>
       <c r="BP19" s="6">
         <v>15</v>
       </c>
@@ -44299,68 +44299,68 @@
       <c r="BR19" s="2"/>
     </row>
     <row r="20" spans="2:70" ht="33" customHeight="1">
-      <c r="B20" s="330"/>
-      <c r="C20" s="330"/>
-      <c r="D20" s="312"/>
-      <c r="E20" s="313"/>
-      <c r="F20" s="308"/>
-      <c r="G20" s="309"/>
-      <c r="H20" s="296"/>
-      <c r="I20" s="297"/>
-      <c r="J20" s="300"/>
-      <c r="K20" s="301"/>
-      <c r="L20" s="304"/>
-      <c r="M20" s="305"/>
-      <c r="N20" s="308"/>
-      <c r="O20" s="309"/>
-      <c r="P20" s="296"/>
-      <c r="Q20" s="297"/>
-      <c r="R20" s="300"/>
-      <c r="S20" s="301"/>
-      <c r="T20" s="304"/>
-      <c r="U20" s="305"/>
-      <c r="V20" s="308"/>
-      <c r="W20" s="309"/>
-      <c r="X20" s="296"/>
-      <c r="Y20" s="297"/>
-      <c r="Z20" s="300"/>
-      <c r="AA20" s="301"/>
-      <c r="AB20" s="312"/>
-      <c r="AC20" s="313"/>
-      <c r="AD20" s="308"/>
-      <c r="AE20" s="309"/>
-      <c r="AF20" s="296"/>
-      <c r="AG20" s="297"/>
-      <c r="AH20" s="300"/>
-      <c r="AI20" s="301"/>
-      <c r="AJ20" s="304"/>
-      <c r="AK20" s="305"/>
-      <c r="AL20" s="333"/>
-      <c r="AM20" s="334"/>
-      <c r="AP20" s="312"/>
-      <c r="AQ20" s="313"/>
-      <c r="AR20" s="308"/>
-      <c r="AS20" s="309"/>
-      <c r="AT20" s="296"/>
-      <c r="AU20" s="297"/>
-      <c r="AV20" s="300"/>
-      <c r="AW20" s="301"/>
-      <c r="AX20" s="312"/>
-      <c r="AY20" s="313"/>
-      <c r="AZ20" s="308"/>
-      <c r="BA20" s="309"/>
-      <c r="BB20" s="296"/>
-      <c r="BC20" s="297"/>
-      <c r="BD20" s="300"/>
-      <c r="BE20" s="301"/>
-      <c r="BF20" s="312"/>
-      <c r="BG20" s="313"/>
-      <c r="BH20" s="308"/>
-      <c r="BI20" s="309"/>
-      <c r="BJ20" s="296"/>
-      <c r="BK20" s="297"/>
-      <c r="BL20" s="300"/>
-      <c r="BM20" s="301"/>
+      <c r="B20" s="295"/>
+      <c r="C20" s="295"/>
+      <c r="D20" s="330"/>
+      <c r="E20" s="331"/>
+      <c r="F20" s="318"/>
+      <c r="G20" s="319"/>
+      <c r="H20" s="322"/>
+      <c r="I20" s="323"/>
+      <c r="J20" s="326"/>
+      <c r="K20" s="327"/>
+      <c r="L20" s="314"/>
+      <c r="M20" s="315"/>
+      <c r="N20" s="318"/>
+      <c r="O20" s="319"/>
+      <c r="P20" s="322"/>
+      <c r="Q20" s="323"/>
+      <c r="R20" s="326"/>
+      <c r="S20" s="327"/>
+      <c r="T20" s="314"/>
+      <c r="U20" s="315"/>
+      <c r="V20" s="318"/>
+      <c r="W20" s="319"/>
+      <c r="X20" s="322"/>
+      <c r="Y20" s="323"/>
+      <c r="Z20" s="326"/>
+      <c r="AA20" s="327"/>
+      <c r="AB20" s="330"/>
+      <c r="AC20" s="331"/>
+      <c r="AD20" s="318"/>
+      <c r="AE20" s="319"/>
+      <c r="AF20" s="322"/>
+      <c r="AG20" s="323"/>
+      <c r="AH20" s="326"/>
+      <c r="AI20" s="327"/>
+      <c r="AJ20" s="314"/>
+      <c r="AK20" s="315"/>
+      <c r="AL20" s="342"/>
+      <c r="AM20" s="343"/>
+      <c r="AP20" s="330"/>
+      <c r="AQ20" s="331"/>
+      <c r="AR20" s="318"/>
+      <c r="AS20" s="319"/>
+      <c r="AT20" s="322"/>
+      <c r="AU20" s="323"/>
+      <c r="AV20" s="326"/>
+      <c r="AW20" s="327"/>
+      <c r="AX20" s="330"/>
+      <c r="AY20" s="331"/>
+      <c r="AZ20" s="318"/>
+      <c r="BA20" s="319"/>
+      <c r="BB20" s="322"/>
+      <c r="BC20" s="323"/>
+      <c r="BD20" s="326"/>
+      <c r="BE20" s="327"/>
+      <c r="BF20" s="330"/>
+      <c r="BG20" s="331"/>
+      <c r="BH20" s="318"/>
+      <c r="BI20" s="319"/>
+      <c r="BJ20" s="322"/>
+      <c r="BK20" s="323"/>
+      <c r="BL20" s="326"/>
+      <c r="BM20" s="327"/>
       <c r="BP20" s="6">
         <v>16</v>
       </c>
@@ -44370,86 +44370,86 @@
       <c r="BR20" s="2"/>
     </row>
     <row r="21" spans="2:70" ht="33" customHeight="1">
-      <c r="B21" s="330"/>
-      <c r="C21" s="330" t="s">
+      <c r="B21" s="295"/>
+      <c r="C21" s="295" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="322"/>
-      <c r="E21" s="323"/>
-      <c r="F21" s="326"/>
-      <c r="G21" s="327"/>
-      <c r="H21" s="314"/>
-      <c r="I21" s="315"/>
-      <c r="J21" s="318"/>
-      <c r="K21" s="319"/>
-      <c r="L21" s="322" t="s">
+      <c r="D21" s="296"/>
+      <c r="E21" s="297"/>
+      <c r="F21" s="300"/>
+      <c r="G21" s="301"/>
+      <c r="H21" s="304"/>
+      <c r="I21" s="305"/>
+      <c r="J21" s="308"/>
+      <c r="K21" s="309"/>
+      <c r="L21" s="296" t="s">
         <v>77</v>
       </c>
-      <c r="M21" s="323"/>
-      <c r="N21" s="326" t="s">
+      <c r="M21" s="297"/>
+      <c r="N21" s="300" t="s">
         <v>78</v>
       </c>
-      <c r="O21" s="327"/>
-      <c r="P21" s="314"/>
-      <c r="Q21" s="315"/>
-      <c r="R21" s="318"/>
-      <c r="S21" s="319"/>
-      <c r="T21" s="322" t="s">
+      <c r="O21" s="301"/>
+      <c r="P21" s="304"/>
+      <c r="Q21" s="305"/>
+      <c r="R21" s="308"/>
+      <c r="S21" s="309"/>
+      <c r="T21" s="296" t="s">
         <v>77</v>
       </c>
-      <c r="U21" s="323"/>
-      <c r="V21" s="326" t="s">
+      <c r="U21" s="297"/>
+      <c r="V21" s="300" t="s">
         <v>79</v>
       </c>
-      <c r="W21" s="327"/>
-      <c r="X21" s="314"/>
-      <c r="Y21" s="315"/>
-      <c r="Z21" s="318"/>
-      <c r="AA21" s="319"/>
-      <c r="AB21" s="322"/>
-      <c r="AC21" s="323"/>
-      <c r="AD21" s="326"/>
-      <c r="AE21" s="327"/>
-      <c r="AF21" s="314"/>
-      <c r="AG21" s="315"/>
-      <c r="AH21" s="318"/>
-      <c r="AI21" s="319"/>
-      <c r="AJ21" s="322"/>
-      <c r="AK21" s="323"/>
-      <c r="AL21" s="335"/>
-      <c r="AM21" s="336"/>
-      <c r="AP21" s="322" t="s">
+      <c r="W21" s="301"/>
+      <c r="X21" s="304"/>
+      <c r="Y21" s="305"/>
+      <c r="Z21" s="308"/>
+      <c r="AA21" s="309"/>
+      <c r="AB21" s="296"/>
+      <c r="AC21" s="297"/>
+      <c r="AD21" s="300"/>
+      <c r="AE21" s="301"/>
+      <c r="AF21" s="304"/>
+      <c r="AG21" s="305"/>
+      <c r="AH21" s="308"/>
+      <c r="AI21" s="309"/>
+      <c r="AJ21" s="296"/>
+      <c r="AK21" s="297"/>
+      <c r="AL21" s="336"/>
+      <c r="AM21" s="337"/>
+      <c r="AP21" s="296" t="s">
         <v>62</v>
       </c>
-      <c r="AQ21" s="323"/>
-      <c r="AR21" s="326" t="s">
+      <c r="AQ21" s="297"/>
+      <c r="AR21" s="300" t="s">
         <v>63</v>
       </c>
-      <c r="AS21" s="327"/>
-      <c r="AT21" s="314"/>
-      <c r="AU21" s="315"/>
-      <c r="AV21" s="318"/>
-      <c r="AW21" s="319"/>
-      <c r="AX21" s="322" t="s">
+      <c r="AS21" s="301"/>
+      <c r="AT21" s="304"/>
+      <c r="AU21" s="305"/>
+      <c r="AV21" s="308"/>
+      <c r="AW21" s="309"/>
+      <c r="AX21" s="296" t="s">
         <v>77</v>
       </c>
-      <c r="AY21" s="323"/>
-      <c r="AZ21" s="326" t="s">
+      <c r="AY21" s="297"/>
+      <c r="AZ21" s="300" t="s">
         <v>78</v>
       </c>
-      <c r="BA21" s="327"/>
-      <c r="BB21" s="314"/>
-      <c r="BC21" s="315"/>
-      <c r="BD21" s="318"/>
-      <c r="BE21" s="319"/>
-      <c r="BF21" s="322"/>
-      <c r="BG21" s="323"/>
-      <c r="BH21" s="326"/>
-      <c r="BI21" s="327"/>
-      <c r="BJ21" s="314"/>
-      <c r="BK21" s="315"/>
-      <c r="BL21" s="318"/>
-      <c r="BM21" s="319"/>
+      <c r="BA21" s="301"/>
+      <c r="BB21" s="304"/>
+      <c r="BC21" s="305"/>
+      <c r="BD21" s="308"/>
+      <c r="BE21" s="309"/>
+      <c r="BF21" s="296"/>
+      <c r="BG21" s="297"/>
+      <c r="BH21" s="300"/>
+      <c r="BI21" s="301"/>
+      <c r="BJ21" s="304"/>
+      <c r="BK21" s="305"/>
+      <c r="BL21" s="308"/>
+      <c r="BM21" s="309"/>
       <c r="BP21" s="6">
         <v>17</v>
       </c>
@@ -44459,68 +44459,68 @@
       <c r="BR21" s="2"/>
     </row>
     <row r="22" spans="2:70" ht="33" customHeight="1">
-      <c r="B22" s="330"/>
-      <c r="C22" s="330"/>
-      <c r="D22" s="324"/>
-      <c r="E22" s="325"/>
-      <c r="F22" s="328"/>
-      <c r="G22" s="329"/>
-      <c r="H22" s="316"/>
-      <c r="I22" s="317"/>
-      <c r="J22" s="320"/>
-      <c r="K22" s="321"/>
-      <c r="L22" s="324"/>
-      <c r="M22" s="325"/>
-      <c r="N22" s="328"/>
-      <c r="O22" s="329"/>
-      <c r="P22" s="316"/>
-      <c r="Q22" s="317"/>
-      <c r="R22" s="320"/>
-      <c r="S22" s="321"/>
-      <c r="T22" s="324"/>
-      <c r="U22" s="325"/>
-      <c r="V22" s="328"/>
-      <c r="W22" s="329"/>
-      <c r="X22" s="316"/>
-      <c r="Y22" s="317"/>
-      <c r="Z22" s="320"/>
-      <c r="AA22" s="321"/>
-      <c r="AB22" s="324"/>
-      <c r="AC22" s="325"/>
-      <c r="AD22" s="328"/>
-      <c r="AE22" s="329"/>
-      <c r="AF22" s="316"/>
-      <c r="AG22" s="317"/>
-      <c r="AH22" s="320"/>
-      <c r="AI22" s="321"/>
-      <c r="AJ22" s="324"/>
-      <c r="AK22" s="325"/>
-      <c r="AL22" s="337"/>
-      <c r="AM22" s="338"/>
-      <c r="AP22" s="324"/>
-      <c r="AQ22" s="325"/>
-      <c r="AR22" s="328"/>
-      <c r="AS22" s="329"/>
-      <c r="AT22" s="316"/>
-      <c r="AU22" s="317"/>
-      <c r="AV22" s="320"/>
-      <c r="AW22" s="321"/>
-      <c r="AX22" s="324"/>
-      <c r="AY22" s="325"/>
-      <c r="AZ22" s="328"/>
-      <c r="BA22" s="329"/>
-      <c r="BB22" s="316"/>
-      <c r="BC22" s="317"/>
-      <c r="BD22" s="320"/>
-      <c r="BE22" s="321"/>
-      <c r="BF22" s="324"/>
-      <c r="BG22" s="325"/>
-      <c r="BH22" s="328"/>
-      <c r="BI22" s="329"/>
-      <c r="BJ22" s="316"/>
-      <c r="BK22" s="317"/>
-      <c r="BL22" s="320"/>
-      <c r="BM22" s="321"/>
+      <c r="B22" s="295"/>
+      <c r="C22" s="295"/>
+      <c r="D22" s="298"/>
+      <c r="E22" s="299"/>
+      <c r="F22" s="302"/>
+      <c r="G22" s="303"/>
+      <c r="H22" s="306"/>
+      <c r="I22" s="307"/>
+      <c r="J22" s="310"/>
+      <c r="K22" s="311"/>
+      <c r="L22" s="298"/>
+      <c r="M22" s="299"/>
+      <c r="N22" s="302"/>
+      <c r="O22" s="303"/>
+      <c r="P22" s="306"/>
+      <c r="Q22" s="307"/>
+      <c r="R22" s="310"/>
+      <c r="S22" s="311"/>
+      <c r="T22" s="298"/>
+      <c r="U22" s="299"/>
+      <c r="V22" s="302"/>
+      <c r="W22" s="303"/>
+      <c r="X22" s="306"/>
+      <c r="Y22" s="307"/>
+      <c r="Z22" s="310"/>
+      <c r="AA22" s="311"/>
+      <c r="AB22" s="298"/>
+      <c r="AC22" s="299"/>
+      <c r="AD22" s="302"/>
+      <c r="AE22" s="303"/>
+      <c r="AF22" s="306"/>
+      <c r="AG22" s="307"/>
+      <c r="AH22" s="310"/>
+      <c r="AI22" s="311"/>
+      <c r="AJ22" s="298"/>
+      <c r="AK22" s="299"/>
+      <c r="AL22" s="338"/>
+      <c r="AM22" s="339"/>
+      <c r="AP22" s="298"/>
+      <c r="AQ22" s="299"/>
+      <c r="AR22" s="302"/>
+      <c r="AS22" s="303"/>
+      <c r="AT22" s="306"/>
+      <c r="AU22" s="307"/>
+      <c r="AV22" s="310"/>
+      <c r="AW22" s="311"/>
+      <c r="AX22" s="298"/>
+      <c r="AY22" s="299"/>
+      <c r="AZ22" s="302"/>
+      <c r="BA22" s="303"/>
+      <c r="BB22" s="306"/>
+      <c r="BC22" s="307"/>
+      <c r="BD22" s="310"/>
+      <c r="BE22" s="311"/>
+      <c r="BF22" s="298"/>
+      <c r="BG22" s="299"/>
+      <c r="BH22" s="302"/>
+      <c r="BI22" s="303"/>
+      <c r="BJ22" s="306"/>
+      <c r="BK22" s="307"/>
+      <c r="BL22" s="310"/>
+      <c r="BM22" s="311"/>
       <c r="BP22" s="6">
         <v>18</v>
       </c>
@@ -44530,683 +44530,997 @@
       <c r="BR22" s="2"/>
     </row>
     <row r="23" spans="2:70" ht="33" customHeight="1">
-      <c r="B23" s="330"/>
-      <c r="C23" s="330"/>
-      <c r="D23" s="310"/>
-      <c r="E23" s="311"/>
-      <c r="F23" s="306"/>
-      <c r="G23" s="307"/>
-      <c r="H23" s="294"/>
-      <c r="I23" s="295"/>
-      <c r="J23" s="298"/>
-      <c r="K23" s="299"/>
-      <c r="L23" s="302" t="s">
+      <c r="B23" s="295"/>
+      <c r="C23" s="295"/>
+      <c r="D23" s="328"/>
+      <c r="E23" s="329"/>
+      <c r="F23" s="316"/>
+      <c r="G23" s="317"/>
+      <c r="H23" s="320"/>
+      <c r="I23" s="321"/>
+      <c r="J23" s="324"/>
+      <c r="K23" s="325"/>
+      <c r="L23" s="312" t="s">
         <v>82</v>
       </c>
-      <c r="M23" s="303"/>
-      <c r="N23" s="306" t="s">
+      <c r="M23" s="313"/>
+      <c r="N23" s="316" t="s">
         <v>83</v>
       </c>
-      <c r="O23" s="307"/>
-      <c r="P23" s="294"/>
-      <c r="Q23" s="295"/>
-      <c r="R23" s="298"/>
-      <c r="S23" s="299"/>
-      <c r="T23" s="302" t="s">
+      <c r="O23" s="317"/>
+      <c r="P23" s="320"/>
+      <c r="Q23" s="321"/>
+      <c r="R23" s="324"/>
+      <c r="S23" s="325"/>
+      <c r="T23" s="312" t="s">
         <v>84</v>
       </c>
-      <c r="U23" s="303"/>
-      <c r="V23" s="306" t="s">
+      <c r="U23" s="313"/>
+      <c r="V23" s="316" t="s">
         <v>85</v>
       </c>
-      <c r="W23" s="307"/>
-      <c r="X23" s="294"/>
-      <c r="Y23" s="295"/>
-      <c r="Z23" s="298"/>
-      <c r="AA23" s="299"/>
-      <c r="AB23" s="310"/>
-      <c r="AC23" s="311"/>
-      <c r="AD23" s="306"/>
-      <c r="AE23" s="307"/>
-      <c r="AF23" s="294"/>
-      <c r="AG23" s="295"/>
-      <c r="AH23" s="298"/>
-      <c r="AI23" s="299"/>
-      <c r="AJ23" s="302"/>
-      <c r="AK23" s="303"/>
-      <c r="AL23" s="331"/>
-      <c r="AM23" s="332"/>
-      <c r="AP23" s="302" t="s">
+      <c r="W23" s="317"/>
+      <c r="X23" s="320"/>
+      <c r="Y23" s="321"/>
+      <c r="Z23" s="324"/>
+      <c r="AA23" s="325"/>
+      <c r="AB23" s="328"/>
+      <c r="AC23" s="329"/>
+      <c r="AD23" s="316"/>
+      <c r="AE23" s="317"/>
+      <c r="AF23" s="320"/>
+      <c r="AG23" s="321"/>
+      <c r="AH23" s="324"/>
+      <c r="AI23" s="325"/>
+      <c r="AJ23" s="312"/>
+      <c r="AK23" s="313"/>
+      <c r="AL23" s="340"/>
+      <c r="AM23" s="341"/>
+      <c r="AP23" s="312" t="s">
         <v>69</v>
       </c>
-      <c r="AQ23" s="303"/>
-      <c r="AR23" s="306" t="s">
+      <c r="AQ23" s="313"/>
+      <c r="AR23" s="316" t="s">
         <v>70</v>
       </c>
-      <c r="AS23" s="307"/>
-      <c r="AT23" s="294"/>
-      <c r="AU23" s="295"/>
-      <c r="AV23" s="298"/>
-      <c r="AW23" s="299"/>
-      <c r="AX23" s="302" t="s">
+      <c r="AS23" s="317"/>
+      <c r="AT23" s="320"/>
+      <c r="AU23" s="321"/>
+      <c r="AV23" s="324"/>
+      <c r="AW23" s="325"/>
+      <c r="AX23" s="312" t="s">
         <v>82</v>
       </c>
-      <c r="AY23" s="303"/>
-      <c r="AZ23" s="306" t="s">
+      <c r="AY23" s="313"/>
+      <c r="AZ23" s="316" t="s">
         <v>83</v>
       </c>
-      <c r="BA23" s="307"/>
-      <c r="BB23" s="294"/>
-      <c r="BC23" s="295"/>
-      <c r="BD23" s="298"/>
-      <c r="BE23" s="299"/>
-      <c r="BF23" s="302"/>
-      <c r="BG23" s="303"/>
-      <c r="BH23" s="306"/>
-      <c r="BI23" s="307"/>
-      <c r="BJ23" s="294"/>
-      <c r="BK23" s="295"/>
-      <c r="BL23" s="298"/>
-      <c r="BM23" s="299"/>
+      <c r="BA23" s="317"/>
+      <c r="BB23" s="320"/>
+      <c r="BC23" s="321"/>
+      <c r="BD23" s="324"/>
+      <c r="BE23" s="325"/>
+      <c r="BF23" s="312"/>
+      <c r="BG23" s="313"/>
+      <c r="BH23" s="316"/>
+      <c r="BI23" s="317"/>
+      <c r="BJ23" s="320"/>
+      <c r="BK23" s="321"/>
+      <c r="BL23" s="324"/>
+      <c r="BM23" s="325"/>
       <c r="BR23" s="2"/>
     </row>
     <row r="24" spans="2:70" ht="33" customHeight="1">
-      <c r="B24" s="330"/>
-      <c r="C24" s="330"/>
-      <c r="D24" s="312"/>
-      <c r="E24" s="313"/>
-      <c r="F24" s="308"/>
-      <c r="G24" s="309"/>
-      <c r="H24" s="296"/>
-      <c r="I24" s="297"/>
-      <c r="J24" s="300"/>
-      <c r="K24" s="301"/>
-      <c r="L24" s="304"/>
-      <c r="M24" s="305"/>
-      <c r="N24" s="308"/>
-      <c r="O24" s="309"/>
-      <c r="P24" s="296"/>
-      <c r="Q24" s="297"/>
-      <c r="R24" s="300"/>
-      <c r="S24" s="301"/>
-      <c r="T24" s="304"/>
-      <c r="U24" s="305"/>
-      <c r="V24" s="308"/>
-      <c r="W24" s="309"/>
-      <c r="X24" s="296"/>
-      <c r="Y24" s="297"/>
-      <c r="Z24" s="300"/>
-      <c r="AA24" s="301"/>
-      <c r="AB24" s="312"/>
-      <c r="AC24" s="313"/>
-      <c r="AD24" s="308"/>
-      <c r="AE24" s="309"/>
-      <c r="AF24" s="296"/>
-      <c r="AG24" s="297"/>
-      <c r="AH24" s="300"/>
-      <c r="AI24" s="301"/>
-      <c r="AJ24" s="304"/>
-      <c r="AK24" s="305"/>
-      <c r="AL24" s="333"/>
-      <c r="AM24" s="334"/>
-      <c r="AP24" s="304"/>
-      <c r="AQ24" s="305"/>
-      <c r="AR24" s="308"/>
-      <c r="AS24" s="309"/>
-      <c r="AT24" s="296"/>
-      <c r="AU24" s="297"/>
-      <c r="AV24" s="300"/>
-      <c r="AW24" s="301"/>
-      <c r="AX24" s="304"/>
-      <c r="AY24" s="305"/>
-      <c r="AZ24" s="308"/>
-      <c r="BA24" s="309"/>
-      <c r="BB24" s="296"/>
-      <c r="BC24" s="297"/>
-      <c r="BD24" s="300"/>
-      <c r="BE24" s="301"/>
-      <c r="BF24" s="304"/>
-      <c r="BG24" s="305"/>
-      <c r="BH24" s="308"/>
-      <c r="BI24" s="309"/>
-      <c r="BJ24" s="296"/>
-      <c r="BK24" s="297"/>
-      <c r="BL24" s="300"/>
-      <c r="BM24" s="301"/>
+      <c r="B24" s="295"/>
+      <c r="C24" s="295"/>
+      <c r="D24" s="330"/>
+      <c r="E24" s="331"/>
+      <c r="F24" s="318"/>
+      <c r="G24" s="319"/>
+      <c r="H24" s="322"/>
+      <c r="I24" s="323"/>
+      <c r="J24" s="326"/>
+      <c r="K24" s="327"/>
+      <c r="L24" s="314"/>
+      <c r="M24" s="315"/>
+      <c r="N24" s="318"/>
+      <c r="O24" s="319"/>
+      <c r="P24" s="322"/>
+      <c r="Q24" s="323"/>
+      <c r="R24" s="326"/>
+      <c r="S24" s="327"/>
+      <c r="T24" s="314"/>
+      <c r="U24" s="315"/>
+      <c r="V24" s="318"/>
+      <c r="W24" s="319"/>
+      <c r="X24" s="322"/>
+      <c r="Y24" s="323"/>
+      <c r="Z24" s="326"/>
+      <c r="AA24" s="327"/>
+      <c r="AB24" s="330"/>
+      <c r="AC24" s="331"/>
+      <c r="AD24" s="318"/>
+      <c r="AE24" s="319"/>
+      <c r="AF24" s="322"/>
+      <c r="AG24" s="323"/>
+      <c r="AH24" s="326"/>
+      <c r="AI24" s="327"/>
+      <c r="AJ24" s="314"/>
+      <c r="AK24" s="315"/>
+      <c r="AL24" s="342"/>
+      <c r="AM24" s="343"/>
+      <c r="AP24" s="314"/>
+      <c r="AQ24" s="315"/>
+      <c r="AR24" s="318"/>
+      <c r="AS24" s="319"/>
+      <c r="AT24" s="322"/>
+      <c r="AU24" s="323"/>
+      <c r="AV24" s="326"/>
+      <c r="AW24" s="327"/>
+      <c r="AX24" s="314"/>
+      <c r="AY24" s="315"/>
+      <c r="AZ24" s="318"/>
+      <c r="BA24" s="319"/>
+      <c r="BB24" s="322"/>
+      <c r="BC24" s="323"/>
+      <c r="BD24" s="326"/>
+      <c r="BE24" s="327"/>
+      <c r="BF24" s="314"/>
+      <c r="BG24" s="315"/>
+      <c r="BH24" s="318"/>
+      <c r="BI24" s="319"/>
+      <c r="BJ24" s="322"/>
+      <c r="BK24" s="323"/>
+      <c r="BL24" s="326"/>
+      <c r="BM24" s="327"/>
       <c r="BR24" s="2"/>
     </row>
     <row r="25" spans="2:70" ht="33" customHeight="1">
-      <c r="B25" s="330" t="s">
+      <c r="B25" s="295" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="330"/>
-      <c r="D25" s="322"/>
-      <c r="E25" s="323"/>
-      <c r="F25" s="326"/>
-      <c r="G25" s="327"/>
-      <c r="H25" s="314"/>
-      <c r="I25" s="315"/>
-      <c r="J25" s="318"/>
-      <c r="K25" s="319"/>
-      <c r="L25" s="322" t="s">
+      <c r="C25" s="295"/>
+      <c r="D25" s="296"/>
+      <c r="E25" s="297"/>
+      <c r="F25" s="300"/>
+      <c r="G25" s="301"/>
+      <c r="H25" s="304"/>
+      <c r="I25" s="305"/>
+      <c r="J25" s="308"/>
+      <c r="K25" s="309"/>
+      <c r="L25" s="296" t="s">
         <v>89</v>
       </c>
-      <c r="M25" s="323"/>
-      <c r="N25" s="326" t="s">
+      <c r="M25" s="297"/>
+      <c r="N25" s="300" t="s">
         <v>90</v>
       </c>
-      <c r="O25" s="327"/>
-      <c r="P25" s="314"/>
-      <c r="Q25" s="315"/>
-      <c r="R25" s="318"/>
-      <c r="S25" s="319"/>
-      <c r="T25" s="322" t="s">
+      <c r="O25" s="301"/>
+      <c r="P25" s="304"/>
+      <c r="Q25" s="305"/>
+      <c r="R25" s="308"/>
+      <c r="S25" s="309"/>
+      <c r="T25" s="296" t="s">
         <v>89</v>
       </c>
-      <c r="U25" s="323"/>
-      <c r="V25" s="326" t="s">
+      <c r="U25" s="297"/>
+      <c r="V25" s="300" t="s">
         <v>91</v>
       </c>
-      <c r="W25" s="327"/>
-      <c r="X25" s="314"/>
-      <c r="Y25" s="315"/>
-      <c r="Z25" s="318"/>
-      <c r="AA25" s="319"/>
-      <c r="AB25" s="322"/>
-      <c r="AC25" s="323"/>
-      <c r="AD25" s="326"/>
-      <c r="AE25" s="327"/>
-      <c r="AF25" s="314"/>
-      <c r="AG25" s="315"/>
-      <c r="AH25" s="318"/>
-      <c r="AI25" s="319"/>
-      <c r="AJ25" s="322" t="s">
+      <c r="W25" s="301"/>
+      <c r="X25" s="304"/>
+      <c r="Y25" s="305"/>
+      <c r="Z25" s="308"/>
+      <c r="AA25" s="309"/>
+      <c r="AB25" s="296"/>
+      <c r="AC25" s="297"/>
+      <c r="AD25" s="300"/>
+      <c r="AE25" s="301"/>
+      <c r="AF25" s="304"/>
+      <c r="AG25" s="305"/>
+      <c r="AH25" s="308"/>
+      <c r="AI25" s="309"/>
+      <c r="AJ25" s="296" t="s">
         <v>80</v>
       </c>
-      <c r="AK25" s="323"/>
-      <c r="AL25" s="335" t="s">
+      <c r="AK25" s="297"/>
+      <c r="AL25" s="336" t="s">
         <v>81</v>
       </c>
-      <c r="AM25" s="336"/>
-      <c r="AP25" s="322" t="s">
+      <c r="AM25" s="337"/>
+      <c r="AP25" s="296" t="s">
         <v>62</v>
       </c>
-      <c r="AQ25" s="323"/>
-      <c r="AR25" s="326" t="s">
+      <c r="AQ25" s="297"/>
+      <c r="AR25" s="300" t="s">
         <v>66</v>
       </c>
-      <c r="AS25" s="327"/>
-      <c r="AT25" s="314"/>
-      <c r="AU25" s="315"/>
-      <c r="AV25" s="318"/>
-      <c r="AW25" s="319"/>
-      <c r="AX25" s="322" t="s">
+      <c r="AS25" s="301"/>
+      <c r="AT25" s="304"/>
+      <c r="AU25" s="305"/>
+      <c r="AV25" s="308"/>
+      <c r="AW25" s="309"/>
+      <c r="AX25" s="296" t="s">
         <v>77</v>
       </c>
-      <c r="AY25" s="323"/>
-      <c r="AZ25" s="326" t="s">
+      <c r="AY25" s="297"/>
+      <c r="AZ25" s="300" t="s">
         <v>79</v>
       </c>
-      <c r="BA25" s="327"/>
-      <c r="BB25" s="314"/>
-      <c r="BC25" s="315"/>
-      <c r="BD25" s="318"/>
-      <c r="BE25" s="319"/>
-      <c r="BF25" s="322"/>
-      <c r="BG25" s="323"/>
-      <c r="BH25" s="326"/>
-      <c r="BI25" s="327"/>
-      <c r="BJ25" s="314" t="s">
+      <c r="BA25" s="301"/>
+      <c r="BB25" s="304"/>
+      <c r="BC25" s="305"/>
+      <c r="BD25" s="308"/>
+      <c r="BE25" s="309"/>
+      <c r="BF25" s="296"/>
+      <c r="BG25" s="297"/>
+      <c r="BH25" s="300"/>
+      <c r="BI25" s="301"/>
+      <c r="BJ25" s="304" t="s">
         <v>89</v>
       </c>
-      <c r="BK25" s="315"/>
-      <c r="BL25" s="318" t="s">
+      <c r="BK25" s="305"/>
+      <c r="BL25" s="308" t="s">
         <v>91</v>
       </c>
-      <c r="BM25" s="319"/>
+      <c r="BM25" s="309"/>
       <c r="BR25" s="2"/>
     </row>
     <row r="26" spans="2:70" ht="33" customHeight="1">
-      <c r="B26" s="330"/>
-      <c r="C26" s="330"/>
-      <c r="D26" s="324"/>
-      <c r="E26" s="325"/>
-      <c r="F26" s="328"/>
-      <c r="G26" s="329"/>
-      <c r="H26" s="316"/>
-      <c r="I26" s="317"/>
-      <c r="J26" s="320"/>
-      <c r="K26" s="321"/>
-      <c r="L26" s="324"/>
-      <c r="M26" s="325"/>
-      <c r="N26" s="328"/>
-      <c r="O26" s="329"/>
-      <c r="P26" s="316"/>
-      <c r="Q26" s="317"/>
-      <c r="R26" s="320"/>
-      <c r="S26" s="321"/>
-      <c r="T26" s="324"/>
-      <c r="U26" s="325"/>
-      <c r="V26" s="328"/>
-      <c r="W26" s="329"/>
-      <c r="X26" s="316"/>
-      <c r="Y26" s="317"/>
-      <c r="Z26" s="320"/>
-      <c r="AA26" s="321"/>
-      <c r="AB26" s="324"/>
-      <c r="AC26" s="325"/>
-      <c r="AD26" s="328"/>
-      <c r="AE26" s="329"/>
-      <c r="AF26" s="316"/>
-      <c r="AG26" s="317"/>
-      <c r="AH26" s="320"/>
-      <c r="AI26" s="321"/>
-      <c r="AJ26" s="324"/>
-      <c r="AK26" s="325"/>
-      <c r="AL26" s="337"/>
-      <c r="AM26" s="338"/>
-      <c r="AP26" s="324"/>
-      <c r="AQ26" s="325"/>
-      <c r="AR26" s="328"/>
-      <c r="AS26" s="329"/>
-      <c r="AT26" s="316"/>
-      <c r="AU26" s="317"/>
-      <c r="AV26" s="320"/>
-      <c r="AW26" s="321"/>
-      <c r="AX26" s="324"/>
-      <c r="AY26" s="325"/>
-      <c r="AZ26" s="328"/>
-      <c r="BA26" s="329"/>
-      <c r="BB26" s="316"/>
-      <c r="BC26" s="317"/>
-      <c r="BD26" s="320"/>
-      <c r="BE26" s="321"/>
-      <c r="BF26" s="324"/>
-      <c r="BG26" s="325"/>
-      <c r="BH26" s="328"/>
-      <c r="BI26" s="329"/>
-      <c r="BJ26" s="316"/>
-      <c r="BK26" s="317"/>
-      <c r="BL26" s="320"/>
-      <c r="BM26" s="321"/>
+      <c r="B26" s="295"/>
+      <c r="C26" s="295"/>
+      <c r="D26" s="298"/>
+      <c r="E26" s="299"/>
+      <c r="F26" s="302"/>
+      <c r="G26" s="303"/>
+      <c r="H26" s="306"/>
+      <c r="I26" s="307"/>
+      <c r="J26" s="310"/>
+      <c r="K26" s="311"/>
+      <c r="L26" s="298"/>
+      <c r="M26" s="299"/>
+      <c r="N26" s="302"/>
+      <c r="O26" s="303"/>
+      <c r="P26" s="306"/>
+      <c r="Q26" s="307"/>
+      <c r="R26" s="310"/>
+      <c r="S26" s="311"/>
+      <c r="T26" s="298"/>
+      <c r="U26" s="299"/>
+      <c r="V26" s="302"/>
+      <c r="W26" s="303"/>
+      <c r="X26" s="306"/>
+      <c r="Y26" s="307"/>
+      <c r="Z26" s="310"/>
+      <c r="AA26" s="311"/>
+      <c r="AB26" s="298"/>
+      <c r="AC26" s="299"/>
+      <c r="AD26" s="302"/>
+      <c r="AE26" s="303"/>
+      <c r="AF26" s="306"/>
+      <c r="AG26" s="307"/>
+      <c r="AH26" s="310"/>
+      <c r="AI26" s="311"/>
+      <c r="AJ26" s="298"/>
+      <c r="AK26" s="299"/>
+      <c r="AL26" s="338"/>
+      <c r="AM26" s="339"/>
+      <c r="AP26" s="298"/>
+      <c r="AQ26" s="299"/>
+      <c r="AR26" s="302"/>
+      <c r="AS26" s="303"/>
+      <c r="AT26" s="306"/>
+      <c r="AU26" s="307"/>
+      <c r="AV26" s="310"/>
+      <c r="AW26" s="311"/>
+      <c r="AX26" s="298"/>
+      <c r="AY26" s="299"/>
+      <c r="AZ26" s="302"/>
+      <c r="BA26" s="303"/>
+      <c r="BB26" s="306"/>
+      <c r="BC26" s="307"/>
+      <c r="BD26" s="310"/>
+      <c r="BE26" s="311"/>
+      <c r="BF26" s="298"/>
+      <c r="BG26" s="299"/>
+      <c r="BH26" s="302"/>
+      <c r="BI26" s="303"/>
+      <c r="BJ26" s="306"/>
+      <c r="BK26" s="307"/>
+      <c r="BL26" s="310"/>
+      <c r="BM26" s="311"/>
       <c r="BR26" s="2"/>
     </row>
     <row r="27" spans="2:70" ht="33" customHeight="1">
-      <c r="B27" s="330"/>
-      <c r="C27" s="330"/>
-      <c r="D27" s="310"/>
-      <c r="E27" s="311"/>
-      <c r="F27" s="306"/>
-      <c r="G27" s="307"/>
-      <c r="H27" s="294"/>
-      <c r="I27" s="295"/>
-      <c r="J27" s="298"/>
-      <c r="K27" s="299"/>
-      <c r="L27" s="302" t="s">
+      <c r="B27" s="295"/>
+      <c r="C27" s="295"/>
+      <c r="D27" s="328"/>
+      <c r="E27" s="329"/>
+      <c r="F27" s="316"/>
+      <c r="G27" s="317"/>
+      <c r="H27" s="320"/>
+      <c r="I27" s="321"/>
+      <c r="J27" s="324"/>
+      <c r="K27" s="325"/>
+      <c r="L27" s="312" t="s">
         <v>92</v>
       </c>
-      <c r="M27" s="303"/>
-      <c r="N27" s="306" t="s">
+      <c r="M27" s="313"/>
+      <c r="N27" s="316" t="s">
         <v>93</v>
       </c>
-      <c r="O27" s="307"/>
-      <c r="P27" s="294"/>
-      <c r="Q27" s="295"/>
-      <c r="R27" s="298"/>
-      <c r="S27" s="299"/>
-      <c r="T27" s="302" t="s">
+      <c r="O27" s="317"/>
+      <c r="P27" s="320"/>
+      <c r="Q27" s="321"/>
+      <c r="R27" s="324"/>
+      <c r="S27" s="325"/>
+      <c r="T27" s="312" t="s">
         <v>94</v>
       </c>
-      <c r="U27" s="303"/>
-      <c r="V27" s="306" t="s">
+      <c r="U27" s="313"/>
+      <c r="V27" s="316" t="s">
         <v>91</v>
       </c>
-      <c r="W27" s="307"/>
-      <c r="X27" s="294"/>
-      <c r="Y27" s="295"/>
-      <c r="Z27" s="298"/>
-      <c r="AA27" s="299"/>
-      <c r="AB27" s="310"/>
-      <c r="AC27" s="311"/>
-      <c r="AD27" s="306"/>
-      <c r="AE27" s="307"/>
-      <c r="AF27" s="294"/>
-      <c r="AG27" s="295"/>
-      <c r="AH27" s="298"/>
-      <c r="AI27" s="299"/>
-      <c r="AJ27" s="302" t="s">
+      <c r="W27" s="317"/>
+      <c r="X27" s="320"/>
+      <c r="Y27" s="321"/>
+      <c r="Z27" s="324"/>
+      <c r="AA27" s="325"/>
+      <c r="AB27" s="328"/>
+      <c r="AC27" s="329"/>
+      <c r="AD27" s="316"/>
+      <c r="AE27" s="317"/>
+      <c r="AF27" s="320"/>
+      <c r="AG27" s="321"/>
+      <c r="AH27" s="324"/>
+      <c r="AI27" s="325"/>
+      <c r="AJ27" s="312" t="s">
         <v>86</v>
       </c>
-      <c r="AK27" s="303"/>
-      <c r="AL27" s="331" t="s">
+      <c r="AK27" s="313"/>
+      <c r="AL27" s="340" t="s">
         <v>81</v>
       </c>
-      <c r="AM27" s="332"/>
-      <c r="AP27" s="302" t="s">
+      <c r="AM27" s="341"/>
+      <c r="AP27" s="312" t="s">
         <v>73</v>
       </c>
-      <c r="AQ27" s="303"/>
-      <c r="AR27" s="306" t="s">
+      <c r="AQ27" s="313"/>
+      <c r="AR27" s="316" t="s">
         <v>74</v>
       </c>
-      <c r="AS27" s="307"/>
-      <c r="AT27" s="294"/>
-      <c r="AU27" s="295"/>
-      <c r="AV27" s="298"/>
-      <c r="AW27" s="299"/>
-      <c r="AX27" s="302" t="s">
+      <c r="AS27" s="317"/>
+      <c r="AT27" s="320"/>
+      <c r="AU27" s="321"/>
+      <c r="AV27" s="324"/>
+      <c r="AW27" s="325"/>
+      <c r="AX27" s="312" t="s">
         <v>84</v>
       </c>
-      <c r="AY27" s="303"/>
-      <c r="AZ27" s="306" t="s">
+      <c r="AY27" s="313"/>
+      <c r="AZ27" s="316" t="s">
         <v>85</v>
       </c>
-      <c r="BA27" s="307"/>
-      <c r="BB27" s="294"/>
-      <c r="BC27" s="295"/>
-      <c r="BD27" s="298"/>
-      <c r="BE27" s="299"/>
-      <c r="BF27" s="302"/>
-      <c r="BG27" s="303"/>
-      <c r="BH27" s="306"/>
-      <c r="BI27" s="307"/>
-      <c r="BJ27" s="294" t="s">
+      <c r="BA27" s="317"/>
+      <c r="BB27" s="320"/>
+      <c r="BC27" s="321"/>
+      <c r="BD27" s="324"/>
+      <c r="BE27" s="325"/>
+      <c r="BF27" s="312"/>
+      <c r="BG27" s="313"/>
+      <c r="BH27" s="316"/>
+      <c r="BI27" s="317"/>
+      <c r="BJ27" s="320" t="s">
         <v>94</v>
       </c>
-      <c r="BK27" s="295"/>
-      <c r="BL27" s="298" t="s">
+      <c r="BK27" s="321"/>
+      <c r="BL27" s="324" t="s">
         <v>98</v>
       </c>
-      <c r="BM27" s="299"/>
+      <c r="BM27" s="325"/>
       <c r="BR27" s="2"/>
     </row>
     <row r="28" spans="2:70" ht="33" customHeight="1">
-      <c r="B28" s="330"/>
-      <c r="C28" s="330"/>
-      <c r="D28" s="312"/>
-      <c r="E28" s="313"/>
-      <c r="F28" s="308"/>
-      <c r="G28" s="309"/>
-      <c r="H28" s="296"/>
-      <c r="I28" s="297"/>
-      <c r="J28" s="300"/>
-      <c r="K28" s="301"/>
-      <c r="L28" s="304"/>
-      <c r="M28" s="305"/>
-      <c r="N28" s="308"/>
-      <c r="O28" s="309"/>
-      <c r="P28" s="296"/>
-      <c r="Q28" s="297"/>
-      <c r="R28" s="300"/>
-      <c r="S28" s="301"/>
-      <c r="T28" s="304"/>
-      <c r="U28" s="305"/>
-      <c r="V28" s="308"/>
-      <c r="W28" s="309"/>
-      <c r="X28" s="296"/>
-      <c r="Y28" s="297"/>
-      <c r="Z28" s="300"/>
-      <c r="AA28" s="301"/>
-      <c r="AB28" s="312"/>
-      <c r="AC28" s="313"/>
-      <c r="AD28" s="308"/>
-      <c r="AE28" s="309"/>
-      <c r="AF28" s="296"/>
-      <c r="AG28" s="297"/>
-      <c r="AH28" s="300"/>
-      <c r="AI28" s="301"/>
-      <c r="AJ28" s="304"/>
-      <c r="AK28" s="305"/>
-      <c r="AL28" s="333"/>
-      <c r="AM28" s="334"/>
-      <c r="AP28" s="304"/>
-      <c r="AQ28" s="305"/>
-      <c r="AR28" s="308"/>
-      <c r="AS28" s="309"/>
-      <c r="AT28" s="296"/>
-      <c r="AU28" s="297"/>
-      <c r="AV28" s="300"/>
-      <c r="AW28" s="301"/>
-      <c r="AX28" s="304"/>
-      <c r="AY28" s="305"/>
-      <c r="AZ28" s="308"/>
-      <c r="BA28" s="309"/>
-      <c r="BB28" s="296"/>
-      <c r="BC28" s="297"/>
-      <c r="BD28" s="300"/>
-      <c r="BE28" s="301"/>
-      <c r="BF28" s="304"/>
-      <c r="BG28" s="305"/>
-      <c r="BH28" s="308"/>
-      <c r="BI28" s="309"/>
-      <c r="BJ28" s="296"/>
-      <c r="BK28" s="297"/>
-      <c r="BL28" s="300"/>
-      <c r="BM28" s="301"/>
+      <c r="B28" s="295"/>
+      <c r="C28" s="295"/>
+      <c r="D28" s="330"/>
+      <c r="E28" s="331"/>
+      <c r="F28" s="318"/>
+      <c r="G28" s="319"/>
+      <c r="H28" s="322"/>
+      <c r="I28" s="323"/>
+      <c r="J28" s="326"/>
+      <c r="K28" s="327"/>
+      <c r="L28" s="314"/>
+      <c r="M28" s="315"/>
+      <c r="N28" s="318"/>
+      <c r="O28" s="319"/>
+      <c r="P28" s="322"/>
+      <c r="Q28" s="323"/>
+      <c r="R28" s="326"/>
+      <c r="S28" s="327"/>
+      <c r="T28" s="314"/>
+      <c r="U28" s="315"/>
+      <c r="V28" s="318"/>
+      <c r="W28" s="319"/>
+      <c r="X28" s="322"/>
+      <c r="Y28" s="323"/>
+      <c r="Z28" s="326"/>
+      <c r="AA28" s="327"/>
+      <c r="AB28" s="330"/>
+      <c r="AC28" s="331"/>
+      <c r="AD28" s="318"/>
+      <c r="AE28" s="319"/>
+      <c r="AF28" s="322"/>
+      <c r="AG28" s="323"/>
+      <c r="AH28" s="326"/>
+      <c r="AI28" s="327"/>
+      <c r="AJ28" s="314"/>
+      <c r="AK28" s="315"/>
+      <c r="AL28" s="342"/>
+      <c r="AM28" s="343"/>
+      <c r="AP28" s="314"/>
+      <c r="AQ28" s="315"/>
+      <c r="AR28" s="318"/>
+      <c r="AS28" s="319"/>
+      <c r="AT28" s="322"/>
+      <c r="AU28" s="323"/>
+      <c r="AV28" s="326"/>
+      <c r="AW28" s="327"/>
+      <c r="AX28" s="314"/>
+      <c r="AY28" s="315"/>
+      <c r="AZ28" s="318"/>
+      <c r="BA28" s="319"/>
+      <c r="BB28" s="322"/>
+      <c r="BC28" s="323"/>
+      <c r="BD28" s="326"/>
+      <c r="BE28" s="327"/>
+      <c r="BF28" s="314"/>
+      <c r="BG28" s="315"/>
+      <c r="BH28" s="318"/>
+      <c r="BI28" s="319"/>
+      <c r="BJ28" s="322"/>
+      <c r="BK28" s="323"/>
+      <c r="BL28" s="326"/>
+      <c r="BM28" s="327"/>
       <c r="BR28" s="2"/>
     </row>
     <row r="29" spans="2:70" ht="33" customHeight="1">
-      <c r="B29" s="330" t="s">
+      <c r="B29" s="295" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="330"/>
-      <c r="D29" s="322"/>
-      <c r="E29" s="323"/>
-      <c r="F29" s="326"/>
-      <c r="G29" s="327"/>
-      <c r="H29" s="314"/>
-      <c r="I29" s="315"/>
-      <c r="J29" s="318"/>
-      <c r="K29" s="319"/>
-      <c r="L29" s="322"/>
-      <c r="M29" s="323"/>
-      <c r="N29" s="326"/>
-      <c r="O29" s="327"/>
-      <c r="P29" s="314"/>
-      <c r="Q29" s="315"/>
-      <c r="R29" s="318"/>
-      <c r="S29" s="319"/>
-      <c r="T29" s="322"/>
-      <c r="U29" s="323"/>
-      <c r="V29" s="326"/>
-      <c r="W29" s="327"/>
-      <c r="X29" s="314" t="s">
+      <c r="C29" s="295"/>
+      <c r="D29" s="296"/>
+      <c r="E29" s="297"/>
+      <c r="F29" s="300"/>
+      <c r="G29" s="301"/>
+      <c r="H29" s="304"/>
+      <c r="I29" s="305"/>
+      <c r="J29" s="308"/>
+      <c r="K29" s="309"/>
+      <c r="L29" s="296"/>
+      <c r="M29" s="297"/>
+      <c r="N29" s="300"/>
+      <c r="O29" s="301"/>
+      <c r="P29" s="304"/>
+      <c r="Q29" s="305"/>
+      <c r="R29" s="308"/>
+      <c r="S29" s="309"/>
+      <c r="T29" s="296"/>
+      <c r="U29" s="297"/>
+      <c r="V29" s="300"/>
+      <c r="W29" s="301"/>
+      <c r="X29" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="Y29" s="315"/>
-      <c r="Z29" s="318" t="s">
+      <c r="Y29" s="305"/>
+      <c r="Z29" s="308" t="s">
         <v>96</v>
       </c>
-      <c r="AA29" s="319"/>
-      <c r="AB29" s="322"/>
-      <c r="AC29" s="323"/>
-      <c r="AD29" s="326"/>
-      <c r="AE29" s="327"/>
-      <c r="AF29" s="314"/>
-      <c r="AG29" s="315"/>
-      <c r="AH29" s="318"/>
-      <c r="AI29" s="319"/>
-      <c r="AJ29" s="322"/>
-      <c r="AK29" s="323"/>
-      <c r="AL29" s="326"/>
-      <c r="AM29" s="327"/>
+      <c r="AA29" s="309"/>
+      <c r="AB29" s="296"/>
+      <c r="AC29" s="297"/>
+      <c r="AD29" s="300"/>
+      <c r="AE29" s="301"/>
+      <c r="AF29" s="304"/>
+      <c r="AG29" s="305"/>
+      <c r="AH29" s="308"/>
+      <c r="AI29" s="309"/>
+      <c r="AJ29" s="296"/>
+      <c r="AK29" s="297"/>
+      <c r="AL29" s="300"/>
+      <c r="AM29" s="301"/>
       <c r="BR29" s="2"/>
     </row>
     <row r="30" spans="2:70" ht="33" customHeight="1">
-      <c r="B30" s="330"/>
-      <c r="C30" s="330"/>
-      <c r="D30" s="324"/>
-      <c r="E30" s="325"/>
-      <c r="F30" s="328"/>
-      <c r="G30" s="329"/>
-      <c r="H30" s="316"/>
-      <c r="I30" s="317"/>
-      <c r="J30" s="320"/>
-      <c r="K30" s="321"/>
-      <c r="L30" s="324"/>
-      <c r="M30" s="325"/>
-      <c r="N30" s="328"/>
-      <c r="O30" s="329"/>
-      <c r="P30" s="316"/>
-      <c r="Q30" s="317"/>
-      <c r="R30" s="320"/>
-      <c r="S30" s="321"/>
-      <c r="T30" s="324"/>
-      <c r="U30" s="325"/>
-      <c r="V30" s="328"/>
-      <c r="W30" s="329"/>
-      <c r="X30" s="316"/>
-      <c r="Y30" s="317"/>
-      <c r="Z30" s="320"/>
-      <c r="AA30" s="321"/>
-      <c r="AB30" s="324"/>
-      <c r="AC30" s="325"/>
-      <c r="AD30" s="328"/>
-      <c r="AE30" s="329"/>
-      <c r="AF30" s="316"/>
-      <c r="AG30" s="317"/>
-      <c r="AH30" s="320"/>
-      <c r="AI30" s="321"/>
-      <c r="AJ30" s="324"/>
-      <c r="AK30" s="325"/>
-      <c r="AL30" s="328"/>
-      <c r="AM30" s="329"/>
+      <c r="B30" s="295"/>
+      <c r="C30" s="295"/>
+      <c r="D30" s="298"/>
+      <c r="E30" s="299"/>
+      <c r="F30" s="302"/>
+      <c r="G30" s="303"/>
+      <c r="H30" s="306"/>
+      <c r="I30" s="307"/>
+      <c r="J30" s="310"/>
+      <c r="K30" s="311"/>
+      <c r="L30" s="298"/>
+      <c r="M30" s="299"/>
+      <c r="N30" s="302"/>
+      <c r="O30" s="303"/>
+      <c r="P30" s="306"/>
+      <c r="Q30" s="307"/>
+      <c r="R30" s="310"/>
+      <c r="S30" s="311"/>
+      <c r="T30" s="298"/>
+      <c r="U30" s="299"/>
+      <c r="V30" s="302"/>
+      <c r="W30" s="303"/>
+      <c r="X30" s="306"/>
+      <c r="Y30" s="307"/>
+      <c r="Z30" s="310"/>
+      <c r="AA30" s="311"/>
+      <c r="AB30" s="298"/>
+      <c r="AC30" s="299"/>
+      <c r="AD30" s="302"/>
+      <c r="AE30" s="303"/>
+      <c r="AF30" s="306"/>
+      <c r="AG30" s="307"/>
+      <c r="AH30" s="310"/>
+      <c r="AI30" s="311"/>
+      <c r="AJ30" s="298"/>
+      <c r="AK30" s="299"/>
+      <c r="AL30" s="302"/>
+      <c r="AM30" s="303"/>
       <c r="BR30" s="2"/>
     </row>
     <row r="31" spans="2:70" ht="33" customHeight="1">
-      <c r="B31" s="330"/>
-      <c r="C31" s="330"/>
-      <c r="D31" s="310"/>
-      <c r="E31" s="311"/>
-      <c r="F31" s="306"/>
-      <c r="G31" s="307"/>
-      <c r="H31" s="294"/>
-      <c r="I31" s="295"/>
-      <c r="J31" s="298"/>
-      <c r="K31" s="299"/>
-      <c r="L31" s="310"/>
-      <c r="M31" s="311"/>
-      <c r="N31" s="306"/>
-      <c r="O31" s="307"/>
-      <c r="P31" s="294"/>
-      <c r="Q31" s="295"/>
-      <c r="R31" s="298"/>
-      <c r="S31" s="299"/>
-      <c r="T31" s="310"/>
-      <c r="U31" s="311"/>
-      <c r="V31" s="306"/>
-      <c r="W31" s="307"/>
-      <c r="X31" s="294" t="s">
+      <c r="B31" s="295"/>
+      <c r="C31" s="295"/>
+      <c r="D31" s="328"/>
+      <c r="E31" s="329"/>
+      <c r="F31" s="316"/>
+      <c r="G31" s="317"/>
+      <c r="H31" s="320"/>
+      <c r="I31" s="321"/>
+      <c r="J31" s="324"/>
+      <c r="K31" s="325"/>
+      <c r="L31" s="328"/>
+      <c r="M31" s="329"/>
+      <c r="N31" s="316"/>
+      <c r="O31" s="317"/>
+      <c r="P31" s="320"/>
+      <c r="Q31" s="321"/>
+      <c r="R31" s="324"/>
+      <c r="S31" s="325"/>
+      <c r="T31" s="328"/>
+      <c r="U31" s="329"/>
+      <c r="V31" s="316"/>
+      <c r="W31" s="317"/>
+      <c r="X31" s="320" t="s">
         <v>60</v>
       </c>
-      <c r="Y31" s="295"/>
-      <c r="Z31" s="298" t="s">
+      <c r="Y31" s="321"/>
+      <c r="Z31" s="324" t="s">
         <v>97</v>
       </c>
-      <c r="AA31" s="299"/>
-      <c r="AB31" s="310"/>
-      <c r="AC31" s="311"/>
-      <c r="AD31" s="306"/>
-      <c r="AE31" s="307"/>
-      <c r="AF31" s="294"/>
-      <c r="AG31" s="295"/>
-      <c r="AH31" s="298"/>
-      <c r="AI31" s="299"/>
-      <c r="AJ31" s="310"/>
-      <c r="AK31" s="311"/>
-      <c r="AL31" s="306"/>
-      <c r="AM31" s="307"/>
+      <c r="AA31" s="325"/>
+      <c r="AB31" s="328"/>
+      <c r="AC31" s="329"/>
+      <c r="AD31" s="316"/>
+      <c r="AE31" s="317"/>
+      <c r="AF31" s="320"/>
+      <c r="AG31" s="321"/>
+      <c r="AH31" s="324"/>
+      <c r="AI31" s="325"/>
+      <c r="AJ31" s="328"/>
+      <c r="AK31" s="329"/>
+      <c r="AL31" s="316"/>
+      <c r="AM31" s="317"/>
       <c r="BR31" s="2"/>
     </row>
     <row r="32" spans="2:70" ht="33" customHeight="1">
-      <c r="B32" s="330"/>
-      <c r="C32" s="330"/>
-      <c r="D32" s="312"/>
-      <c r="E32" s="313"/>
-      <c r="F32" s="308"/>
-      <c r="G32" s="309"/>
-      <c r="H32" s="296"/>
-      <c r="I32" s="297"/>
-      <c r="J32" s="300"/>
-      <c r="K32" s="301"/>
-      <c r="L32" s="312"/>
-      <c r="M32" s="313"/>
-      <c r="N32" s="308"/>
-      <c r="O32" s="309"/>
-      <c r="P32" s="296"/>
-      <c r="Q32" s="297"/>
-      <c r="R32" s="300"/>
-      <c r="S32" s="301"/>
-      <c r="T32" s="312"/>
-      <c r="U32" s="313"/>
-      <c r="V32" s="308"/>
-      <c r="W32" s="309"/>
-      <c r="X32" s="296"/>
-      <c r="Y32" s="297"/>
-      <c r="Z32" s="300"/>
-      <c r="AA32" s="301"/>
-      <c r="AB32" s="312"/>
-      <c r="AC32" s="313"/>
-      <c r="AD32" s="308"/>
-      <c r="AE32" s="309"/>
-      <c r="AF32" s="296"/>
-      <c r="AG32" s="297"/>
-      <c r="AH32" s="300"/>
-      <c r="AI32" s="301"/>
-      <c r="AJ32" s="312"/>
-      <c r="AK32" s="313"/>
-      <c r="AL32" s="308"/>
-      <c r="AM32" s="309"/>
+      <c r="B32" s="295"/>
+      <c r="C32" s="295"/>
+      <c r="D32" s="330"/>
+      <c r="E32" s="331"/>
+      <c r="F32" s="318"/>
+      <c r="G32" s="319"/>
+      <c r="H32" s="322"/>
+      <c r="I32" s="323"/>
+      <c r="J32" s="326"/>
+      <c r="K32" s="327"/>
+      <c r="L32" s="330"/>
+      <c r="M32" s="331"/>
+      <c r="N32" s="318"/>
+      <c r="O32" s="319"/>
+      <c r="P32" s="322"/>
+      <c r="Q32" s="323"/>
+      <c r="R32" s="326"/>
+      <c r="S32" s="327"/>
+      <c r="T32" s="330"/>
+      <c r="U32" s="331"/>
+      <c r="V32" s="318"/>
+      <c r="W32" s="319"/>
+      <c r="X32" s="322"/>
+      <c r="Y32" s="323"/>
+      <c r="Z32" s="326"/>
+      <c r="AA32" s="327"/>
+      <c r="AB32" s="330"/>
+      <c r="AC32" s="331"/>
+      <c r="AD32" s="318"/>
+      <c r="AE32" s="319"/>
+      <c r="AF32" s="322"/>
+      <c r="AG32" s="323"/>
+      <c r="AH32" s="326"/>
+      <c r="AI32" s="327"/>
+      <c r="AJ32" s="330"/>
+      <c r="AK32" s="331"/>
+      <c r="AL32" s="318"/>
+      <c r="AM32" s="319"/>
       <c r="BR32" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="430">
-    <mergeCell ref="D2:K2"/>
-    <mergeCell ref="L2:S2"/>
-    <mergeCell ref="T2:AA2"/>
-    <mergeCell ref="AB2:AI2"/>
-    <mergeCell ref="AJ2:AM2"/>
-    <mergeCell ref="D3:K3"/>
-    <mergeCell ref="L3:S3"/>
-    <mergeCell ref="T3:AA3"/>
-    <mergeCell ref="AB3:AI3"/>
-    <mergeCell ref="AJ3:AM3"/>
-    <mergeCell ref="AF4:AI4"/>
-    <mergeCell ref="AJ4:AM4"/>
-    <mergeCell ref="B5:C8"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:G6"/>
-    <mergeCell ref="H5:I6"/>
-    <mergeCell ref="J5:K6"/>
-    <mergeCell ref="L5:M6"/>
-    <mergeCell ref="N5:O6"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="P4:S4"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="X4:AA4"/>
-    <mergeCell ref="AH5:AI6"/>
-    <mergeCell ref="AJ5:AK6"/>
-    <mergeCell ref="AL5:AM6"/>
-    <mergeCell ref="P5:Q6"/>
-    <mergeCell ref="R5:S6"/>
-    <mergeCell ref="T5:U6"/>
-    <mergeCell ref="V5:W6"/>
-    <mergeCell ref="X5:Y6"/>
-    <mergeCell ref="L9:M10"/>
-    <mergeCell ref="N9:O10"/>
-    <mergeCell ref="P9:Q10"/>
-    <mergeCell ref="R9:S10"/>
-    <mergeCell ref="T9:U10"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="Z5:AA6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="H7:I8"/>
-    <mergeCell ref="J7:K8"/>
-    <mergeCell ref="L7:M8"/>
-    <mergeCell ref="N7:O8"/>
+    <mergeCell ref="BB27:BC28"/>
+    <mergeCell ref="BD27:BE28"/>
+    <mergeCell ref="BF27:BG28"/>
+    <mergeCell ref="BH27:BI28"/>
+    <mergeCell ref="BJ27:BK28"/>
+    <mergeCell ref="BL27:BM28"/>
+    <mergeCell ref="AP27:AQ28"/>
+    <mergeCell ref="AR27:AS28"/>
+    <mergeCell ref="AT27:AU28"/>
+    <mergeCell ref="AV27:AW28"/>
+    <mergeCell ref="AX27:AY28"/>
+    <mergeCell ref="AZ27:BA28"/>
+    <mergeCell ref="AH31:AI32"/>
+    <mergeCell ref="AJ31:AK32"/>
+    <mergeCell ref="AL31:AM32"/>
+    <mergeCell ref="P31:Q32"/>
+    <mergeCell ref="R31:S32"/>
+    <mergeCell ref="T31:U32"/>
+    <mergeCell ref="V31:W32"/>
+    <mergeCell ref="X31:Y32"/>
+    <mergeCell ref="Z31:AA32"/>
+    <mergeCell ref="D31:E32"/>
+    <mergeCell ref="F31:G32"/>
+    <mergeCell ref="H31:I32"/>
+    <mergeCell ref="J31:K32"/>
+    <mergeCell ref="L31:M32"/>
+    <mergeCell ref="N31:O32"/>
+    <mergeCell ref="BB25:BC26"/>
+    <mergeCell ref="BD25:BE26"/>
+    <mergeCell ref="BF25:BG26"/>
+    <mergeCell ref="AB29:AC30"/>
+    <mergeCell ref="AD29:AE30"/>
+    <mergeCell ref="AF29:AG30"/>
+    <mergeCell ref="AH29:AI30"/>
+    <mergeCell ref="AJ29:AK30"/>
+    <mergeCell ref="AL29:AM30"/>
+    <mergeCell ref="P29:Q30"/>
+    <mergeCell ref="R29:S30"/>
+    <mergeCell ref="T29:U30"/>
+    <mergeCell ref="V29:W30"/>
+    <mergeCell ref="X29:Y30"/>
+    <mergeCell ref="Z29:AA30"/>
+    <mergeCell ref="AB31:AC32"/>
+    <mergeCell ref="AD31:AE32"/>
+    <mergeCell ref="AF31:AG32"/>
+    <mergeCell ref="BH25:BI26"/>
+    <mergeCell ref="BJ25:BK26"/>
+    <mergeCell ref="BL25:BM26"/>
+    <mergeCell ref="AP25:AQ26"/>
+    <mergeCell ref="AR25:AS26"/>
+    <mergeCell ref="AT25:AU26"/>
+    <mergeCell ref="AV25:AW26"/>
+    <mergeCell ref="AX25:AY26"/>
+    <mergeCell ref="AZ25:BA26"/>
+    <mergeCell ref="BH23:BI24"/>
+    <mergeCell ref="BJ23:BK24"/>
+    <mergeCell ref="BL23:BM24"/>
+    <mergeCell ref="B29:C32"/>
+    <mergeCell ref="D29:E30"/>
+    <mergeCell ref="F29:G30"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="J29:K30"/>
+    <mergeCell ref="L29:M30"/>
+    <mergeCell ref="N29:O30"/>
+    <mergeCell ref="AV23:AW24"/>
+    <mergeCell ref="AX23:AY24"/>
+    <mergeCell ref="AZ23:BA24"/>
+    <mergeCell ref="BB23:BC24"/>
+    <mergeCell ref="BD23:BE24"/>
+    <mergeCell ref="BF23:BG24"/>
+    <mergeCell ref="AH27:AI28"/>
+    <mergeCell ref="AJ27:AK28"/>
+    <mergeCell ref="AL27:AM28"/>
+    <mergeCell ref="AP23:AQ24"/>
+    <mergeCell ref="AR23:AS24"/>
+    <mergeCell ref="AT23:AU24"/>
+    <mergeCell ref="V27:W28"/>
+    <mergeCell ref="X27:Y28"/>
+    <mergeCell ref="Z27:AA28"/>
+    <mergeCell ref="AB27:AC28"/>
+    <mergeCell ref="AD27:AE28"/>
+    <mergeCell ref="AF27:AG28"/>
+    <mergeCell ref="BL21:BM22"/>
+    <mergeCell ref="D27:E28"/>
+    <mergeCell ref="F27:G28"/>
+    <mergeCell ref="H27:I28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="L27:M28"/>
+    <mergeCell ref="N27:O28"/>
+    <mergeCell ref="P27:Q28"/>
+    <mergeCell ref="R27:S28"/>
+    <mergeCell ref="T27:U28"/>
+    <mergeCell ref="AZ21:BA22"/>
+    <mergeCell ref="BB21:BC22"/>
+    <mergeCell ref="BD21:BE22"/>
+    <mergeCell ref="BF21:BG22"/>
+    <mergeCell ref="BH21:BI22"/>
+    <mergeCell ref="BJ21:BK22"/>
+    <mergeCell ref="AL25:AM26"/>
+    <mergeCell ref="AP21:AQ22"/>
+    <mergeCell ref="AR21:AS22"/>
+    <mergeCell ref="AT21:AU22"/>
+    <mergeCell ref="AV21:AW22"/>
+    <mergeCell ref="AX21:AY22"/>
+    <mergeCell ref="Z25:AA26"/>
+    <mergeCell ref="AB25:AC26"/>
+    <mergeCell ref="AD25:AE26"/>
+    <mergeCell ref="AF25:AG26"/>
+    <mergeCell ref="AH25:AI26"/>
+    <mergeCell ref="AJ25:AK26"/>
+    <mergeCell ref="N25:O26"/>
+    <mergeCell ref="P25:Q26"/>
+    <mergeCell ref="R25:S26"/>
+    <mergeCell ref="T25:U26"/>
+    <mergeCell ref="V25:W26"/>
+    <mergeCell ref="X25:Y26"/>
+    <mergeCell ref="V21:W22"/>
+    <mergeCell ref="X21:Y22"/>
+    <mergeCell ref="Z21:AA22"/>
+    <mergeCell ref="B25:C28"/>
+    <mergeCell ref="D25:E26"/>
+    <mergeCell ref="F25:G26"/>
+    <mergeCell ref="H25:I26"/>
+    <mergeCell ref="J25:K26"/>
+    <mergeCell ref="L25:M26"/>
+    <mergeCell ref="BB19:BC20"/>
+    <mergeCell ref="BD19:BE20"/>
+    <mergeCell ref="BF19:BG20"/>
+    <mergeCell ref="AB23:AC24"/>
+    <mergeCell ref="AD23:AE24"/>
+    <mergeCell ref="AF23:AG24"/>
+    <mergeCell ref="AH23:AI24"/>
+    <mergeCell ref="AJ23:AK24"/>
+    <mergeCell ref="AL23:AM24"/>
+    <mergeCell ref="P23:Q24"/>
+    <mergeCell ref="R23:S24"/>
+    <mergeCell ref="T23:U24"/>
+    <mergeCell ref="V23:W24"/>
+    <mergeCell ref="X23:Y24"/>
+    <mergeCell ref="Z23:AA24"/>
+    <mergeCell ref="D23:E24"/>
+    <mergeCell ref="F23:G24"/>
+    <mergeCell ref="H23:I24"/>
+    <mergeCell ref="BH19:BI20"/>
+    <mergeCell ref="BJ19:BK20"/>
+    <mergeCell ref="BL19:BM20"/>
+    <mergeCell ref="AP19:AQ20"/>
+    <mergeCell ref="AR19:AS20"/>
+    <mergeCell ref="AT19:AU20"/>
+    <mergeCell ref="AV19:AW20"/>
+    <mergeCell ref="AX19:AY20"/>
+    <mergeCell ref="AZ19:BA20"/>
+    <mergeCell ref="J23:K24"/>
+    <mergeCell ref="L23:M24"/>
+    <mergeCell ref="N23:O24"/>
+    <mergeCell ref="BB17:BC18"/>
+    <mergeCell ref="BD17:BE18"/>
+    <mergeCell ref="BF17:BG18"/>
+    <mergeCell ref="BH17:BI18"/>
+    <mergeCell ref="BJ17:BK18"/>
+    <mergeCell ref="BL17:BM18"/>
+    <mergeCell ref="AP17:AQ18"/>
+    <mergeCell ref="AR17:AS18"/>
+    <mergeCell ref="AT17:AU18"/>
+    <mergeCell ref="AV17:AW18"/>
+    <mergeCell ref="AX17:AY18"/>
+    <mergeCell ref="AZ17:BA18"/>
+    <mergeCell ref="AB21:AC22"/>
+    <mergeCell ref="AD21:AE22"/>
+    <mergeCell ref="AF21:AG22"/>
+    <mergeCell ref="AH21:AI22"/>
+    <mergeCell ref="AJ21:AK22"/>
+    <mergeCell ref="AL21:AM22"/>
+    <mergeCell ref="P21:Q22"/>
+    <mergeCell ref="R21:S22"/>
+    <mergeCell ref="T21:U22"/>
+    <mergeCell ref="BH15:BI16"/>
+    <mergeCell ref="BJ15:BK16"/>
+    <mergeCell ref="BL15:BM16"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="D21:E22"/>
+    <mergeCell ref="F21:G22"/>
+    <mergeCell ref="H21:I22"/>
+    <mergeCell ref="J21:K22"/>
+    <mergeCell ref="L21:M22"/>
+    <mergeCell ref="N21:O22"/>
+    <mergeCell ref="AV15:AW16"/>
+    <mergeCell ref="AX15:AY16"/>
+    <mergeCell ref="AZ15:BA16"/>
+    <mergeCell ref="BB15:BC16"/>
+    <mergeCell ref="BD15:BE16"/>
+    <mergeCell ref="BF15:BG16"/>
+    <mergeCell ref="AH19:AI20"/>
+    <mergeCell ref="AJ19:AK20"/>
+    <mergeCell ref="AL19:AM20"/>
+    <mergeCell ref="AP15:AQ16"/>
+    <mergeCell ref="AR15:AS16"/>
+    <mergeCell ref="AT15:AU16"/>
+    <mergeCell ref="V19:W20"/>
+    <mergeCell ref="X19:Y20"/>
+    <mergeCell ref="Z19:AA20"/>
+    <mergeCell ref="AB19:AC20"/>
+    <mergeCell ref="AD19:AE20"/>
+    <mergeCell ref="AF19:AG20"/>
+    <mergeCell ref="BL13:BM14"/>
+    <mergeCell ref="D19:E20"/>
+    <mergeCell ref="F19:G20"/>
+    <mergeCell ref="H19:I20"/>
+    <mergeCell ref="J19:K20"/>
+    <mergeCell ref="L19:M20"/>
+    <mergeCell ref="N19:O20"/>
+    <mergeCell ref="P19:Q20"/>
+    <mergeCell ref="R19:S20"/>
+    <mergeCell ref="T19:U20"/>
+    <mergeCell ref="AZ13:BA14"/>
+    <mergeCell ref="BB13:BC14"/>
+    <mergeCell ref="BD13:BE14"/>
+    <mergeCell ref="BF13:BG14"/>
+    <mergeCell ref="BH13:BI14"/>
+    <mergeCell ref="BJ13:BK14"/>
+    <mergeCell ref="AL17:AM18"/>
+    <mergeCell ref="N17:O18"/>
+    <mergeCell ref="P17:Q18"/>
+    <mergeCell ref="R17:S18"/>
+    <mergeCell ref="T17:U18"/>
+    <mergeCell ref="V17:W18"/>
+    <mergeCell ref="X17:Y18"/>
+    <mergeCell ref="BH11:BI12"/>
+    <mergeCell ref="BJ11:BK12"/>
+    <mergeCell ref="BL11:BM12"/>
+    <mergeCell ref="AZ11:BA12"/>
+    <mergeCell ref="BB11:BC12"/>
+    <mergeCell ref="BD11:BE12"/>
+    <mergeCell ref="BF11:BG12"/>
+    <mergeCell ref="AP13:AQ14"/>
+    <mergeCell ref="AR13:AS14"/>
+    <mergeCell ref="AT13:AU14"/>
+    <mergeCell ref="AV13:AW14"/>
+    <mergeCell ref="AX13:AY14"/>
+    <mergeCell ref="Z17:AA18"/>
+    <mergeCell ref="AB17:AC18"/>
+    <mergeCell ref="AD17:AE18"/>
+    <mergeCell ref="AF17:AG18"/>
+    <mergeCell ref="AH17:AI18"/>
+    <mergeCell ref="AJ17:AK18"/>
+    <mergeCell ref="AD13:AE14"/>
+    <mergeCell ref="AF13:AG14"/>
+    <mergeCell ref="AH13:AI14"/>
+    <mergeCell ref="B17:B24"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="D17:E18"/>
+    <mergeCell ref="F17:G18"/>
+    <mergeCell ref="H17:I18"/>
+    <mergeCell ref="J17:K18"/>
+    <mergeCell ref="L17:M18"/>
+    <mergeCell ref="AV11:AW12"/>
+    <mergeCell ref="AX11:AY12"/>
+    <mergeCell ref="AH15:AI16"/>
+    <mergeCell ref="AJ15:AK16"/>
+    <mergeCell ref="AL15:AM16"/>
+    <mergeCell ref="AP11:AQ12"/>
+    <mergeCell ref="AR11:AS12"/>
+    <mergeCell ref="AT11:AU12"/>
+    <mergeCell ref="V15:W16"/>
+    <mergeCell ref="X15:Y16"/>
+    <mergeCell ref="Z15:AA16"/>
+    <mergeCell ref="AB15:AC16"/>
+    <mergeCell ref="AD15:AE16"/>
+    <mergeCell ref="AF15:AG16"/>
+    <mergeCell ref="B9:B16"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="BL9:BM10"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="F15:G16"/>
+    <mergeCell ref="H15:I16"/>
+    <mergeCell ref="J15:K16"/>
+    <mergeCell ref="L15:M16"/>
+    <mergeCell ref="N15:O16"/>
+    <mergeCell ref="P15:Q16"/>
+    <mergeCell ref="R15:S16"/>
+    <mergeCell ref="T15:U16"/>
+    <mergeCell ref="AZ9:BA10"/>
+    <mergeCell ref="BB9:BC10"/>
+    <mergeCell ref="BD9:BE10"/>
+    <mergeCell ref="BF9:BG10"/>
+    <mergeCell ref="BH9:BI10"/>
+    <mergeCell ref="BJ9:BK10"/>
+    <mergeCell ref="AL13:AM14"/>
+    <mergeCell ref="AP9:AQ10"/>
+    <mergeCell ref="AR9:AS10"/>
+    <mergeCell ref="AT9:AU10"/>
+    <mergeCell ref="AV9:AW10"/>
+    <mergeCell ref="AX9:AY10"/>
+    <mergeCell ref="Z13:AA14"/>
+    <mergeCell ref="AB13:AC14"/>
+    <mergeCell ref="AJ13:AK14"/>
+    <mergeCell ref="N13:O14"/>
+    <mergeCell ref="P13:Q14"/>
+    <mergeCell ref="R13:S14"/>
+    <mergeCell ref="T13:U14"/>
+    <mergeCell ref="V13:W14"/>
+    <mergeCell ref="X13:Y14"/>
+    <mergeCell ref="BF7:BG8"/>
+    <mergeCell ref="BH7:BI8"/>
+    <mergeCell ref="AB11:AC12"/>
+    <mergeCell ref="AD11:AE12"/>
+    <mergeCell ref="Z9:AA10"/>
+    <mergeCell ref="AB9:AC10"/>
+    <mergeCell ref="AD9:AE10"/>
+    <mergeCell ref="AF9:AG10"/>
+    <mergeCell ref="AH9:AI10"/>
+    <mergeCell ref="BJ7:BK8"/>
+    <mergeCell ref="BL7:BM8"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="H13:I14"/>
+    <mergeCell ref="J13:K14"/>
+    <mergeCell ref="L13:M14"/>
+    <mergeCell ref="AT7:AU8"/>
+    <mergeCell ref="AV7:AW8"/>
+    <mergeCell ref="AX7:AY8"/>
+    <mergeCell ref="AZ7:BA8"/>
+    <mergeCell ref="BB7:BC8"/>
+    <mergeCell ref="BD7:BE8"/>
+    <mergeCell ref="AF11:AG12"/>
+    <mergeCell ref="AH11:AI12"/>
+    <mergeCell ref="AJ11:AK12"/>
+    <mergeCell ref="AL11:AM12"/>
+    <mergeCell ref="AP7:AQ8"/>
+    <mergeCell ref="AR7:AS8"/>
+    <mergeCell ref="T11:U12"/>
+    <mergeCell ref="V11:W12"/>
+    <mergeCell ref="X11:Y12"/>
+    <mergeCell ref="Z11:AA12"/>
+    <mergeCell ref="BJ5:BK6"/>
+    <mergeCell ref="BL5:BM6"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="H11:I12"/>
+    <mergeCell ref="J11:K12"/>
+    <mergeCell ref="L11:M12"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="P11:Q12"/>
+    <mergeCell ref="R11:S12"/>
+    <mergeCell ref="AX5:AY6"/>
+    <mergeCell ref="AZ5:BA6"/>
+    <mergeCell ref="BB5:BC6"/>
+    <mergeCell ref="BD5:BE6"/>
+    <mergeCell ref="BF5:BG6"/>
+    <mergeCell ref="BH5:BI6"/>
+    <mergeCell ref="AJ9:AK10"/>
+    <mergeCell ref="AL9:AM10"/>
+    <mergeCell ref="AP5:AQ6"/>
+    <mergeCell ref="AR5:AS6"/>
+    <mergeCell ref="F9:G10"/>
+    <mergeCell ref="H9:I10"/>
+    <mergeCell ref="J9:K10"/>
+    <mergeCell ref="X9:Y10"/>
     <mergeCell ref="BJ4:BM4"/>
     <mergeCell ref="AB7:AC8"/>
     <mergeCell ref="AD7:AE8"/>
@@ -45231,366 +45545,52 @@
     <mergeCell ref="AB5:AC6"/>
     <mergeCell ref="AD5:AE6"/>
     <mergeCell ref="AB4:AE4"/>
-    <mergeCell ref="BJ5:BK6"/>
-    <mergeCell ref="BL5:BM6"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="H11:I12"/>
-    <mergeCell ref="J11:K12"/>
-    <mergeCell ref="L11:M12"/>
-    <mergeCell ref="N11:O12"/>
-    <mergeCell ref="P11:Q12"/>
-    <mergeCell ref="R11:S12"/>
-    <mergeCell ref="AX5:AY6"/>
-    <mergeCell ref="AZ5:BA6"/>
-    <mergeCell ref="BB5:BC6"/>
-    <mergeCell ref="BD5:BE6"/>
-    <mergeCell ref="BF5:BG6"/>
-    <mergeCell ref="BH5:BI6"/>
-    <mergeCell ref="AJ9:AK10"/>
-    <mergeCell ref="AL9:AM10"/>
-    <mergeCell ref="AP5:AQ6"/>
-    <mergeCell ref="AR5:AS6"/>
-    <mergeCell ref="F9:G10"/>
-    <mergeCell ref="H9:I10"/>
-    <mergeCell ref="J9:K10"/>
-    <mergeCell ref="X9:Y10"/>
-    <mergeCell ref="BJ7:BK8"/>
-    <mergeCell ref="BL7:BM8"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="H13:I14"/>
-    <mergeCell ref="J13:K14"/>
-    <mergeCell ref="L13:M14"/>
-    <mergeCell ref="AT7:AU8"/>
-    <mergeCell ref="AV7:AW8"/>
-    <mergeCell ref="AX7:AY8"/>
-    <mergeCell ref="AZ7:BA8"/>
-    <mergeCell ref="BB7:BC8"/>
-    <mergeCell ref="BD7:BE8"/>
-    <mergeCell ref="AF11:AG12"/>
-    <mergeCell ref="AH11:AI12"/>
-    <mergeCell ref="AJ11:AK12"/>
-    <mergeCell ref="AL11:AM12"/>
-    <mergeCell ref="AP7:AQ8"/>
-    <mergeCell ref="AR7:AS8"/>
-    <mergeCell ref="T11:U12"/>
-    <mergeCell ref="V11:W12"/>
-    <mergeCell ref="X11:Y12"/>
-    <mergeCell ref="Z11:AA12"/>
-    <mergeCell ref="AJ13:AK14"/>
-    <mergeCell ref="N13:O14"/>
-    <mergeCell ref="P13:Q14"/>
-    <mergeCell ref="R13:S14"/>
-    <mergeCell ref="T13:U14"/>
-    <mergeCell ref="V13:W14"/>
-    <mergeCell ref="X13:Y14"/>
-    <mergeCell ref="BF7:BG8"/>
-    <mergeCell ref="BH7:BI8"/>
-    <mergeCell ref="AB11:AC12"/>
-    <mergeCell ref="AD11:AE12"/>
-    <mergeCell ref="Z9:AA10"/>
-    <mergeCell ref="AB9:AC10"/>
-    <mergeCell ref="AD9:AE10"/>
-    <mergeCell ref="AF9:AG10"/>
-    <mergeCell ref="AH9:AI10"/>
-    <mergeCell ref="BL9:BM10"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="F15:G16"/>
-    <mergeCell ref="H15:I16"/>
-    <mergeCell ref="J15:K16"/>
-    <mergeCell ref="L15:M16"/>
-    <mergeCell ref="N15:O16"/>
-    <mergeCell ref="P15:Q16"/>
-    <mergeCell ref="R15:S16"/>
-    <mergeCell ref="T15:U16"/>
-    <mergeCell ref="AZ9:BA10"/>
-    <mergeCell ref="BB9:BC10"/>
-    <mergeCell ref="BD9:BE10"/>
-    <mergeCell ref="BF9:BG10"/>
-    <mergeCell ref="BH9:BI10"/>
-    <mergeCell ref="BJ9:BK10"/>
-    <mergeCell ref="AL13:AM14"/>
-    <mergeCell ref="AP9:AQ10"/>
-    <mergeCell ref="AR9:AS10"/>
-    <mergeCell ref="AT9:AU10"/>
-    <mergeCell ref="AV9:AW10"/>
-    <mergeCell ref="AX9:AY10"/>
-    <mergeCell ref="Z13:AA14"/>
-    <mergeCell ref="AB13:AC14"/>
-    <mergeCell ref="B17:B24"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="D17:E18"/>
-    <mergeCell ref="F17:G18"/>
-    <mergeCell ref="H17:I18"/>
-    <mergeCell ref="J17:K18"/>
-    <mergeCell ref="L17:M18"/>
-    <mergeCell ref="AV11:AW12"/>
-    <mergeCell ref="AX11:AY12"/>
-    <mergeCell ref="AH15:AI16"/>
-    <mergeCell ref="AJ15:AK16"/>
-    <mergeCell ref="AL15:AM16"/>
-    <mergeCell ref="AP11:AQ12"/>
-    <mergeCell ref="AR11:AS12"/>
-    <mergeCell ref="AT11:AU12"/>
-    <mergeCell ref="V15:W16"/>
-    <mergeCell ref="X15:Y16"/>
-    <mergeCell ref="Z15:AA16"/>
-    <mergeCell ref="AB15:AC16"/>
-    <mergeCell ref="AD15:AE16"/>
-    <mergeCell ref="AF15:AG16"/>
-    <mergeCell ref="B9:B16"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="T17:U18"/>
-    <mergeCell ref="V17:W18"/>
-    <mergeCell ref="X17:Y18"/>
-    <mergeCell ref="BH11:BI12"/>
-    <mergeCell ref="BJ11:BK12"/>
-    <mergeCell ref="BL11:BM12"/>
-    <mergeCell ref="AZ11:BA12"/>
-    <mergeCell ref="BB11:BC12"/>
-    <mergeCell ref="BD11:BE12"/>
-    <mergeCell ref="BF11:BG12"/>
-    <mergeCell ref="AP13:AQ14"/>
-    <mergeCell ref="AR13:AS14"/>
-    <mergeCell ref="AT13:AU14"/>
-    <mergeCell ref="AV13:AW14"/>
-    <mergeCell ref="AX13:AY14"/>
-    <mergeCell ref="Z17:AA18"/>
-    <mergeCell ref="AB17:AC18"/>
-    <mergeCell ref="AD17:AE18"/>
-    <mergeCell ref="AF17:AG18"/>
-    <mergeCell ref="AH17:AI18"/>
-    <mergeCell ref="AJ17:AK18"/>
-    <mergeCell ref="AD13:AE14"/>
-    <mergeCell ref="AF13:AG14"/>
-    <mergeCell ref="AH13:AI14"/>
-    <mergeCell ref="Z19:AA20"/>
-    <mergeCell ref="AB19:AC20"/>
-    <mergeCell ref="AD19:AE20"/>
-    <mergeCell ref="AF19:AG20"/>
-    <mergeCell ref="BL13:BM14"/>
-    <mergeCell ref="D19:E20"/>
-    <mergeCell ref="F19:G20"/>
-    <mergeCell ref="H19:I20"/>
-    <mergeCell ref="J19:K20"/>
-    <mergeCell ref="L19:M20"/>
-    <mergeCell ref="N19:O20"/>
-    <mergeCell ref="P19:Q20"/>
-    <mergeCell ref="R19:S20"/>
-    <mergeCell ref="T19:U20"/>
-    <mergeCell ref="AZ13:BA14"/>
-    <mergeCell ref="BB13:BC14"/>
-    <mergeCell ref="BD13:BE14"/>
-    <mergeCell ref="BF13:BG14"/>
-    <mergeCell ref="BH13:BI14"/>
-    <mergeCell ref="BJ13:BK14"/>
-    <mergeCell ref="AL17:AM18"/>
-    <mergeCell ref="N17:O18"/>
-    <mergeCell ref="P17:Q18"/>
-    <mergeCell ref="R17:S18"/>
-    <mergeCell ref="BH15:BI16"/>
-    <mergeCell ref="BJ15:BK16"/>
-    <mergeCell ref="BL15:BM16"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="D21:E22"/>
-    <mergeCell ref="F21:G22"/>
-    <mergeCell ref="H21:I22"/>
-    <mergeCell ref="J21:K22"/>
-    <mergeCell ref="L21:M22"/>
-    <mergeCell ref="N21:O22"/>
-    <mergeCell ref="AV15:AW16"/>
-    <mergeCell ref="AX15:AY16"/>
-    <mergeCell ref="AZ15:BA16"/>
-    <mergeCell ref="BB15:BC16"/>
-    <mergeCell ref="BD15:BE16"/>
-    <mergeCell ref="BF15:BG16"/>
-    <mergeCell ref="AH19:AI20"/>
-    <mergeCell ref="AJ19:AK20"/>
-    <mergeCell ref="AL19:AM20"/>
-    <mergeCell ref="AP15:AQ16"/>
-    <mergeCell ref="AR15:AS16"/>
-    <mergeCell ref="AT15:AU16"/>
-    <mergeCell ref="V19:W20"/>
-    <mergeCell ref="X19:Y20"/>
-    <mergeCell ref="J23:K24"/>
-    <mergeCell ref="L23:M24"/>
-    <mergeCell ref="N23:O24"/>
-    <mergeCell ref="BB17:BC18"/>
-    <mergeCell ref="BD17:BE18"/>
-    <mergeCell ref="BF17:BG18"/>
-    <mergeCell ref="BH17:BI18"/>
-    <mergeCell ref="BJ17:BK18"/>
-    <mergeCell ref="BL17:BM18"/>
-    <mergeCell ref="AP17:AQ18"/>
-    <mergeCell ref="AR17:AS18"/>
-    <mergeCell ref="AT17:AU18"/>
-    <mergeCell ref="AV17:AW18"/>
-    <mergeCell ref="AX17:AY18"/>
-    <mergeCell ref="AZ17:BA18"/>
-    <mergeCell ref="AB21:AC22"/>
-    <mergeCell ref="AD21:AE22"/>
-    <mergeCell ref="AF21:AG22"/>
-    <mergeCell ref="AH21:AI22"/>
-    <mergeCell ref="AJ21:AK22"/>
-    <mergeCell ref="AL21:AM22"/>
-    <mergeCell ref="P21:Q22"/>
-    <mergeCell ref="R21:S22"/>
-    <mergeCell ref="T21:U22"/>
-    <mergeCell ref="BH19:BI20"/>
-    <mergeCell ref="BJ19:BK20"/>
-    <mergeCell ref="BL19:BM20"/>
-    <mergeCell ref="AP19:AQ20"/>
-    <mergeCell ref="AR19:AS20"/>
-    <mergeCell ref="AT19:AU20"/>
-    <mergeCell ref="AV19:AW20"/>
-    <mergeCell ref="AX19:AY20"/>
-    <mergeCell ref="AZ19:BA20"/>
-    <mergeCell ref="B25:C28"/>
-    <mergeCell ref="D25:E26"/>
-    <mergeCell ref="F25:G26"/>
-    <mergeCell ref="H25:I26"/>
-    <mergeCell ref="J25:K26"/>
-    <mergeCell ref="L25:M26"/>
-    <mergeCell ref="BB19:BC20"/>
-    <mergeCell ref="BD19:BE20"/>
-    <mergeCell ref="BF19:BG20"/>
-    <mergeCell ref="AB23:AC24"/>
-    <mergeCell ref="AD23:AE24"/>
-    <mergeCell ref="AF23:AG24"/>
-    <mergeCell ref="AH23:AI24"/>
-    <mergeCell ref="AJ23:AK24"/>
-    <mergeCell ref="AL23:AM24"/>
-    <mergeCell ref="P23:Q24"/>
-    <mergeCell ref="R23:S24"/>
-    <mergeCell ref="T23:U24"/>
-    <mergeCell ref="V23:W24"/>
-    <mergeCell ref="X23:Y24"/>
-    <mergeCell ref="Z23:AA24"/>
-    <mergeCell ref="D23:E24"/>
-    <mergeCell ref="F23:G24"/>
-    <mergeCell ref="H23:I24"/>
-    <mergeCell ref="AV21:AW22"/>
-    <mergeCell ref="AX21:AY22"/>
-    <mergeCell ref="Z25:AA26"/>
-    <mergeCell ref="AB25:AC26"/>
-    <mergeCell ref="AD25:AE26"/>
-    <mergeCell ref="AF25:AG26"/>
-    <mergeCell ref="AH25:AI26"/>
-    <mergeCell ref="AJ25:AK26"/>
-    <mergeCell ref="N25:O26"/>
-    <mergeCell ref="P25:Q26"/>
-    <mergeCell ref="R25:S26"/>
-    <mergeCell ref="T25:U26"/>
-    <mergeCell ref="V25:W26"/>
-    <mergeCell ref="X25:Y26"/>
-    <mergeCell ref="V21:W22"/>
-    <mergeCell ref="X21:Y22"/>
-    <mergeCell ref="Z21:AA22"/>
-    <mergeCell ref="Z27:AA28"/>
-    <mergeCell ref="AB27:AC28"/>
-    <mergeCell ref="AD27:AE28"/>
-    <mergeCell ref="AF27:AG28"/>
-    <mergeCell ref="BL21:BM22"/>
-    <mergeCell ref="D27:E28"/>
-    <mergeCell ref="F27:G28"/>
-    <mergeCell ref="H27:I28"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="L27:M28"/>
-    <mergeCell ref="N27:O28"/>
-    <mergeCell ref="P27:Q28"/>
-    <mergeCell ref="R27:S28"/>
-    <mergeCell ref="T27:U28"/>
-    <mergeCell ref="AZ21:BA22"/>
-    <mergeCell ref="BB21:BC22"/>
-    <mergeCell ref="BD21:BE22"/>
-    <mergeCell ref="BF21:BG22"/>
-    <mergeCell ref="BH21:BI22"/>
-    <mergeCell ref="BJ21:BK22"/>
-    <mergeCell ref="AL25:AM26"/>
-    <mergeCell ref="AP21:AQ22"/>
-    <mergeCell ref="AR21:AS22"/>
-    <mergeCell ref="AT21:AU22"/>
-    <mergeCell ref="BH23:BI24"/>
-    <mergeCell ref="BJ23:BK24"/>
-    <mergeCell ref="BL23:BM24"/>
-    <mergeCell ref="B29:C32"/>
-    <mergeCell ref="D29:E30"/>
-    <mergeCell ref="F29:G30"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="J29:K30"/>
-    <mergeCell ref="L29:M30"/>
-    <mergeCell ref="N29:O30"/>
-    <mergeCell ref="AV23:AW24"/>
-    <mergeCell ref="AX23:AY24"/>
-    <mergeCell ref="AZ23:BA24"/>
-    <mergeCell ref="BB23:BC24"/>
-    <mergeCell ref="BD23:BE24"/>
-    <mergeCell ref="BF23:BG24"/>
-    <mergeCell ref="AH27:AI28"/>
-    <mergeCell ref="AJ27:AK28"/>
-    <mergeCell ref="AL27:AM28"/>
-    <mergeCell ref="AP23:AQ24"/>
-    <mergeCell ref="AR23:AS24"/>
-    <mergeCell ref="AT23:AU24"/>
-    <mergeCell ref="V27:W28"/>
-    <mergeCell ref="X27:Y28"/>
-    <mergeCell ref="BH25:BI26"/>
-    <mergeCell ref="BJ25:BK26"/>
-    <mergeCell ref="BL25:BM26"/>
-    <mergeCell ref="AP25:AQ26"/>
-    <mergeCell ref="AR25:AS26"/>
-    <mergeCell ref="AT25:AU26"/>
-    <mergeCell ref="AV25:AW26"/>
-    <mergeCell ref="AX25:AY26"/>
-    <mergeCell ref="AZ25:BA26"/>
-    <mergeCell ref="D31:E32"/>
-    <mergeCell ref="F31:G32"/>
-    <mergeCell ref="H31:I32"/>
-    <mergeCell ref="J31:K32"/>
-    <mergeCell ref="L31:M32"/>
-    <mergeCell ref="N31:O32"/>
-    <mergeCell ref="BB25:BC26"/>
-    <mergeCell ref="BD25:BE26"/>
-    <mergeCell ref="BF25:BG26"/>
-    <mergeCell ref="AB29:AC30"/>
-    <mergeCell ref="AD29:AE30"/>
-    <mergeCell ref="AF29:AG30"/>
-    <mergeCell ref="AH29:AI30"/>
-    <mergeCell ref="AJ29:AK30"/>
-    <mergeCell ref="AL29:AM30"/>
-    <mergeCell ref="P29:Q30"/>
-    <mergeCell ref="R29:S30"/>
-    <mergeCell ref="T29:U30"/>
-    <mergeCell ref="V29:W30"/>
-    <mergeCell ref="X29:Y30"/>
-    <mergeCell ref="Z29:AA30"/>
-    <mergeCell ref="AB31:AC32"/>
-    <mergeCell ref="AD31:AE32"/>
-    <mergeCell ref="AF31:AG32"/>
-    <mergeCell ref="AH31:AI32"/>
-    <mergeCell ref="AJ31:AK32"/>
-    <mergeCell ref="AL31:AM32"/>
-    <mergeCell ref="P31:Q32"/>
-    <mergeCell ref="R31:S32"/>
-    <mergeCell ref="T31:U32"/>
-    <mergeCell ref="V31:W32"/>
-    <mergeCell ref="X31:Y32"/>
-    <mergeCell ref="Z31:AA32"/>
-    <mergeCell ref="BB27:BC28"/>
-    <mergeCell ref="BD27:BE28"/>
-    <mergeCell ref="BF27:BG28"/>
-    <mergeCell ref="BH27:BI28"/>
-    <mergeCell ref="BJ27:BK28"/>
-    <mergeCell ref="BL27:BM28"/>
-    <mergeCell ref="AP27:AQ28"/>
-    <mergeCell ref="AR27:AS28"/>
-    <mergeCell ref="AT27:AU28"/>
-    <mergeCell ref="AV27:AW28"/>
-    <mergeCell ref="AX27:AY28"/>
-    <mergeCell ref="AZ27:BA28"/>
+    <mergeCell ref="L9:M10"/>
+    <mergeCell ref="N9:O10"/>
+    <mergeCell ref="P9:Q10"/>
+    <mergeCell ref="R9:S10"/>
+    <mergeCell ref="T9:U10"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="Z5:AA6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="H7:I8"/>
+    <mergeCell ref="J7:K8"/>
+    <mergeCell ref="L7:M8"/>
+    <mergeCell ref="N7:O8"/>
+    <mergeCell ref="AF4:AI4"/>
+    <mergeCell ref="AJ4:AM4"/>
+    <mergeCell ref="B5:C8"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:G6"/>
+    <mergeCell ref="H5:I6"/>
+    <mergeCell ref="J5:K6"/>
+    <mergeCell ref="L5:M6"/>
+    <mergeCell ref="N5:O6"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="P4:S4"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="X4:AA4"/>
+    <mergeCell ref="AH5:AI6"/>
+    <mergeCell ref="AJ5:AK6"/>
+    <mergeCell ref="AL5:AM6"/>
+    <mergeCell ref="P5:Q6"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="T5:U6"/>
+    <mergeCell ref="V5:W6"/>
+    <mergeCell ref="X5:Y6"/>
+    <mergeCell ref="D2:K2"/>
+    <mergeCell ref="L2:S2"/>
+    <mergeCell ref="T2:AA2"/>
+    <mergeCell ref="AB2:AI2"/>
+    <mergeCell ref="AJ2:AM2"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="T3:AA3"/>
+    <mergeCell ref="AB3:AI3"/>
+    <mergeCell ref="AJ3:AM3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
@@ -57332,7 +57332,7 @@
     <col min="4" max="4" width="12.25" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.75" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.25" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="5.125" style="11" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="67" customWidth="1"/>
     <col min="9" max="9" width="12.25" style="67" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="12.25" style="67" customWidth="1"/>
@@ -57341,11 +57341,13 @@
     <col min="14" max="14" width="13.75" style="67" customWidth="1"/>
     <col min="15" max="15" width="19.25" style="67" customWidth="1"/>
     <col min="16" max="17" width="13.75" style="67" customWidth="1"/>
-    <col min="18" max="18" width="12.25" style="67" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="11"/>
+    <col min="18" max="18" width="5.875" customWidth="1"/>
+    <col min="19" max="19" width="3.25" style="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="28" width="10.625" style="11" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:55" s="33" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="2:55" s="33" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="B1" s="60" t="s">
         <v>581</v>
       </c>
@@ -57360,7 +57362,16 @@
       <c r="O1" s="59"/>
       <c r="P1" s="59"/>
       <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
+      <c r="R1"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="34"/>
       <c r="AG1" s="62"/>
       <c r="AI1" s="37"/>
       <c r="AJ1" s="37">
@@ -57404,7 +57415,10 @@
       <c r="BB1" s="38"/>
       <c r="BC1" s="38"/>
     </row>
-    <row r="3" spans="2:55">
+    <row r="2" spans="2:55" ht="26.25" thickBot="1">
+      <c r="R2" s="123"/>
+    </row>
+    <row r="3" spans="2:55" ht="30">
       <c r="B3" s="63" t="s">
         <v>582</v>
       </c>
@@ -57449,6 +57463,32 @@
       </c>
       <c r="Q3" s="66" t="s">
         <v>590</v>
+      </c>
+      <c r="R3" s="33"/>
+      <c r="T3" s="68" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))))</f>
+        <v>o͘</v>
+      </c>
+      <c r="U3" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="V3" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="W3" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="X3" s="63" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y3" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z3" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA3" s="63" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="2:55" ht="34.5">
@@ -57496,6 +57536,42 @@
       <c r="Q4" s="76">
         <v>1</v>
       </c>
+      <c r="R4" s="33"/>
+      <c r="S4" s="11">
+        <v>1</v>
+      </c>
+      <c r="T4" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E4,4)))), $T$3)</f>
+        <v>o͘</v>
+      </c>
+      <c r="U4" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="V4" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="W4" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="X4" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="Y4" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="Z4" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="AA4" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
+        <v>n</v>
+      </c>
     </row>
     <row r="5" spans="2:55" ht="34.5">
       <c r="B5" s="69">
@@ -57546,6 +57622,42 @@
       <c r="Q5" s="76">
         <v>6</v>
       </c>
+      <c r="R5" s="33"/>
+      <c r="S5" s="11">
+        <v>2</v>
+      </c>
+      <c r="T5" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E5,4)))), $T$3)</f>
+        <v>ó͘</v>
+      </c>
+      <c r="U5" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="V5" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="W5" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="X5" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="Y5" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="Z5" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="AA5" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
+        <v>ń</v>
+      </c>
     </row>
     <row r="6" spans="2:55" ht="34.5">
       <c r="B6" s="69">
@@ -57596,6 +57708,42 @@
       <c r="Q6" s="76">
         <v>5</v>
       </c>
+      <c r="R6" s="33"/>
+      <c r="S6" s="11">
+        <v>3</v>
+      </c>
+      <c r="T6" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E6,4)))), $T$3)</f>
+        <v>ò͘</v>
+      </c>
+      <c r="U6" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="V6" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="W6" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="X6" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="Y6" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="Z6" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="AA6" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
     </row>
     <row r="7" spans="2:55" ht="34.5">
       <c r="B7" s="69">
@@ -57644,6 +57792,42 @@
       <c r="Q7" s="76">
         <v>3</v>
       </c>
+      <c r="R7" s="33"/>
+      <c r="S7" s="11">
+        <v>4</v>
+      </c>
+      <c r="T7" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E7,4)))), $T$3)</f>
+        <v>o͘</v>
+      </c>
+      <c r="U7" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="V7" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="W7" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="X7" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="Y7" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="Z7" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="AA7" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
+        <v>n</v>
+      </c>
     </row>
     <row r="8" spans="2:55" ht="34.5">
       <c r="B8" s="69">
@@ -57694,6 +57878,42 @@
       <c r="Q8" s="76">
         <v>2</v>
       </c>
+      <c r="R8" s="33"/>
+      <c r="S8" s="11">
+        <v>5</v>
+      </c>
+      <c r="T8" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E8,4)))), "")</f>
+        <v>ǒ͘</v>
+      </c>
+      <c r="U8" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="V8" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="W8" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="X8" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="Y8" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="Z8" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="AA8" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
+        <v>ň</v>
+      </c>
     </row>
     <row r="9" spans="2:55" ht="34.5">
       <c r="B9" s="79">
@@ -57742,6 +57962,42 @@
       <c r="Q9" s="76">
         <v>7</v>
       </c>
+      <c r="R9" s="33"/>
+      <c r="S9" s="11">
+        <v>6</v>
+      </c>
+      <c r="T9" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E9,4)))), "")</f>
+        <v>ó͘</v>
+      </c>
+      <c r="U9" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="V9" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="W9" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="X9" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="Y9" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="Z9" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="AA9" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
+        <v>ń</v>
+      </c>
     </row>
     <row r="10" spans="2:55" ht="34.5">
       <c r="B10" s="69">
@@ -57791,6 +58047,42 @@
       </c>
       <c r="Q10" s="76">
         <v>8</v>
+      </c>
+      <c r="R10" s="33"/>
+      <c r="S10" s="11">
+        <v>7</v>
+      </c>
+      <c r="T10" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E10,4)))), "")</f>
+        <v>ō͘</v>
+      </c>
+      <c r="U10" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="V10" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="W10" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="X10" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="Y10" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="Z10" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="AA10" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
+        <v>n̄</v>
       </c>
     </row>
     <row r="11" spans="2:55" ht="34.5">
@@ -57837,6 +58129,42 @@
         <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("a", _xlfn.UNICHAR(HEX2DEC(RIGHT(P11,4)))), "")</f>
         <v/>
       </c>
+      <c r="R11" s="33"/>
+      <c r="S11" s="11">
+        <v>8</v>
+      </c>
+      <c r="T11" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E11,4)))), "")</f>
+        <v>o̍͘</v>
+      </c>
+      <c r="U11" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
+        <v>a̍</v>
+      </c>
+      <c r="V11" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
+        <v>i̍</v>
+      </c>
+      <c r="W11" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
+        <v>u̍</v>
+      </c>
+      <c r="X11" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
+        <v>e̍</v>
+      </c>
+      <c r="Y11" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
+        <v>o̍</v>
+      </c>
+      <c r="Z11" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
+        <v>m̍</v>
+      </c>
+      <c r="AA11" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
+        <v>n̍</v>
+      </c>
     </row>
     <row r="12" spans="2:55" ht="30">
       <c r="B12" s="69">
@@ -57853,6 +58181,41 @@
         <f t="shared" si="0"/>
         <v>a̋</v>
       </c>
+      <c r="S12" s="11">
+        <v>9</v>
+      </c>
+      <c r="T12" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E12,4)))), "")</f>
+        <v>ő͘</v>
+      </c>
+      <c r="U12" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
+        <v>a̋</v>
+      </c>
+      <c r="V12" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
+        <v>i̋</v>
+      </c>
+      <c r="W12" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
+        <v>ű</v>
+      </c>
+      <c r="X12" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
+        <v>e̋</v>
+      </c>
+      <c r="Y12" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
+        <v>ő</v>
+      </c>
+      <c r="Z12" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
+        <v>m̋</v>
+      </c>
+      <c r="AA12" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
+        <v>n̋</v>
+      </c>
     </row>
     <row r="13" spans="2:55" ht="30">
       <c r="B13" s="69">
@@ -57874,6 +58237,41 @@
       </c>
       <c r="I13" s="66" t="s">
         <v>618</v>
+      </c>
+      <c r="S13" s="11">
+        <v>0</v>
+      </c>
+      <c r="T13" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E13,4)))), "")</f>
+        <v>o̊͘</v>
+      </c>
+      <c r="U13" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
+        <v>å</v>
+      </c>
+      <c r="V13" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
+        <v>i̊</v>
+      </c>
+      <c r="W13" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
+        <v>ů</v>
+      </c>
+      <c r="X13" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
+        <v>e̊</v>
+      </c>
+      <c r="Y13" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
+        <v>o̊</v>
+      </c>
+      <c r="Z13" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
+        <v>m̊</v>
+      </c>
+      <c r="AA13" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
+        <v>n̊</v>
       </c>
     </row>
     <row r="14" spans="2:55">
@@ -57925,9 +58323,37 @@
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
+      <c r="T16" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="U16" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="V16" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="W16" s="63" t="s">
+        <v>249</v>
+      </c>
+      <c r="X16" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y16" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z16" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="AC16" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O4,4))), "n"), "")</f>
+        <v>lūn</v>
+      </c>
+      <c r="AD16" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O4,4))), "o"), "")</f>
+        <v>ngōo</v>
+      </c>
     </row>
-    <row r="17" spans="2:18" ht="30">
+    <row r="17" spans="2:30" ht="30">
       <c r="B17" s="69">
         <v>1</v>
       </c>
@@ -57951,8 +58377,47 @@
         <f t="shared" si="1"/>
         <v>⁴</v>
       </c>
+      <c r="S17" s="11">
+        <v>1</v>
+      </c>
+      <c r="T17" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="U17" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="V17" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="W17" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="X17" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="Y17" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="Z17" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
+        <v>n̄</v>
+      </c>
+      <c r="AC17" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O7,4))), "n"), "")</f>
+        <v>lǔn</v>
+      </c>
+      <c r="AD17" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O7,4))), "o"), "")</f>
+        <v>ngǒo</v>
+      </c>
     </row>
-    <row r="18" spans="2:18" ht="30">
+    <row r="18" spans="2:30" ht="30">
       <c r="B18" s="69">
         <v>2</v>
       </c>
@@ -57976,8 +58441,47 @@
         <f t="shared" si="1"/>
         <v>⁵</v>
       </c>
+      <c r="S18" s="11">
+        <v>2</v>
+      </c>
+      <c r="T18" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="U18" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="V18" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="W18" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="X18" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="Y18" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="Z18" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="AC18" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O6,4))), "n"), "")</f>
+        <v>lùn</v>
+      </c>
+      <c r="AD18" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O6,4))), "o"), "")</f>
+        <v>ngòo</v>
+      </c>
     </row>
-    <row r="19" spans="2:18" ht="30">
+    <row r="19" spans="2:30" ht="30">
       <c r="B19" s="69">
         <v>3</v>
       </c>
@@ -58001,8 +58505,47 @@
         <f t="shared" si="1"/>
         <v>⁶</v>
       </c>
+      <c r="S19" s="11">
+        <v>3</v>
+      </c>
+      <c r="T19" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="U19" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="V19" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="W19" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="X19" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="Y19" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="Z19" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="AC19" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O9,4))), "n"), "")</f>
+        <v>lūn</v>
+      </c>
+      <c r="AD19" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O9,4))), "o"), "")</f>
+        <v>ngōo</v>
+      </c>
     </row>
-    <row r="20" spans="2:18" ht="30">
+    <row r="20" spans="2:30" ht="30">
       <c r="B20" s="79">
         <v>4</v>
       </c>
@@ -58024,8 +58567,47 @@
         <f t="shared" si="1"/>
         <v>⁷</v>
       </c>
+      <c r="S20" s="11">
+        <v>4</v>
+      </c>
+      <c r="T20" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="U20" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="V20" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="W20" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="X20" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="Y20" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="Z20" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="AC20" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O8,4))), "n"), "")</f>
+        <v>lún</v>
+      </c>
+      <c r="AD20" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O8,4))), "o"), "")</f>
+        <v>ngóo</v>
+      </c>
     </row>
-    <row r="21" spans="2:18" ht="30">
+    <row r="21" spans="2:30" ht="30">
       <c r="B21" s="69">
         <v>5</v>
       </c>
@@ -58049,8 +58631,47 @@
         <f t="shared" si="1"/>
         <v>⁸</v>
       </c>
+      <c r="S21" s="11">
+        <v>5</v>
+      </c>
+      <c r="T21" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="U21" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="V21" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="W21" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="X21" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="Y21" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="Z21" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
+      <c r="AC21" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O11,4))), "n"), "")</f>
+        <v>lǔn</v>
+      </c>
+      <c r="AD21" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O11,4))), "o"), "")</f>
+        <v>ngǒo</v>
+      </c>
     </row>
-    <row r="22" spans="2:18" ht="30">
+    <row r="22" spans="2:30" ht="30">
       <c r="B22" s="69">
         <v>6</v>
       </c>
@@ -58074,8 +58695,47 @@
         <f t="shared" si="1"/>
         <v>⁹</v>
       </c>
+      <c r="S22" s="11">
+        <v>6</v>
+      </c>
+      <c r="T22" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
+        <v>â</v>
+      </c>
+      <c r="U22" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
+        <v>î</v>
+      </c>
+      <c r="V22" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
+        <v>û</v>
+      </c>
+      <c r="W22" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
+        <v>ê</v>
+      </c>
+      <c r="X22" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
+        <v>ô</v>
+      </c>
+      <c r="Y22" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
+        <v>m̂</v>
+      </c>
+      <c r="Z22" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
+        <v>n̂</v>
+      </c>
+      <c r="AC22" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O5,4))), "n"), "")</f>
+        <v>lûn</v>
+      </c>
+      <c r="AD22" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O5,4))), "o"), "")</f>
+        <v>ngôo</v>
+      </c>
     </row>
-    <row r="23" spans="2:18" ht="30">
+    <row r="23" spans="2:30" ht="30">
       <c r="B23" s="69">
         <v>7</v>
       </c>
@@ -58099,8 +58759,47 @@
         <f t="shared" si="1"/>
         <v>⁰</v>
       </c>
+      <c r="S23" s="11">
+        <v>7</v>
+      </c>
+      <c r="T23" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
+        <v>ā</v>
+      </c>
+      <c r="U23" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
+        <v>ī</v>
+      </c>
+      <c r="V23" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
+        <v>ū</v>
+      </c>
+      <c r="W23" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
+        <v>ē</v>
+      </c>
+      <c r="X23" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
+        <v>ō</v>
+      </c>
+      <c r="Y23" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
+        <v>m̄</v>
+      </c>
+      <c r="Z23" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
+        <v>n̄</v>
+      </c>
+      <c r="AC23" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O10,4))), "n"), "")</f>
+        <v>lún</v>
+      </c>
+      <c r="AD23" s="11" t="str">
+        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O10,4))), "o"), "")</f>
+        <v>ngóo</v>
+      </c>
     </row>
-    <row r="24" spans="2:18" ht="30">
+    <row r="24" spans="2:30" ht="30">
       <c r="B24" s="69">
         <v>8</v>
       </c>
@@ -58118,8 +58817,39 @@
         <v>áh</v>
       </c>
       <c r="H24" s="11"/>
+      <c r="S24" s="11">
+        <v>8</v>
+      </c>
+      <c r="T24" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="U24" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="V24" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="W24" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="X24" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="Y24" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="Z24" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
+        <v>ń</v>
+      </c>
     </row>
-    <row r="25" spans="2:18" ht="30">
+    <row r="25" spans="2:30" ht="30">
       <c r="B25" s="69">
         <v>9</v>
       </c>
@@ -58142,9 +58872,8 @@
       <c r="O25" s="11"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
     </row>
-    <row r="26" spans="2:18" ht="30">
+    <row r="26" spans="2:30" ht="30">
       <c r="B26" s="69">
         <v>0</v>
       </c>
@@ -58167,13 +58896,369 @@
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
     </row>
-    <row r="38" spans="6:7">
+    <row r="29" spans="2:30">
+      <c r="T29" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="U29" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="V29" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="W29" s="63" t="s">
+        <v>249</v>
+      </c>
+      <c r="X29" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y29" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z29" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="AC29" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="AD29" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="30" spans="2:30" ht="30">
+      <c r="S30" s="11">
+        <v>1</v>
+      </c>
+      <c r="T30" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="U30" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="V30" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="W30" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="X30" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="Y30" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="Z30" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
+        <v>n</v>
+      </c>
+      <c r="AC30" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
+        <v>lo</v>
+      </c>
+      <c r="AD30" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4)))), "r", IF(OR(S30=4, S30=8), "k", "")), "")</f>
+        <v>lor</v>
+      </c>
+    </row>
+    <row r="31" spans="2:30" ht="30">
+      <c r="S31" s="11">
+        <v>2</v>
+      </c>
+      <c r="T31" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="U31" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="V31" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="W31" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="X31" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="Y31" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="Z31" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
+        <v/>
+      </c>
+      <c r="AC31" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
+        <v>ló</v>
+      </c>
+      <c r="AD31" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4)))), "r", IF(OR(S31=4, S31=8), "k", "")), "")</f>
+        <v>lór</v>
+      </c>
+    </row>
+    <row r="32" spans="2:30" ht="30">
+      <c r="S32" s="11">
+        <v>3</v>
+      </c>
+      <c r="T32" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
+        <v>a</v>
+      </c>
+      <c r="U32" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
+        <v>i</v>
+      </c>
+      <c r="V32" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
+        <v>u</v>
+      </c>
+      <c r="W32" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
+        <v>e</v>
+      </c>
+      <c r="X32" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
+        <v>o</v>
+      </c>
+      <c r="Y32" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
+        <v>m</v>
+      </c>
+      <c r="Z32" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
+        <v>n</v>
+      </c>
+      <c r="AC32" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
+        <v>lò</v>
+      </c>
+      <c r="AD32" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4)))), "r", IF(OR(S32=4, S32=8), "k", "")), "")</f>
+        <v>lòr</v>
+      </c>
+    </row>
+    <row r="33" spans="6:30" ht="30">
+      <c r="S33" s="11">
+        <v>4</v>
+      </c>
+      <c r="T33" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="U33" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="V33" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="W33" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="X33" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="Y33" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="Z33" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="AC33" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4)))), "k"), "")</f>
+        <v>lók</v>
+      </c>
+      <c r="AD33" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4)))), "r", IF(OR(S33=4, S33=8), "k", "")), "")</f>
+        <v>lórk</v>
+      </c>
+    </row>
+    <row r="34" spans="6:30" ht="30">
+      <c r="S34" s="11">
+        <v>5</v>
+      </c>
+      <c r="T34" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
+        <v>à</v>
+      </c>
+      <c r="U34" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
+        <v>ì</v>
+      </c>
+      <c r="V34" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
+        <v>ù</v>
+      </c>
+      <c r="W34" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
+        <v>è</v>
+      </c>
+      <c r="X34" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
+        <v>ò</v>
+      </c>
+      <c r="Y34" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
+        <v>m̀</v>
+      </c>
+      <c r="Z34" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
+        <v>ǹ</v>
+      </c>
+      <c r="AC34" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
+        <v>lǒ</v>
+      </c>
+      <c r="AD34" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4)))), "r", IF(OR(S34=4, S34=8), "k", "")), "")</f>
+        <v>lǒr</v>
+      </c>
+    </row>
+    <row r="35" spans="6:30" ht="30">
+      <c r="S35" s="11">
+        <v>6</v>
+      </c>
+      <c r="T35" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="U35" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="V35" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="W35" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="X35" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="Y35" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="Z35" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="AC35" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
+        <v>ló</v>
+      </c>
+      <c r="AD35" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4)))), "r", IF(OR(S35=4, S35=8), "k", "")), "")</f>
+        <v>lór</v>
+      </c>
+    </row>
+    <row r="36" spans="6:30" ht="30">
+      <c r="S36" s="11">
+        <v>7</v>
+      </c>
+      <c r="T36" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
+        <v>ǎ</v>
+      </c>
+      <c r="U36" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
+        <v>ǐ</v>
+      </c>
+      <c r="V36" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
+        <v>ǔ</v>
+      </c>
+      <c r="W36" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
+        <v>ě</v>
+      </c>
+      <c r="X36" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
+        <v>ǒ</v>
+      </c>
+      <c r="Y36" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
+        <v>m̌</v>
+      </c>
+      <c r="Z36" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
+        <v>ň</v>
+      </c>
+      <c r="AC36" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M5,4))))), "")</f>
+        <v>lō</v>
+      </c>
+      <c r="AD36" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M5,4)))), "r", IF(OR(S36=4, S36=8), "k", "")), "")</f>
+        <v>lōr</v>
+      </c>
+    </row>
+    <row r="37" spans="6:30" ht="30">
+      <c r="S37" s="11">
+        <v>8</v>
+      </c>
+      <c r="T37" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(U$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
+        <v>á</v>
+      </c>
+      <c r="U37" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(V$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
+        <v>í</v>
+      </c>
+      <c r="V37" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(W$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
+        <v>ú</v>
+      </c>
+      <c r="W37" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(X$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
+        <v>é</v>
+      </c>
+      <c r="X37" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Y$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
+        <v>ó</v>
+      </c>
+      <c r="Y37" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(Z$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
+        <v>ḿ</v>
+      </c>
+      <c r="Z37" s="77" t="str">
+        <f>IFERROR( _xlfn.CONCAT(AA$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
+        <v>ń</v>
+      </c>
+      <c r="AC37" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M10,4)))), "k"), "")</f>
+        <v>lo̍k</v>
+      </c>
+      <c r="AD37" s="97" t="str">
+        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M10,4)))), "r", IF(OR(S37=4, S37=8), "k", "")), "")</f>
+        <v>lo̍rk</v>
+      </c>
+    </row>
+    <row r="38" spans="6:30">
       <c r="F38" s="67"/>
       <c r="G38" s="67"/>
     </row>
-    <row r="39" spans="6:7">
+    <row r="39" spans="6:30">
       <c r="F39" s="67"/>
       <c r="G39" s="67"/>
     </row>
@@ -58190,36 +59275,18 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492F0654-E373-48D5-9724-36529E809595}">
-  <dimension ref="B1:V37"/>
-  <sheetFormatPr defaultRowHeight="25.5"/>
+  <dimension ref="B1:G19"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.625" customWidth="1"/>
     <col min="2" max="2" width="9" style="145"/>
     <col min="3" max="4" width="19.625" customWidth="1"/>
     <col min="5" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="8" width="19.625" customWidth="1"/>
-    <col min="9" max="9" width="3.25" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="18" width="10.625" style="11" customWidth="1"/>
-    <col min="19" max="22" width="9" style="11"/>
+    <col min="6" max="7" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15.75" customHeight="1" thickBot="1">
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="33"/>
-    </row>
-    <row r="2" spans="2:22" s="143" customFormat="1" ht="31.5" thickBot="1">
+    <row r="1" spans="2:7" ht="15.75" customHeight="1" thickBot="1"/>
+    <row r="2" spans="2:7" s="143" customFormat="1" ht="31.5" thickBot="1">
       <c r="B2" s="148" t="s">
         <v>872</v>
       </c>
@@ -58235,23 +59302,8 @@
       <c r="G2" s="153" t="s">
         <v>871</v>
       </c>
-      <c r="H2" s="123"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
     </row>
-    <row r="3" spans="2:22" ht="30.75" thickBot="1">
+    <row r="3" spans="2:7" ht="27.75" thickBot="1">
       <c r="B3" s="43"/>
       <c r="C3" s="144" t="s">
         <v>576</v>
@@ -58267,34 +59319,8 @@
         <f xml:space="preserve"> _xlfn.UNICODE(G2)</f>
         <v>12444</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="J3" s="68" t="str">
-        <f xml:space="preserve"> _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))))</f>
-        <v>o͘</v>
-      </c>
-      <c r="K3" s="63" t="s">
-        <v>223</v>
-      </c>
-      <c r="L3" s="63" t="s">
-        <v>267</v>
-      </c>
-      <c r="M3" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="N3" s="63" t="s">
-        <v>249</v>
-      </c>
-      <c r="O3" s="63" t="s">
-        <v>235</v>
-      </c>
-      <c r="P3" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q3" s="63" t="s">
-        <v>194</v>
-      </c>
     </row>
-    <row r="4" spans="2:22" ht="30.75" thickBot="1">
+    <row r="4" spans="2:7" ht="27.75" thickBot="1">
       <c r="B4" s="43" t="s">
         <v>874</v>
       </c>
@@ -58312,44 +59338,8 @@
         <f xml:space="preserve"> DEC2HEX(G3)</f>
         <v>309C</v>
       </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="11">
-        <v>1</v>
-      </c>
-      <c r="J4" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E4,4)))), $J$3)</f>
-        <v>o͘</v>
-      </c>
-      <c r="K4" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
-        <v>a</v>
-      </c>
-      <c r="L4" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
-        <v>i</v>
-      </c>
-      <c r="M4" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
-        <v>u</v>
-      </c>
-      <c r="N4" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
-        <v>e</v>
-      </c>
-      <c r="O4" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
-        <v>o</v>
-      </c>
-      <c r="P4" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
-        <v>m</v>
-      </c>
-      <c r="Q4" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E4,4))))), "")</f>
-        <v>n</v>
-      </c>
     </row>
-    <row r="5" spans="2:22" ht="30.75" thickBot="1">
+    <row r="5" spans="2:7" ht="27.75" thickBot="1">
       <c r="B5" s="39" t="s">
         <v>871</v>
       </c>
@@ -58367,44 +59357,8 @@
         <f>_xlfn.CONCAT("U+",F19)</f>
         <v>U+</v>
       </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="11">
-        <v>2</v>
-      </c>
-      <c r="J5" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E5,4)))), $J$3)</f>
-        <v>ó͘</v>
-      </c>
-      <c r="K5" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
-        <v>á</v>
-      </c>
-      <c r="L5" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
-        <v>í</v>
-      </c>
-      <c r="M5" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
-        <v>ú</v>
-      </c>
-      <c r="N5" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
-        <v>é</v>
-      </c>
-      <c r="O5" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
-        <v>ó</v>
-      </c>
-      <c r="P5" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
-        <v>ḿ</v>
-      </c>
-      <c r="Q5" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E5,4))))), "")</f>
-        <v>ń</v>
-      </c>
     </row>
-    <row r="6" spans="2:22" ht="30.75" thickBot="1">
+    <row r="6" spans="2:7" ht="27.75" thickBot="1">
       <c r="B6" s="39"/>
       <c r="C6" s="144" t="s">
         <v>578</v>
@@ -58417,44 +59371,8 @@
         <f>RIGHT(C5,4)</f>
         <v>309C</v>
       </c>
-      <c r="H6" s="33"/>
-      <c r="I6" s="11">
-        <v>3</v>
-      </c>
-      <c r="J6" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E6,4)))), $J$3)</f>
-        <v>ò͘</v>
-      </c>
-      <c r="K6" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
-        <v>à</v>
-      </c>
-      <c r="L6" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
-        <v>ì</v>
-      </c>
-      <c r="M6" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
-        <v>ù</v>
-      </c>
-      <c r="N6" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
-        <v>è</v>
-      </c>
-      <c r="O6" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
-        <v>ò</v>
-      </c>
-      <c r="P6" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
-        <v>m̀</v>
-      </c>
-      <c r="Q6" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E6,4))))), "")</f>
-        <v>ǹ</v>
-      </c>
     </row>
-    <row r="7" spans="2:22" ht="30.75" thickBot="1">
+    <row r="7" spans="2:7" ht="27.75" thickBot="1">
       <c r="B7" s="39"/>
       <c r="C7" s="144"/>
       <c r="D7" s="39"/>
@@ -58462,87 +59380,15 @@
         <f xml:space="preserve"> HEX2DEC(G6)</f>
         <v>12444</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="11">
-        <v>4</v>
-      </c>
-      <c r="J7" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E7,4)))), $J$3)</f>
-        <v>o͘</v>
-      </c>
-      <c r="K7" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
-        <v>a</v>
-      </c>
-      <c r="L7" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
-        <v>i</v>
-      </c>
-      <c r="M7" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
-        <v>u</v>
-      </c>
-      <c r="N7" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
-        <v>e</v>
-      </c>
-      <c r="O7" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
-        <v>o</v>
-      </c>
-      <c r="P7" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
-        <v>m</v>
-      </c>
-      <c r="Q7" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E7,4))))), "")</f>
-        <v>n</v>
-      </c>
     </row>
-    <row r="8" spans="2:22" ht="30.75" thickBot="1">
+    <row r="8" spans="2:7" ht="24.75" thickBot="1">
       <c r="B8"/>
       <c r="G8" s="154" t="str">
         <f xml:space="preserve"> _xlfn.UNICHAR(G7)</f>
         <v>゜</v>
       </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="11">
-        <v>5</v>
-      </c>
-      <c r="J8" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E8,4)))), "")</f>
-        <v>ǒ͘</v>
-      </c>
-      <c r="K8" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
-        <v>ǎ</v>
-      </c>
-      <c r="L8" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
-        <v>ǐ</v>
-      </c>
-      <c r="M8" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
-        <v>ǔ</v>
-      </c>
-      <c r="N8" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
-        <v>ě</v>
-      </c>
-      <c r="O8" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
-        <v>ǒ</v>
-      </c>
-      <c r="P8" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
-        <v>m̌</v>
-      </c>
-      <c r="Q8" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E8,4))))), "")</f>
-        <v>ň</v>
-      </c>
     </row>
-    <row r="9" spans="2:22" ht="30.75" thickBot="1">
+    <row r="9" spans="2:7" ht="19.5" thickBot="1">
       <c r="B9" s="148" t="s">
         <v>872</v>
       </c>
@@ -58553,44 +59399,8 @@
         <v>575</v>
       </c>
       <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="11">
-        <v>6</v>
-      </c>
-      <c r="J9" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E9,4)))), "")</f>
-        <v>ó͘</v>
-      </c>
-      <c r="K9" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
-        <v>á</v>
-      </c>
-      <c r="L9" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
-        <v>í</v>
-      </c>
-      <c r="M9" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
-        <v>ú</v>
-      </c>
-      <c r="N9" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
-        <v>é</v>
-      </c>
-      <c r="O9" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
-        <v>ó</v>
-      </c>
-      <c r="P9" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
-        <v>ḿ</v>
-      </c>
-      <c r="Q9" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E9,4))))), "")</f>
-        <v>ń</v>
-      </c>
     </row>
-    <row r="10" spans="2:22" ht="30.75" thickBot="1">
+    <row r="10" spans="2:7" ht="24.75" thickBot="1">
       <c r="B10" s="147" t="s">
         <v>876</v>
       </c>
@@ -58602,44 +59412,8 @@
         <v>876</v>
       </c>
       <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="11">
-        <v>7</v>
-      </c>
-      <c r="J10" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E10,4)))), "")</f>
-        <v>ō͘</v>
-      </c>
-      <c r="K10" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
-        <v>ā</v>
-      </c>
-      <c r="L10" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
-        <v>ī</v>
-      </c>
-      <c r="M10" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
-        <v>ū</v>
-      </c>
-      <c r="N10" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
-        <v>ē</v>
-      </c>
-      <c r="O10" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
-        <v>ō</v>
-      </c>
-      <c r="P10" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
-        <v>m̄</v>
-      </c>
-      <c r="Q10" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E10,4))))), "")</f>
-        <v>n̄</v>
-      </c>
     </row>
-    <row r="11" spans="2:22" ht="30.75" thickBot="1">
+    <row r="11" spans="2:7" ht="24.75" thickBot="1">
       <c r="B11" s="39" t="s">
         <v>438</v>
       </c>
@@ -58647,44 +59421,8 @@
       <c r="D11" s="39" t="s">
         <v>438</v>
       </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="11">
-        <v>8</v>
-      </c>
-      <c r="J11" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E11,4)))), "")</f>
-        <v>o̍͘</v>
-      </c>
-      <c r="K11" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
-        <v>a̍</v>
-      </c>
-      <c r="L11" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
-        <v>i̍</v>
-      </c>
-      <c r="M11" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
-        <v>u̍</v>
-      </c>
-      <c r="N11" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
-        <v>e̍</v>
-      </c>
-      <c r="O11" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
-        <v>o̍</v>
-      </c>
-      <c r="P11" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
-        <v>m̍</v>
-      </c>
-      <c r="Q11" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E11,4))))), "")</f>
-        <v>n̍</v>
-      </c>
     </row>
-    <row r="12" spans="2:22" ht="30.75" thickBot="1">
+    <row r="12" spans="2:7" ht="24.75" thickBot="1">
       <c r="B12" s="147" t="s">
         <v>444</v>
       </c>
@@ -58692,43 +59430,8 @@
       <c r="D12" s="147" t="s">
         <v>444</v>
       </c>
-      <c r="I12" s="11">
-        <v>9</v>
-      </c>
-      <c r="J12" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E12,4)))), "")</f>
-        <v>ő͘</v>
-      </c>
-      <c r="K12" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
-        <v>a̋</v>
-      </c>
-      <c r="L12" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
-        <v>i̋</v>
-      </c>
-      <c r="M12" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
-        <v>ű</v>
-      </c>
-      <c r="N12" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
-        <v>e̋</v>
-      </c>
-      <c r="O12" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
-        <v>ő</v>
-      </c>
-      <c r="P12" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
-        <v>m̋</v>
-      </c>
-      <c r="Q12" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E12="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E12,4))))), "")</f>
-        <v>n̋</v>
-      </c>
     </row>
-    <row r="13" spans="2:22" ht="35.25" thickBot="1">
+    <row r="13" spans="2:7" ht="35.25" thickBot="1">
       <c r="B13" s="39" t="s">
         <v>875</v>
       </c>
@@ -58737,43 +59440,8 @@
         <f xml:space="preserve"> _xlfn.CONCAT(B12,B10)</f>
         <v>əŋ</v>
       </c>
-      <c r="I13" s="11">
-        <v>0</v>
-      </c>
-      <c r="J13" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT("o", _xlfn.UNICHAR(HEX2DEC(RIGHT("U+0358",4))), _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!E13,4)))), "")</f>
-        <v>o̊͘</v>
-      </c>
-      <c r="K13" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
-        <v>å</v>
-      </c>
-      <c r="L13" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
-        <v>i̊</v>
-      </c>
-      <c r="M13" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
-        <v>ů</v>
-      </c>
-      <c r="N13" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
-        <v>e̊</v>
-      </c>
-      <c r="O13" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
-        <v>o̊</v>
-      </c>
-      <c r="P13" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
-        <v>m̊</v>
-      </c>
-      <c r="Q13" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E13="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E13,4))))), "")</f>
-        <v>n̊</v>
-      </c>
     </row>
-    <row r="14" spans="2:22" ht="26.25" thickBot="1">
+    <row r="14" spans="2:7" ht="24.75" thickBot="1">
       <c r="B14" s="147" t="s">
         <v>878</v>
       </c>
@@ -58782,718 +59450,14 @@
         <v>878</v>
       </c>
     </row>
-    <row r="16" spans="2:22">
-      <c r="J16" s="63" t="s">
-        <v>223</v>
-      </c>
-      <c r="K16" s="63" t="s">
-        <v>267</v>
-      </c>
-      <c r="L16" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="M16" s="63" t="s">
-        <v>249</v>
-      </c>
-      <c r="N16" s="63" t="s">
-        <v>235</v>
-      </c>
-      <c r="O16" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="P16" s="63" t="s">
-        <v>194</v>
-      </c>
-      <c r="S16" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O4,4))), "n"), "")</f>
-        <v>lūn</v>
-      </c>
-      <c r="T16" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O4,4))), "o"), "")</f>
-        <v>ngōo</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" ht="30">
-      <c r="I17" s="11">
-        <v>1</v>
-      </c>
-      <c r="J17" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
-        <v>ā</v>
-      </c>
-      <c r="K17" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
-        <v>ī</v>
-      </c>
-      <c r="L17" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
-        <v>ū</v>
-      </c>
-      <c r="M17" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
-        <v>ē</v>
-      </c>
-      <c r="N17" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
-        <v>ō</v>
-      </c>
-      <c r="O17" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
-        <v>m̄</v>
-      </c>
-      <c r="P17" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E17="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E17,4))))), "")</f>
-        <v>n̄</v>
-      </c>
-      <c r="S17" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O7,4))), "n"), "")</f>
-        <v>lǔn</v>
-      </c>
-      <c r="T17" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O7,4))), "o"), "")</f>
-        <v>ngǒo</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" ht="30">
+    <row r="18" spans="2:2">
       <c r="B18" s="33" t="s">
         <v>579</v>
       </c>
-      <c r="I18" s="11">
-        <v>2</v>
-      </c>
-      <c r="J18" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
-        <v>á</v>
-      </c>
-      <c r="K18" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
-        <v>í</v>
-      </c>
-      <c r="L18" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
-        <v>ú</v>
-      </c>
-      <c r="M18" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
-        <v>é</v>
-      </c>
-      <c r="N18" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
-        <v>ó</v>
-      </c>
-      <c r="O18" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
-        <v>ḿ</v>
-      </c>
-      <c r="P18" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E18="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E18,4))))), "")</f>
-        <v>ń</v>
-      </c>
-      <c r="S18" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O6,4))), "n"), "")</f>
-        <v>lùn</v>
-      </c>
-      <c r="T18" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O6,4))), "o"), "")</f>
-        <v>ngòo</v>
-      </c>
     </row>
-    <row r="19" spans="2:20" ht="30">
+    <row r="19" spans="2:2">
       <c r="B19" s="33" t="s">
         <v>580</v>
-      </c>
-      <c r="I19" s="11">
-        <v>3</v>
-      </c>
-      <c r="J19" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
-        <v>ǎ</v>
-      </c>
-      <c r="K19" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
-        <v>ǐ</v>
-      </c>
-      <c r="L19" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
-        <v>ǔ</v>
-      </c>
-      <c r="M19" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
-        <v>ě</v>
-      </c>
-      <c r="N19" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
-        <v>ǒ</v>
-      </c>
-      <c r="O19" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
-        <v>m̌</v>
-      </c>
-      <c r="P19" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E19="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E19,4))))), "")</f>
-        <v>ň</v>
-      </c>
-      <c r="S19" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O9,4))), "n"), "")</f>
-        <v>lūn</v>
-      </c>
-      <c r="T19" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O9,4))), "o"), "")</f>
-        <v>ngōo</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" ht="30">
-      <c r="I20" s="11">
-        <v>4</v>
-      </c>
-      <c r="J20" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
-        <v>ǎ</v>
-      </c>
-      <c r="K20" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
-        <v>ǐ</v>
-      </c>
-      <c r="L20" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
-        <v>ǔ</v>
-      </c>
-      <c r="M20" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
-        <v>ě</v>
-      </c>
-      <c r="N20" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
-        <v>ǒ</v>
-      </c>
-      <c r="O20" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
-        <v>m̌</v>
-      </c>
-      <c r="P20" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E20="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E20,4))))), "")</f>
-        <v>ň</v>
-      </c>
-      <c r="S20" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O8,4))), "n"), "")</f>
-        <v>lún</v>
-      </c>
-      <c r="T20" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O8,4))), "o"), "")</f>
-        <v>ngóo</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" ht="30">
-      <c r="I21" s="11">
-        <v>5</v>
-      </c>
-      <c r="J21" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
-        <v>à</v>
-      </c>
-      <c r="K21" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
-        <v>ì</v>
-      </c>
-      <c r="L21" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
-        <v>ù</v>
-      </c>
-      <c r="M21" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
-        <v>è</v>
-      </c>
-      <c r="N21" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
-        <v>ò</v>
-      </c>
-      <c r="O21" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
-        <v>m̀</v>
-      </c>
-      <c r="P21" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E21="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E21,4))))), "")</f>
-        <v>ǹ</v>
-      </c>
-      <c r="S21" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O11,4))), "n"), "")</f>
-        <v>lǔn</v>
-      </c>
-      <c r="T21" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O11,4))), "o"), "")</f>
-        <v>ngǒo</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" ht="30">
-      <c r="I22" s="11">
-        <v>6</v>
-      </c>
-      <c r="J22" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
-        <v>â</v>
-      </c>
-      <c r="K22" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
-        <v>î</v>
-      </c>
-      <c r="L22" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
-        <v>û</v>
-      </c>
-      <c r="M22" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
-        <v>ê</v>
-      </c>
-      <c r="N22" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
-        <v>ô</v>
-      </c>
-      <c r="O22" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
-        <v>m̂</v>
-      </c>
-      <c r="P22" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E22="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E22,4))))), "")</f>
-        <v>n̂</v>
-      </c>
-      <c r="S22" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O5,4))), "n"), "")</f>
-        <v>lûn</v>
-      </c>
-      <c r="T22" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O5,4))), "o"), "")</f>
-        <v>ngôo</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" ht="30">
-      <c r="I23" s="11">
-        <v>7</v>
-      </c>
-      <c r="J23" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
-        <v>ā</v>
-      </c>
-      <c r="K23" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
-        <v>ī</v>
-      </c>
-      <c r="L23" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
-        <v>ū</v>
-      </c>
-      <c r="M23" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
-        <v>ē</v>
-      </c>
-      <c r="N23" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
-        <v>ō</v>
-      </c>
-      <c r="O23" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
-        <v>m̄</v>
-      </c>
-      <c r="P23" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E23="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E23,4))))), "")</f>
-        <v>n̄</v>
-      </c>
-      <c r="S23" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("l", "u", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O10,4))), "n"), "")</f>
-        <v>lún</v>
-      </c>
-      <c r="T23" s="11" t="str">
-        <f xml:space="preserve"> IFERROR( _xlfn.CONCAT("n", "g", "o", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$O10,4))), "o"), "")</f>
-        <v>ngóo</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" ht="30">
-      <c r="I24" s="11">
-        <v>8</v>
-      </c>
-      <c r="J24" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
-        <v>á</v>
-      </c>
-      <c r="K24" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
-        <v>í</v>
-      </c>
-      <c r="L24" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
-        <v>ú</v>
-      </c>
-      <c r="M24" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
-        <v>é</v>
-      </c>
-      <c r="N24" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
-        <v>ó</v>
-      </c>
-      <c r="O24" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
-        <v>ḿ</v>
-      </c>
-      <c r="P24" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E24="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E24,4))))), "")</f>
-        <v>ń</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20">
-      <c r="J29" s="63" t="s">
-        <v>223</v>
-      </c>
-      <c r="K29" s="63" t="s">
-        <v>267</v>
-      </c>
-      <c r="L29" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="M29" s="63" t="s">
-        <v>249</v>
-      </c>
-      <c r="N29" s="63" t="s">
-        <v>235</v>
-      </c>
-      <c r="O29" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="P29" s="63" t="s">
-        <v>194</v>
-      </c>
-      <c r="S29" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="T29" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" ht="30">
-      <c r="I30" s="11">
-        <v>1</v>
-      </c>
-      <c r="J30" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
-        <v>a</v>
-      </c>
-      <c r="K30" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
-        <v>i</v>
-      </c>
-      <c r="L30" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
-        <v>u</v>
-      </c>
-      <c r="M30" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
-        <v>e</v>
-      </c>
-      <c r="N30" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
-        <v>o</v>
-      </c>
-      <c r="O30" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
-        <v>m</v>
-      </c>
-      <c r="P30" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$E28="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$E28,4))))), "")</f>
-        <v>n</v>
-      </c>
-      <c r="S30" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
-        <v>lo</v>
-      </c>
-      <c r="T30" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4)))), "r", IF(OR(I30=4, I30=8), "k", "")), "")</f>
-        <v>lor</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" ht="30">
-      <c r="I31" s="11">
-        <v>2</v>
-      </c>
-      <c r="J31" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
-        <v/>
-      </c>
-      <c r="K31" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
-        <v/>
-      </c>
-      <c r="L31" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
-        <v/>
-      </c>
-      <c r="M31" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
-        <v/>
-      </c>
-      <c r="N31" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
-        <v/>
-      </c>
-      <c r="O31" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
-        <v/>
-      </c>
-      <c r="P31" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$M3="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M3,4))))), "")</f>
-        <v/>
-      </c>
-      <c r="S31" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
-        <v>ló</v>
-      </c>
-      <c r="T31" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4)))), "r", IF(OR(I31=4, I31=8), "k", "")), "")</f>
-        <v>lór</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20" ht="30">
-      <c r="I32" s="11">
-        <v>3</v>
-      </c>
-      <c r="J32" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
-        <v>a</v>
-      </c>
-      <c r="K32" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
-        <v>i</v>
-      </c>
-      <c r="L32" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
-        <v>u</v>
-      </c>
-      <c r="M32" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
-        <v>e</v>
-      </c>
-      <c r="N32" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
-        <v>o</v>
-      </c>
-      <c r="O32" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
-        <v>m</v>
-      </c>
-      <c r="P32" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$M4="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M4,4))))), "")</f>
-        <v>n</v>
-      </c>
-      <c r="S32" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
-        <v>lò</v>
-      </c>
-      <c r="T32" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4)))), "r", IF(OR(I32=4, I32=8), "k", "")), "")</f>
-        <v>lòr</v>
-      </c>
-    </row>
-    <row r="33" spans="9:20" ht="30">
-      <c r="I33" s="11">
-        <v>4</v>
-      </c>
-      <c r="J33" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
-        <v>á</v>
-      </c>
-      <c r="K33" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
-        <v>í</v>
-      </c>
-      <c r="L33" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
-        <v>ú</v>
-      </c>
-      <c r="M33" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
-        <v>é</v>
-      </c>
-      <c r="N33" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
-        <v>ó</v>
-      </c>
-      <c r="O33" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
-        <v>ḿ</v>
-      </c>
-      <c r="P33" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$M6="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M6,4))))), "")</f>
-        <v>ń</v>
-      </c>
-      <c r="S33" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4)))), "k"), "")</f>
-        <v>lók</v>
-      </c>
-      <c r="T33" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4)))), "r", IF(OR(I33=4, I33=8), "k", "")), "")</f>
-        <v>lórk</v>
-      </c>
-    </row>
-    <row r="34" spans="9:20" ht="30">
-      <c r="I34" s="11">
-        <v>5</v>
-      </c>
-      <c r="J34" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
-        <v>à</v>
-      </c>
-      <c r="K34" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
-        <v>ì</v>
-      </c>
-      <c r="L34" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
-        <v>ù</v>
-      </c>
-      <c r="M34" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
-        <v>è</v>
-      </c>
-      <c r="N34" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
-        <v>ò</v>
-      </c>
-      <c r="O34" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
-        <v>m̀</v>
-      </c>
-      <c r="P34" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$M7="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M7,4))))), "")</f>
-        <v>ǹ</v>
-      </c>
-      <c r="S34" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
-        <v>lǒ</v>
-      </c>
-      <c r="T34" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4)))), "r", IF(OR(I34=4, I34=8), "k", "")), "")</f>
-        <v>lǒr</v>
-      </c>
-    </row>
-    <row r="35" spans="9:20" ht="30">
-      <c r="I35" s="11">
-        <v>6</v>
-      </c>
-      <c r="J35" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
-        <v>á</v>
-      </c>
-      <c r="K35" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
-        <v>í</v>
-      </c>
-      <c r="L35" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
-        <v>ú</v>
-      </c>
-      <c r="M35" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
-        <v>é</v>
-      </c>
-      <c r="N35" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
-        <v>ó</v>
-      </c>
-      <c r="O35" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
-        <v>ḿ</v>
-      </c>
-      <c r="P35" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$M8="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M8,4))))), "")</f>
-        <v>ń</v>
-      </c>
-      <c r="S35" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
-        <v>ló</v>
-      </c>
-      <c r="T35" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4)))), "r", IF(OR(I35=4, I35=8), "k", "")), "")</f>
-        <v>lór</v>
-      </c>
-    </row>
-    <row r="36" spans="9:20" ht="30">
-      <c r="I36" s="11">
-        <v>7</v>
-      </c>
-      <c r="J36" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
-        <v>ǎ</v>
-      </c>
-      <c r="K36" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
-        <v>ǐ</v>
-      </c>
-      <c r="L36" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
-        <v>ǔ</v>
-      </c>
-      <c r="M36" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
-        <v>ě</v>
-      </c>
-      <c r="N36" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
-        <v>ǒ</v>
-      </c>
-      <c r="O36" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
-        <v>m̌</v>
-      </c>
-      <c r="P36" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$M9="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M9,4))))), "")</f>
-        <v>ň</v>
-      </c>
-      <c r="S36" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M5,4))))), "")</f>
-        <v>lō</v>
-      </c>
-      <c r="T36" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M5="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M5,4)))), "r", IF(OR(I36=4, I36=8), "k", "")), "")</f>
-        <v>lōr</v>
-      </c>
-    </row>
-    <row r="37" spans="9:20" ht="30">
-      <c r="I37" s="11">
-        <v>8</v>
-      </c>
-      <c r="J37" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(K$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
-        <v>á</v>
-      </c>
-      <c r="K37" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(L$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
-        <v>í</v>
-      </c>
-      <c r="L37" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(M$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
-        <v>ú</v>
-      </c>
-      <c r="M37" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(N$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
-        <v>é</v>
-      </c>
-      <c r="N37" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(O$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
-        <v>ó</v>
-      </c>
-      <c r="O37" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(P$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
-        <v>ḿ</v>
-      </c>
-      <c r="P37" s="77" t="str">
-        <f>IFERROR( _xlfn.CONCAT(Q$3, IF(【調】韻母標調!$M11="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M11,4))))), "")</f>
-        <v>ń</v>
-      </c>
-      <c r="S37" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M10,4)))), "k"), "")</f>
-        <v>lo̍k</v>
-      </c>
-      <c r="T37" s="97" t="str">
-        <f>IFERROR( _xlfn.CONCAT("l", "o", IF(【調】韻母標調!$M10="", "", _xlfn.UNICHAR(HEX2DEC(RIGHT(【調】韻母標調!$M10,4)))), "r", IF(OR(I37=4, I37=8), "k", "")), "")</f>
-        <v>lo̍rk</v>
       </c>
     </row>
   </sheetData>
